--- a/src/assets/xlsx/translations.xlsx
+++ b/src/assets/xlsx/translations.xlsx
@@ -14,84 +14,84 @@
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author/>
-    <author>tc={05738eee-845b-436b-9526-3b14bc25132d}</author>
-    <author>tc={095d24a0-ceb8-40a2-9b80-ccbad5dd97ce}</author>
-    <author>tc={09f4e7cb-2300-43c7-a8d6-346ffdf051bd}</author>
-    <author>tc={09ff2aa2-9cbc-4690-84b0-7ed3e4bc8efc}</author>
-    <author>tc={0c6b2add-4a3f-46f9-9082-89f09b601231}</author>
-    <author>tc={125657d9-ef8a-410f-b01e-d20c93c8d8cd}</author>
-    <author>tc={183e35ff-3766-4a1c-8e82-a2736913f9b5}</author>
-    <author>tc={199ad6dd-3501-4fd3-84c5-1cd4aceb521d}</author>
-    <author>tc={1d01c816-c748-4232-82e8-358d5e8d6db9}</author>
-    <author>tc={230eda97-7c65-4055-9fc3-d4a89c3ee95a}</author>
-    <author>tc={261798a4-c59a-433e-9b7d-d47dbbaf965c}</author>
-    <author>tc={29106ef4-2c1b-402c-8b82-02a3250baa12}</author>
-    <author>tc={29c2b519-44e3-45e1-94a4-c99a4877615d}</author>
-    <author>tc={2bf4c17b-f636-4e52-99ed-422d794d9d70}</author>
-    <author>tc={2c4cd90c-8622-477c-81aa-77a8be70c8a7}</author>
-    <author>tc={2e7d5d43-0ec6-4d7f-86fe-6cbc007747a8}</author>
-    <author>tc={3680fb3c-fe26-49c3-80a8-b3695cf43903}</author>
-    <author>tc={36afca42-4a2e-47de-a6a3-b38f509e683a}</author>
-    <author>tc={38c1c8fd-c36c-48cf-b4ee-f5324bb8f334}</author>
-    <author>tc={3ea7c14b-455f-4549-b0a5-47ab339941ae}</author>
-    <author>tc={42d69537-7ca1-4d8f-aaa8-8a19ae5c9f35}</author>
-    <author>tc={461e9a4d-8388-412a-aae8-f04ea0a44482}</author>
-    <author>tc={48d7ce8e-73ad-4915-9dff-cf228eb517ba}</author>
-    <author>tc={4c882b70-bfa0-4514-ace2-818ad374f3d6}</author>
-    <author>tc={4d5b8d4e-e7de-44a3-aaf1-0a8cf576240c}</author>
-    <author>tc={506a9c41-f51f-4a83-ba14-95461c824ef7}</author>
-    <author>tc={50b60560-22ab-416d-b3f2-d897752b43c6}</author>
-    <author>tc={5af38ea6-f33c-4526-99d9-52bf00ad222e}</author>
-    <author>tc={5e19d234-12e3-4dd8-b7ba-ff492b5ef407}</author>
-    <author>tc={62915ae0-5617-4430-8fe4-90455a4dbd95}</author>
-    <author>tc={69751bdb-90af-4dd3-9447-76aabe4f13fe}</author>
-    <author>tc={6a15dc04-d87d-4aa5-8d27-163cd998422c}</author>
-    <author>tc={6bfc90e7-a529-4297-abff-3086791bc4f5}</author>
-    <author>tc={6faab978-2b20-44f0-b3d7-67a87749564d}</author>
-    <author>tc={755b8beb-612d-4ff1-a315-2a95dc38f0e3}</author>
-    <author>tc={76203e11-78e5-46ee-a3de-ece22de2f387}</author>
-    <author>tc={7aa346ad-20a2-4416-b296-90cf15d25294}</author>
-    <author>tc={7b01e9a2-7798-4406-a713-3eaf32d9ca32}</author>
-    <author>tc={7db8b465-aa0b-4f8d-9278-c6fee85dcb7b}</author>
-    <author>tc={83ef9796-bf61-4a0f-a74f-4c21d0b38e20}</author>
-    <author>tc={86d7ffc6-327d-48ed-948b-48599ca2b8ef}</author>
-    <author>tc={871c753d-3906-4b87-8593-d6ce8678ac7b}</author>
-    <author>tc={8a4f013e-762c-45ee-a50b-baca35debd3f}</author>
-    <author>tc={8b817bb4-1df5-442b-a60a-4c44ed154b8c}</author>
-    <author>tc={8ee779ae-b960-4a62-8ac5-a04f1a8b9d2f}</author>
-    <author>tc={8f88c2df-e98b-4a17-8f32-fcab67910b3f}</author>
-    <author>tc={967357b8-a868-4acd-b746-3fb2afa7b64d}</author>
-    <author>tc={96e68654-dd48-436d-ba2f-d6222a7ba18b}</author>
-    <author>tc={98185a0c-9d22-46c1-82b3-154fed723813}</author>
-    <author>tc={a378985e-9c03-4601-ae76-36673e5af1a6}</author>
-    <author>tc={a4247db8-e7d0-4d9c-8de7-35179e7d017b}</author>
-    <author>tc={a596ce0a-ff1e-47d2-9a3b-08b5947f9ea2}</author>
-    <author>tc={b3aebbf4-9cd8-4732-8b0f-3a0b799ab7a6}</author>
-    <author>tc={b44a2d08-b98a-42d2-8d2b-7e241c6808b5}</author>
-    <author>tc={b5181456-eb16-4a9a-9b70-10412a4ec734}</author>
-    <author>tc={b55da5f3-9ea4-40c9-997d-22498a32c5f9}</author>
-    <author>tc={c1e2f56d-3583-4ea5-9c4c-a4a2ade66c29}</author>
-    <author>tc={c3f809d7-68d8-4dd1-af6f-17af5a1aa17f}</author>
-    <author>tc={c9acedbd-d5e3-4b5a-bbc8-4eca725f3262}</author>
-    <author>tc={c9e44899-5ade-4cb8-bf3e-44d35ec7627f}</author>
-    <author>tc={cf0543ab-85a0-49c0-ab0a-df310df21b4c}</author>
-    <author>tc={cf8cf740-314d-4ab7-a7a7-83dbdd78b9d0}</author>
-    <author>tc={d21f074b-3c98-4907-8310-5baed7847c15}</author>
-    <author>tc={d2f66c33-55cf-4e66-a5b0-a7dbf881243e}</author>
-    <author>tc={d6dcc41f-46c5-4ac0-aa26-ad223ac45671}</author>
-    <author>tc={d73f8d07-3c7d-4f88-96cf-887c12d092aa}</author>
-    <author>tc={d9d26a02-38d9-441d-b20a-4090730d88cb}</author>
-    <author>tc={df83af1c-437c-4c47-b3dc-5002fff775bd}</author>
-    <author>tc={e0abb297-1b92-4aeb-8bc0-07df461c455c}</author>
-    <author>tc={e24c064d-e97b-4ad8-80e0-da51fbda7c83}</author>
-    <author>tc={e6dc5e0c-4dc9-4eab-98e6-f2169bdcc938}</author>
-    <author>tc={e9025376-bdba-4586-bb3b-994d27c65656}</author>
-    <author>tc={eac85b5c-76d5-444e-ae58-467ff4302e20}</author>
-    <author>tc={ed25c706-4b16-4d7e-881a-33f63d79cf08}</author>
-    <author>tc={edbf5c5e-7092-46a1-a74d-18ceaf61a177}</author>
-    <author>tc={f4f19ce4-b85f-4922-8185-d088942a8235}</author>
-    <author>tc={f955ea67-5e95-4d09-a683-327fb746a452}</author>
-    <author>tc={ff812722-9c4d-458a-a22d-735ec621f0dd}</author>
+    <author>tc={0642b6e7-f3b4-4604-aa06-56b1f9daecfb}</author>
+    <author>tc={11a504f8-1d02-4656-850c-8aa1902d87df}</author>
+    <author>tc={121fc451-ea23-48d8-a9ea-7e69f55a7e7a}</author>
+    <author>tc={12342dae-419d-4c23-b25b-7edd29130b23}</author>
+    <author>tc={12fd690a-c630-4174-a521-0db06cdf17ff}</author>
+    <author>tc={1456e244-18d2-463f-bb1b-be677acd7065}</author>
+    <author>tc={189bca0b-5553-4f62-87a6-f17ee63347dc}</author>
+    <author>tc={18ea824d-a593-4f70-b2e8-e2ff375afd0a}</author>
+    <author>tc={18fab238-33ec-457f-8457-ff954a98761d}</author>
+    <author>tc={199a0ac3-5bd7-4f80-88ea-131eb216fae1}</author>
+    <author>tc={1d7763f1-c79a-4619-ab6c-2b75c19f9500}</author>
+    <author>tc={1e5296b9-dbad-4083-987f-65e1e5240ad0}</author>
+    <author>tc={20078d2e-a9a8-4d56-a40d-85ef10cac6b0}</author>
+    <author>tc={236c5b68-fd4d-4825-afc8-57d3cc7d5740}</author>
+    <author>tc={236e0b35-3aa9-480f-b355-c657c883b392}</author>
+    <author>tc={254b1eef-136b-4996-bdcd-505897ade49b}</author>
+    <author>tc={25570a33-6c76-4892-9fd6-8211a690375f}</author>
+    <author>tc={25d17016-b1d4-4325-ad64-69767647bf65}</author>
+    <author>tc={27a859a3-133f-48a0-95e3-14a4f878885b}</author>
+    <author>tc={2d94f0be-9556-4d69-8654-3da20ae15feb}</author>
+    <author>tc={2df1de04-3c3b-4de0-9a16-3fde31f67766}</author>
+    <author>tc={2e1627aa-5dd4-4350-b5d8-14cef989b766}</author>
+    <author>tc={319bd969-2d9a-4246-9ee2-831de2a5d16b}</author>
+    <author>tc={3248f61d-8890-4427-a1de-f6ba24530e60}</author>
+    <author>tc={353c4bf7-de6a-4eb1-bf43-f3cffa95358a}</author>
+    <author>tc={37e7f729-3b24-4fb8-b2ef-a18713fe5f35}</author>
+    <author>tc={3bbd5712-2c2f-4bca-a50c-e3061f71ba6d}</author>
+    <author>tc={3ce6be39-397f-4f2d-a369-bc01e5c80a5f}</author>
+    <author>tc={3f9c57a0-b429-4192-bc01-fbaedcda9e99}</author>
+    <author>tc={440f0d14-77f9-4041-b2f1-01c4471c73ce}</author>
+    <author>tc={45c21352-2444-4244-9597-8284cfa31c96}</author>
+    <author>tc={4e8d7dc9-ecb5-44f4-bc6e-8a338b32de5e}</author>
+    <author>tc={4f6acda5-f4c8-4c8e-8424-05ffa41f0f14}</author>
+    <author>tc={575d1362-2d9a-48c3-aa2d-8a2734231c0c}</author>
+    <author>tc={5aca1fcb-eb14-495c-bd9c-4ff8d7064ebc}</author>
+    <author>tc={5be2d6a9-9f46-4c32-81ff-1d5df8b45743}</author>
+    <author>tc={5cd33e73-04ea-4baf-853e-77ff8d79a722}</author>
+    <author>tc={5d8cdf9f-1a22-437e-bc81-2e788ba130d1}</author>
+    <author>tc={62fd50b0-ab69-49b6-ae5e-f8a7c33a70be}</author>
+    <author>tc={6be8c85c-f7a4-4f76-826d-b4c9272fdd2c}</author>
+    <author>tc={71eb0a58-1c32-4dd6-ab7a-1a14cbfd0e5a}</author>
+    <author>tc={7291c08e-d08c-4d42-ade7-5ca3b4084159}</author>
+    <author>tc={7715205c-5f0b-4c02-8e90-2c54d99ed6f1}</author>
+    <author>tc={83617bd9-9e41-4dcb-adba-5c3a3743d318}</author>
+    <author>tc={83f4dd8a-e29f-4f48-9948-d5308573dbbe}</author>
+    <author>tc={89110fac-62ec-4e82-966d-4f8f167f7b30}</author>
+    <author>tc={892fe179-c59d-4e84-8ca6-84aa7fa357b7}</author>
+    <author>tc={8a0d1b13-5dbb-4d92-afb0-99b90d47d197}</author>
+    <author>tc={8a7d8e93-78d6-4daf-a2f0-26b4c94260b1}</author>
+    <author>tc={8aba2c84-630d-47ec-a4c2-c7f99bb28e3a}</author>
+    <author>tc={917ccef4-6e37-40bc-88e7-47651279c387}</author>
+    <author>tc={984b5d1e-3126-4bcc-9ac4-927c104950a0}</author>
+    <author>tc={998ab636-60a7-4401-902e-a291407bcf13}</author>
+    <author>tc={9c28bb68-a2e4-4b24-9d52-193c5ad50568}</author>
+    <author>tc={9c9d9a41-5851-45e0-8f33-bd040e592c6a}</author>
+    <author>tc={9ece4987-cc9b-4a49-9713-10571468e24a}</author>
+    <author>tc={a074977c-c51f-4720-94bf-d48bfd618fd5}</author>
+    <author>tc={a0fa8e44-cb60-4c4a-bea8-24962bde096b}</author>
+    <author>tc={a3d6418e-f8eb-451c-9129-fca03642d421}</author>
+    <author>tc={a4cf48b0-228d-4124-9b4e-6d82e2156821}</author>
+    <author>tc={af621491-136a-4f72-adbd-fe110fd44bdd}</author>
+    <author>tc={afd2880a-2090-429f-b0d9-61a2c81ed722}</author>
+    <author>tc={b297ef8d-a32b-4451-a313-0cc9da6a9145}</author>
+    <author>tc={b331d5b7-57c4-4420-b677-4f4564dff3b7}</author>
+    <author>tc={bea03f73-a1b1-4fb5-82ba-eddbb18e505c}</author>
+    <author>tc={bfdbb542-6cc5-4260-b49f-51887d2cee3e}</author>
+    <author>tc={c3af2e15-5fe9-480a-ba6c-a652344cc8ca}</author>
+    <author>tc={c7620f24-01d0-4306-9a18-9e570b8b62bb}</author>
+    <author>tc={d544cc66-83c1-496b-bf7a-688bf603216e}</author>
+    <author>tc={d59698be-4169-43c4-83c0-f66df470a3a7}</author>
+    <author>tc={d83a8ff2-a011-4457-bf3b-ed78fa652031}</author>
+    <author>tc={dc919a31-9e8b-4ef5-8b77-e2eee98a5cef}</author>
+    <author>tc={e71aa858-6cae-470b-b846-d9c023e5f56e}</author>
+    <author>tc={eab2f0e9-cd66-4950-aa65-8276ce51db6d}</author>
+    <author>tc={eb868fd7-39ca-44a9-b83d-59638c6ad1d1}</author>
+    <author>tc={eccc4054-00f5-4edd-a1cb-3ffc308ac98c}</author>
+    <author>tc={ecdd1fb5-13d4-4e8a-805c-a561e6f1e405}</author>
+    <author>tc={f3c03ad7-edd7-4846-84f3-c8487513eb97}</author>
   </authors>
   <commentList>
     <comment authorId="0" ref="B19">
@@ -100,7 +100,50 @@
 Text between * displays as italics.</t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{05738eee-845b-436b-9526-3b14bc25132d}" ref="A1">
+    <comment authorId="1" xr:uid="{0642b6e7-f3b4-4604-aa06-56b1f9daecfb}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Marked in gray are currently not used in version Act 2 of the site.
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{11a504f8-1d02-4656-850c-8aa1902d87df}" ref="J1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Not part of the Direct demo.
+Please don’t include this language to the site for now.
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{121fc451-ea23-48d8-a9ea-7e69f55a7e7a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	2/3 people (he/him).
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{12342dae-419d-4c23-b25b-7edd29130b23}" ref="L57">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	needs review
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{12fd690a-c630-4174-a521-0db06cdf17ff}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -109,79 +152,43 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{095d24a0-ceb8-40a2-9b80-ccbad5dd97ce}" ref="A1">
+    <comment authorId="6" xr:uid="{1456e244-18d2-463f-bb1b-be677acd7065}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Three people (including proofreader), all go by he/him.
+	Check out https://motherencore.com to see in context.
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{09f4e7cb-2300-43c7-a8d6-346ffdf051bd}" ref="A1">
+    <comment authorId="7" xr:uid="{189bca0b-5553-4f62-87a6-f17ee63347dc}" ref="E9">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Changed "demo" to Act 1
+	Made the MOTHER Shop link into the JP version
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{09ff2aa2-9cbc-4690-84b0-7ed3e4bc8efc}" ref="A1">
+    <comment authorId="8" xr:uid="{18ea824d-a593-4f70-b2e8-e2ff375afd0a}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
+	Marked in gray are currently not used in version Act 2 of the site.
 </t>
       </text>
     </comment>
-    <comment authorId="5" xr:uid="{0c6b2add-4a3f-46f9-9082-89f09b601231}" ref="A1">
+    <comment authorId="9" xr:uid="{18fab238-33ec-457f-8457-ff954a98761d}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	한국어
+	This is Markdown syntax for links, please keep the parentheses and brackets like they are in English.
 </t>
       </text>
     </comment>
-    <comment authorId="6" xr:uid="{125657d9-ef8a-410f-b01e-d20c93c8d8cd}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Just duplicating the Spanish column so it doesn't end up empty
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{183e35ff-3766-4a1c-8e82-a2736913f9b5}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Backslash added to prevent the text from being interpreted as a title.
-</t>
-      </text>
-    </comment>
-    <comment authorId="8" xr:uid="{199ad6dd-3501-4fd3-84c5-1cd4aceb521d}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	This is European Spanish (Español Castellano)
-</t>
-      </text>
-    </comment>
-    <comment authorId="9" xr:uid="{1d01c816-c748-4232-82e8-358d5e8d6db9}" ref="A1">
+    <comment authorId="10" xr:uid="{199a0ac3-5bd7-4f80-88ea-131eb216fae1}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -190,28 +197,45 @@
 </t>
       </text>
     </comment>
-    <comment authorId="10" xr:uid="{230eda97-7c65-4055-9fc3-d4a89c3ee95a}" ref="B63">
+    <comment authorId="11" xr:uid="{1d7763f1-c79a-4619-ab6c-2b75c19f9500}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	![alt_text](image_url)
-You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
-You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
-Click the link on the left to access the Drive folder where to upload your translated image.
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Roots no longer exists, this should be changed or removed.
+Reply:
+	I suggest we remove this paragraph entirely, what do you think @bismuthbloom@gmail.com?
+Reply:
+	Yeah I'm going to remove it with this push.
 </t>
       </text>
     </comment>
-    <comment authorId="11" xr:uid="{261798a4-c59a-433e-9b7d-d47dbbaf965c}" ref="A1">
+    <comment authorId="12" xr:uid="{1e5296b9-dbad-4083-987f-65e1e5240ad0}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Same here.
+	All features are separated into a entry; it's less work than refactoring the spreedsheet 
+parser.
 </t>
       </text>
     </comment>
-    <comment authorId="12" xr:uid="{29106ef4-2c1b-402c-8b82-02a3250baa12}" ref="F18">
+    <comment authorId="13" xr:uid="{20078d2e-a9a8-4d56-a40d-85ef10cac6b0}" ref="L42">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	miiight need a quick review
+</t>
+      </text>
+    </comment>
+    <comment authorId="14" xr:uid="{236c5b68-fd4d-4825-afc8-57d3cc7d5740}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -230,279 +254,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="13" xr:uid="{29c2b519-44e3-45e1-94a4-c99a4877615d}" ref="A1">
+    <comment authorId="15" xr:uid="{236e0b35-3aa9-480f-b355-c657c883b392}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	2/3 people (he/him).
+	Three people: she/her and he/him.
 </t>
       </text>
     </comment>
-    <comment authorId="14" xr:uid="{2bf4c17b-f636-4e52-99ed-422d794d9d70}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	ACT２完成とともにリリース
-</t>
-      </text>
-    </comment>
-    <comment authorId="15" xr:uid="{2c4cd90c-8622-477c-81aa-77a8be70c8a7}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Please mind the final whitespace
-</t>
-      </text>
-    </comment>
-    <comment authorId="16" xr:uid="{2e7d5d43-0ec6-4d7f-86fe-6cbc007747a8}" ref="J1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Don’t include to the site update.
-</t>
-      </text>
-    </comment>
-    <comment authorId="17" xr:uid="{3680fb3c-fe26-49c3-80a8-b3695cf43903}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Two people (he/him).
-</t>
-      </text>
-    </comment>
-    <comment authorId="18" xr:uid="{36afca42-4a2e-47de-a6a3-b38f509e683a}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	she/her
-</t>
-      </text>
-    </comment>
-    <comment authorId="19" xr:uid="{38c1c8fd-c36c-48cf-b4ee-f5324bb8f334}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	“It [Act 1] is entirely playable in (your language)!”
-But I think the English line can remain empty as it’s kinda expected for the game to be playable in English anyway.
-</t>
-      </text>
-    </comment>
-    <comment authorId="20" xr:uid="{3ea7c14b-455f-4549-b0a5-47ab339941ae}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Marked in gray are currently not used in version Act 2 of the site.
-</t>
-      </text>
-    </comment>
-    <comment authorId="21" xr:uid="{42d69537-7ca1-4d8f-aaa8-8a19ae5c9f35}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	ACT1完成とともに変更
-</t>
-      </text>
-    </comment>
-    <comment authorId="22" xr:uid="{461e9a4d-8388-412a-aae8-f04ea0a44482}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Add "[" at the start of the cell. Fixed in the current json file, but for future it should be fixed here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="23" xr:uid="{48d7ce8e-73ad-4915-9dff-cf228eb517ba}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	All features are separated into a entry; it's less work than refactoring the spreedsheet 
-parser.
-</t>
-      </text>
-    </comment>
-    <comment authorId="24" xr:uid="{4c882b70-bfa0-4514-ace2-818ad374f3d6}" ref="F63">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	![몰?루](/Assets/Funny/idk_ko.jpeg)
-</t>
-      </text>
-    </comment>
-    <comment authorId="25" xr:uid="{4d5b8d4e-e7de-44a3-aaf1-0a8cf576240c}" ref="B15">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Edited "wanting for" to "cheering for"
-</t>
-      </text>
-    </comment>
-    <comment authorId="26" xr:uid="{506a9c41-f51f-4a83-ba14-95461c824ef7}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No change needed here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="27" xr:uid="{50b60560-22ab-416d-b3f2-d897752b43c6}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Roots no longer exists, this should be changed or removed.
-Reply:
-	I suggest we remove this paragraph entirely, what do you think @bismuthbloom@gmail.com?
-Reply:
-	Yeah I'm going to remove it with this push.
-</t>
-      </text>
-    </comment>
-    <comment authorId="28" xr:uid="{5af38ea6-f33c-4526-99d9-52bf00ad222e}" ref="E9">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Made the MOTHER Shop link into the JP version
-</t>
-      </text>
-    </comment>
-    <comment authorId="29" xr:uid="{5e19d234-12e3-4dd8-b7ba-ff492b5ef407}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Deutsch
-</t>
-      </text>
-    </comment>
-    <comment authorId="30" xr:uid="{62915ae0-5617-4430-8fe4-90455a4dbd95}" ref="A89">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Include Japanese and Chinese.
-</t>
-      </text>
-    </comment>
-    <comment authorId="31" xr:uid="{69751bdb-90af-4dd3-9447-76aabe4f13fe}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No change needed here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="32" xr:uid="{6a15dc04-d87d-4aa5-8d27-163cd998422c}" ref="E79">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	援のお気持ちありがとうございます！この作品はあくまでファンゲームですので、お金は一切受け取りません。サポートしていただきたい場合はファンゲームを広めるか、作品の開発陣の個別のプロジェクトに支援できます。また、クレジットページにて開発陣のSNSへのリンクがございますので、そちらからフォローしてみることもできます。
-</t>
-      </text>
-    </comment>
-    <comment authorId="33" xr:uid="{6bfc90e7-a529-4297-abff-3086791bc4f5}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Italiano
-</t>
-      </text>
-    </comment>
-    <comment authorId="34" xr:uid="{6faab978-2b20-44f0-b3d7-67a87749564d}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Check out https://motherencore.com to see in context.
-</t>
-      </text>
-    </comment>
-    <comment authorId="35" xr:uid="{755b8beb-612d-4ff1-a315-2a95dc38f0e3}" ref="E15">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Proofreading needed
-</t>
-      </text>
-    </comment>
-    <comment authorId="36" xr:uid="{76203e11-78e5-46ee-a3de-ece22de2f387}" ref="L40">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	eh
-</t>
-      </text>
-    </comment>
-    <comment authorId="37" xr:uid="{7aa346ad-20a2-4416-b296-90cf15d25294}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Polski
-</t>
-      </text>
-    </comment>
-    <comment authorId="38" xr:uid="{7b01e9a2-7798-4406-a713-3eaf32d9ca32}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	From here, roles have to be singular and gender-neutral.
-If “programmer” can’t be gender-neutral in your language, you can go with “programming” (see next column) instead, and so on.
-Once a cell is done, you can remove the bold style.
-</t>
-      </text>
-    </comment>
-    <comment authorId="39" xr:uid="{7db8b465-aa0b-4f8d-9278-c6fee85dcb7b}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Two people (he/him)
-</t>
-      </text>
-    </comment>
-    <comment authorId="40" xr:uid="{83ef9796-bf61-4a0f-a74f-4c21d0b38e20}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Two people: she/her and he/him.
-</t>
-      </text>
-    </comment>
-    <comment authorId="41" xr:uid="{86d7ffc6-327d-48ed-948b-48599ca2b8ef}" ref="A1">
+    <comment authorId="16" xr:uid="{254b1eef-136b-4996-bdcd-505897ade49b}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -511,7 +272,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="42" xr:uid="{871c753d-3906-4b87-8593-d6ce8678ac7b}" ref="J1">
+    <comment authorId="17" xr:uid="{25570a33-6c76-4892-9fd6-8211a690375f}" ref="F63">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -519,20 +280,15 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Don’t include to the site update.
+	where should I post 'Assets/Funny/idk_kr.png'?
+Reply:
+	If you made your own image, you can put it here: https://drive.google.com/drive/folders/1NLNj-Z_oVAlbAMDAWYYLLhvqIfbirBr4
+Reply:
+	ok!
 </t>
       </text>
     </comment>
-    <comment authorId="43" xr:uid="{8a4f013e-762c-45ee-a50b-baca35debd3f}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	English
-</t>
-      </text>
-    </comment>
-    <comment authorId="44" xr:uid="{8b817bb4-1df5-442b-a60a-4c44ed154b8c}" ref="A1">
+    <comment authorId="18" xr:uid="{25d17016-b1d4-4325-ad64-69767647bf65}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -546,46 +302,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="45" xr:uid="{8ee779ae-b960-4a62-8ac5-a04f1a8b9d2f}" ref="A1">
+    <comment authorId="19" xr:uid="{27a859a3-133f-48a0-95e3-14a4f878885b}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	This is Markdown syntax for links, please keep the parentheses and brackets like they are in English.
+	Same here.
 </t>
       </text>
     </comment>
-    <comment authorId="46" xr:uid="{8f88c2df-e98b-4a17-8f32-fcab67910b3f}" ref="L42">
+    <comment authorId="20" xr:uid="{2d94f0be-9556-4d69-8654-3da20ae15feb}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	miiight need a quick review
+	This one doesn’t need to be changed, as it already applied to one single person.
 </t>
       </text>
     </comment>
-    <comment authorId="47" xr:uid="{967357b8-a868-4acd-b746-3fb2afa7b64d}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Three people: she/her and he/him.
-</t>
-      </text>
-    </comment>
-    <comment authorId="48" xr:uid="{96e68654-dd48-436d-ba2f-d6222a7ba18b}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Three people: she/her and he/him.
-</t>
-      </text>
-    </comment>
-    <comment authorId="49" xr:uid="{98185a0c-9d22-46c1-82b3-154fed723813}" ref="A1">
+    <comment authorId="21" xr:uid="{2df1de04-3c3b-4de0-9a16-3fde31f67766}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -597,7 +332,19 @@
 </t>
       </text>
     </comment>
-    <comment authorId="50" xr:uid="{a378985e-9c03-4601-ae76-36673e5af1a6}" ref="B63">
+    <comment authorId="22" xr:uid="{2e1627aa-5dd4-4350-b5d8-14cef989b766}" ref="L31">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	turnipman i beg you give this a look
+</t>
+      </text>
+    </comment>
+    <comment authorId="23" xr:uid="{319bd969-2d9a-4246-9ee2-831de2a5d16b}" ref="B63">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -609,7 +356,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="51" xr:uid="{a4247db8-e7d0-4d9c-8de7-35179e7d017b}" ref="B63">
+    <comment authorId="24" xr:uid="{3248f61d-8890-4427-a1de-f6ba24530e60}" ref="L49">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -617,13 +364,65 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	The English answer is an image:
-https://motherencore.com/Assets/Funny/idk.png
-If you want to use an image in your language too, please specify its full url.
+	wip
 </t>
       </text>
     </comment>
-    <comment authorId="52" xr:uid="{a596ce0a-ff1e-47d2-9a3b-08b5947f9ea2}" ref="E90">
+    <comment authorId="25" xr:uid="{353c4bf7-de6a-4eb1-bf43-f3cffa95358a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	This is European Spanish (Español Castellano)
+</t>
+      </text>
+    </comment>
+    <comment authorId="26" xr:uid="{37e7f729-3b24-4fb8-b2ef-a18713fe5f35}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	실제 웹사이트에 따라 수정 필요
+Modify according to the website
+</t>
+      </text>
+    </comment>
+    <comment authorId="27" xr:uid="{3bbd5712-2c2f-4bca-a50c-e3061f71ba6d}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Three people (including proofreader), all go by he/him.
+</t>
+      </text>
+    </comment>
+    <comment authorId="28" xr:uid="{3ce6be39-397f-4f2d-a369-bc01e5c80a5f}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	From here, roles have to be singular and gender-neutral.
+If “programmer” can’t be gender-neutral in your language, you can go with “programming” (see next column) instead, and so on.
+Once a cell is done, you can remove the bold style.
+</t>
+      </text>
+    </comment>
+    <comment authorId="29" xr:uid="{3f9c57a0-b429-4192-bc01-fbaedcda9e99}" ref="K1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Don’t include to the site update.
+</t>
+      </text>
+    </comment>
+    <comment authorId="30" xr:uid="{440f0d14-77f9-4041-b2f1-01c4471c73ce}" ref="E90">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -632,16 +431,56 @@
 </t>
       </text>
     </comment>
-    <comment authorId="53" xr:uid="{b3aebbf4-9cd8-4732-8b0f-3a0b799ab7a6}" ref="A1">
+    <comment authorId="31" xr:uid="{45c21352-2444-4244-9597-8284cfa31c96}" ref="F10">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Two people, he/him and any pronouns.
+	실제 웹사이트에 따라 수정 필요
+Modify according to the website
 </t>
       </text>
     </comment>
-    <comment authorId="54" xr:uid="{b44a2d08-b98a-42d2-8d2b-7e241c6808b5}" ref="B31">
+    <comment authorId="32" xr:uid="{4e8d7dc9-ecb5-44f4-bc6e-8a338b32de5e}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	English
+</t>
+      </text>
+    </comment>
+    <comment authorId="33" xr:uid="{4f6acda5-f4c8-4c8e-8424-05ffa41f0f14}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	한국어
+</t>
+      </text>
+    </comment>
+    <comment authorId="34" xr:uid="{575d1362-2d9a-48c3-aa2d-8a2734231c0c}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	she/her
+</t>
+      </text>
+    </comment>
+    <comment authorId="35" xr:uid="{5aca1fcb-eb14-495c-bd9c-4ff8d7064ebc}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	These links are deprecated.
+</t>
+      </text>
+    </comment>
+    <comment authorId="36" xr:uid="{5be2d6a9-9f46-4c32-81ff-1d5df8b45743}" ref="B31">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -663,16 +502,61 @@
 </t>
       </text>
     </comment>
-    <comment authorId="55" xr:uid="{b5181456-eb16-4a9a-9b70-10412a4ec734}" ref="A1">
+    <comment authorId="37" xr:uid="{5cd33e73-04ea-4baf-853e-77ff8d79a722}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	These links are deprecated.
+	Marked in gray are currently not used in version Act 2 of the site.
 </t>
       </text>
     </comment>
-    <comment authorId="56" xr:uid="{b55da5f3-9ea4-40c9-997d-22498a32c5f9}" ref="A1">
+    <comment authorId="38" xr:uid="{5d8cdf9f-1a22-437e-bc81-2e788ba130d1}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No change needed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="39" xr:uid="{62fd50b0-ab69-49b6-ae5e-f8a7c33a70be}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Polski
+</t>
+      </text>
+    </comment>
+    <comment authorId="40" xr:uid="{6be8c85c-f7a4-4f76-826d-b4c9272fdd2c}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Français
+</t>
+      </text>
+    </comment>
+    <comment authorId="41" xr:uid="{71eb0a58-1c32-4dd6-ab7a-1a14cbfd0e5a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Português brasileiro
+</t>
+      </text>
+    </comment>
+    <comment authorId="42" xr:uid="{7291c08e-d08c-4d42-ade7-5ca3b4084159}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Three people: she/her and he/him.
+</t>
+      </text>
+    </comment>
+    <comment authorId="43" xr:uid="{7715205c-5f0b-4c02-8e90-2c54d99ed6f1}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -681,16 +565,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="57" xr:uid="{c1e2f56d-3583-4ea5-9c4c-a4a2ade66c29}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Français
-</t>
-      </text>
-    </comment>
-    <comment authorId="58" xr:uid="{c3f809d7-68d8-4dd1-af6f-17af5a1aa17f}" ref="L57">
+    <comment authorId="44" xr:uid="{83617bd9-9e41-4dcb-adba-5c3a3743d318}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -698,11 +573,50 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	needs review
+	Backslash added to prevent the text from being interpreted as a title.
 </t>
       </text>
     </comment>
-    <comment authorId="59" xr:uid="{c9acedbd-d5e3-4b5a-bbc8-4eca725f3262}" ref="K1">
+    <comment authorId="45" xr:uid="{83f4dd8a-e29f-4f48-9948-d5308573dbbe}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
+</t>
+      </text>
+    </comment>
+    <comment authorId="46" xr:uid="{89110fac-62ec-4e82-966d-4f8f167f7b30}" ref="E79">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	援のお気持ちありがとうございます！この作品はあくまでファンゲームですので、お金は一切受け取りません。サポートしていただきたい場合はファンゲームを広めるか、作品の開発陣の個別のプロジェクトに支援できます。また、クレジットページにて開発陣のSNSへのリンクがございますので、そちらからフォローしてみることもできます。
+</t>
+      </text>
+    </comment>
+    <comment authorId="47" xr:uid="{892fe179-c59d-4e84-8ca6-84aa7fa357b7}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ACT２完成とともにリリース
+</t>
+      </text>
+    </comment>
+    <comment authorId="48" xr:uid="{8a0d1b13-5dbb-4d92-afb0-99b90d47d197}" ref="L27">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	can replace "недруг" with "ворог", but generally just needs review
+</t>
+      </text>
+    </comment>
+    <comment authorId="49" xr:uid="{8a7d8e93-78d6-4daf-a2f0-26b4c94260b1}" ref="J1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -714,28 +628,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="60" xr:uid="{c9e44899-5ade-4cb8-bf3e-44d35ec7627f}" ref="L27">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	can replace "недруг" with "ворог", but generally just needs review
-</t>
-      </text>
-    </comment>
-    <comment authorId="61" xr:uid="{cf0543ab-85a0-49c0-ab0a-df310df21b4c}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
-</t>
-      </text>
-    </comment>
-    <comment authorId="62" xr:uid="{cf8cf740-314d-4ab7-a7a7-83dbdd78b9d0}" ref="A1">
+    <comment authorId="50" xr:uid="{8aba2c84-630d-47ec-a4c2-c7f99bb28e3a}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -744,16 +637,82 @@
 </t>
       </text>
     </comment>
-    <comment authorId="63" xr:uid="{d21f074b-3c98-4907-8310-5baed7847c15}" ref="A1">
+    <comment authorId="51" xr:uid="{917ccef4-6e37-40bc-88e7-47651279c387}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Español
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Changed "demo" to Act 1
 </t>
       </text>
     </comment>
-    <comment authorId="64" xr:uid="{d2f66c33-55cf-4e66-a5b0-a7dbf881243e}" ref="F1">
+    <comment authorId="52" xr:uid="{984b5d1e-3126-4bcc-9ac4-927c104950a0}" ref="L40">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	eh
+</t>
+      </text>
+    </comment>
+    <comment authorId="53" xr:uid="{998ab636-60a7-4401-902e-a291407bcf13}" ref="A89">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Include Japanese and Chinese.
+</t>
+      </text>
+    </comment>
+    <comment authorId="54" xr:uid="{9c28bb68-a2e4-4b24-9d52-193c5ad50568}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Sam uses she/her pronouns now, change your translations if needed
+</t>
+      </text>
+    </comment>
+    <comment authorId="55" xr:uid="{9c9d9a41-5851-45e0-8f33-bd040e592c6a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Deutsch
+</t>
+      </text>
+    </comment>
+    <comment authorId="56" xr:uid="{9ece4987-cc9b-4a49-9713-10571468e24a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Two people (he/him)
+</t>
+      </text>
+    </comment>
+    <comment authorId="57" xr:uid="{a074977c-c51f-4720-94bf-d48bfd618fd5}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Two people, he/him and any pronouns.
+</t>
+      </text>
+    </comment>
+    <comment authorId="58" xr:uid="{a0fa8e44-cb60-4c4a-bea8-24962bde096b}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No change needed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="59" xr:uid="{a3d6418e-f8eb-451c-9129-fca03642d421}" ref="F1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -766,63 +725,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="65" xr:uid="{d6dcc41f-46c5-4ac0-aa26-ad223ac45671}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	This one doesn’t need to be changed, as it already applied to one single person.
-</t>
-      </text>
-    </comment>
-    <comment authorId="66" xr:uid="{d73f8d07-3c7d-4f88-96cf-887c12d092aa}" ref="L31">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	turnipman i beg you give this a look
-</t>
-      </text>
-    </comment>
-    <comment authorId="67" xr:uid="{d9d26a02-38d9-441d-b20a-4090730d88cb}" ref="F63">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	where should I post 'Assets/Funny/idk_kr.png'?
-Reply:
-	If you made your own image, you can put it here: https://drive.google.com/drive/folders/1NLNj-Z_oVAlbAMDAWYYLLhvqIfbirBr4
-Reply:
-	ok!
-</t>
-      </text>
-    </comment>
-    <comment authorId="68" xr:uid="{df83af1c-437c-4c47-b3dc-5002fff775bd}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Sam uses she/her pronouns now, change your translations if needed
-</t>
-      </text>
-    </comment>
-    <comment authorId="69" xr:uid="{e0abb297-1b92-4aeb-8bc0-07df461c455c}" ref="F10">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	실제 웹사이트에 따라 수정 필요
-Modify according to the website
-</t>
-      </text>
-    </comment>
-    <comment authorId="70" xr:uid="{e24c064d-e97b-4ad8-80e0-da51fbda7c83}" ref="A1">
+    <comment authorId="60" xr:uid="{a4cf48b0-228d-4124-9b4e-6d82e2156821}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -831,16 +734,19 @@
 </t>
       </text>
     </comment>
-    <comment authorId="71" xr:uid="{e6dc5e0c-4dc9-4eab-98e6-f2169bdcc938}" ref="A1">
+    <comment authorId="61" xr:uid="{af621491-136a-4f72-adbd-fe110fd44bdd}" ref="B63">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Português brasileiro
+	![alt_text](image_url)
+You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
+You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
+Click the link on the left to access the Drive folder where to upload your translated image.
 </t>
       </text>
     </comment>
-    <comment authorId="72" xr:uid="{e9025376-bdba-4586-bb3b-994d27c65656}" ref="L49">
+    <comment authorId="62" xr:uid="{afd2880a-2090-429f-b0d9-61a2c81ed722}" ref="J1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -848,29 +754,155 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	wip
+	Don’t include to the site update.
 </t>
       </text>
     </comment>
-    <comment authorId="73" xr:uid="{eac85b5c-76d5-444e-ae58-467ff4302e20}" ref="A1">
+    <comment authorId="63" xr:uid="{b297ef8d-a32b-4451-a313-0cc9da6a9145}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Marked in gray are currently not used in version Act 2 of the site.
+	“It [Act 1] is entirely playable in (your language)!”
+But I think the English line can remain empty as it’s kinda expected for the game to be playable in English anyway.
 </t>
       </text>
     </comment>
-    <comment authorId="74" xr:uid="{ed25c706-4b16-4d7e-881a-33f63d79cf08}" ref="A1">
+    <comment authorId="64" xr:uid="{b331d5b7-57c4-4420-b677-4f4564dff3b7}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Marked in gray are currently not used in version Act 2 of the site.
+	Two people (he/him).
 </t>
       </text>
     </comment>
-    <comment authorId="75" xr:uid="{edbf5c5e-7092-46a1-a74d-18ceaf61a177}" ref="L44">
+    <comment authorId="65" xr:uid="{bea03f73-a1b1-4fb5-82ba-eddbb18e505c}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Español
+</t>
+      </text>
+    </comment>
+    <comment authorId="66" xr:uid="{bfdbb542-6cc5-4260-b49f-51887d2cee3e}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Italiano
+</t>
+      </text>
+    </comment>
+    <comment authorId="67" xr:uid="{c3af2e15-5fe9-480a-ba6c-a652344cc8ca}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Please mind the final whitespace
+</t>
+      </text>
+    </comment>
+    <comment authorId="68" xr:uid="{c7620f24-01d0-4306-9a18-9e570b8b62bb}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Two people: she/her and he/him.
+</t>
+      </text>
+    </comment>
+    <comment authorId="69" xr:uid="{d544cc66-83c1-496b-bf7a-688bf603216e}" ref="E15">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Proofreading needed
+</t>
+      </text>
+    </comment>
+    <comment authorId="70" xr:uid="{d59698be-4169-43c4-83c0-f66df470a3a7}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Русский
+</t>
+      </text>
+    </comment>
+    <comment authorId="71" xr:uid="{d83a8ff2-a011-4457-bf3b-ed78fa652031}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ACT1完成とともに変更
+</t>
+      </text>
+    </comment>
+    <comment authorId="72" xr:uid="{dc919a31-9e8b-4ef5-8b77-e2eee98a5cef}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Add "[" at the start of the cell. Fixed in the current json file, but for future it should be fixed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="73" xr:uid="{e71aa858-6cae-470b-b846-d9c023e5f56e}" ref="B63">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	The English answer is an image:
+https://motherencore.com/Assets/Funny/idk.png
+If you want to use an image in your language too, please specify its full url.
+</t>
+      </text>
+    </comment>
+    <comment authorId="74" xr:uid="{eab2f0e9-cd66-4950-aa65-8276ce51db6d}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Just duplicating the Spanish column so it doesn't end up empty
+</t>
+      </text>
+    </comment>
+    <comment authorId="75" xr:uid="{eb868fd7-39ca-44a9-b83d-59638c6ad1d1}" ref="B15">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Edited "wanting for" to "cheering for"
+</t>
+      </text>
+    </comment>
+    <comment authorId="76" xr:uid="{eccc4054-00f5-4edd-a1cb-3ffc308ac98c}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
+</t>
+      </text>
+    </comment>
+    <comment authorId="77" xr:uid="{ecdd1fb5-13d4-4e8a-805c-a561e6f1e405}" ref="F63">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	![몰?루](/Assets/Funny/idk_ko.jpeg)
+</t>
+      </text>
+    </comment>
+    <comment authorId="78" xr:uid="{f3c03ad7-edd7-4846-84f3-c8487513eb97}" ref="L44">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -882,44 +914,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="76" xr:uid="{f4f19ce4-b85f-4922-8185-d088942a8235}" ref="J1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Not part of the Direct demo.
-Please don’t include this language to the site for now.
-</t>
-      </text>
-    </comment>
-    <comment authorId="77" xr:uid="{f955ea67-5e95-4d09-a683-327fb746a452}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	실제 웹사이트에 따라 수정 필요
-Modify according to the website
-</t>
-      </text>
-    </comment>
-    <comment authorId="78" xr:uid="{ff812722-9c4d-458a-a22d-735ec621f0dd}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Русский
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="1115">
   <si>
     <t>key</t>
   </si>
@@ -2069,7 +2069,7 @@
     <t>El sistema de combate de Encore introduce mecánicas totalmente nuevas! Con Puntos de Habilidad, Encores, Subidones de adrenalina y mucho más, ¡hay un sinfín de formas únicas de enfrentarse a los enemigos! Tendrás que analizar todas tus opciones y pensar con rapidez para poder derrotar a los peligrosos adversarios de este juego.</t>
   </si>
   <si>
-    <t>O sistema de batalhas do Encore traz mecânicas completamente novas! Com Pontos de Habilidade, Bis, Picos de Adrenalinae muito mais, você terá uma porção de formas únicas de encarar os inimigos! Analise bem suas opções e tenha um racicínio rápido para derrotar os vilões mais poderosos do jogo.</t>
+    <t>O sistema de batalhas do Encore traz mecânicas completamente novas! Com Pontos de Habilidade, Bis, Picos de Adrenalina e muito mais, você terá uma porção de formas diferentes de encarar os inimigos! Analise bem suas opções e tenha um racicínio rápido para derrotar os vilões mais poderosos do jogo.</t>
   </si>
   <si>
     <t>System walki Encore wprowadza zupełnie nowe mechaniki! Dzięki Punktom Umiejętności, Paskiem Encore, Przypływom Adrenaliny i nie tylko, masz do dyspozycji mnóstwo unikalnych sposobów na walkę z przeciwnikami! Aby pokonać swoich wrogów, będziesz musiał rozważyć wszystkie dostępne opcje i polegać na szybkim myśleniu.</t>
@@ -2103,6 +2103,9 @@
   </si>
   <si>
     <t>Habilidades de Campo y Mazmorras</t>
+  </si>
+  <si>
+    <t>Habilidades de Campo e Masmorras</t>
   </si>
   <si>
     <t>Umiejętności w Polu i Lochy</t>
@@ -2137,6 +2140,9 @@
   </si>
   <si>
     <t>Una de las novedades en la serie son las habilidades de campo que podrás desbloquear para los miembros de tu equipo. Al usar estas habilidades, podrás abrir nuevos caminos, resolver acertijos y obtener ventaja frente a los enemigos en el mundo exterior. ¡Encore también incluye nuevas mazmorras repletas de obstáculos únicos, algo nunca antes visto en la saga!</t>
+  </si>
+  <si>
+    <t>Descubra as Habilidades de Campo, algo totalmente novo na série. Ao usá-las, a sua equipe vai descobrir novos caminhos, resolver quebra-cabeças e ganhar vantagem sobre os inimigos que encontra pela frente.</t>
   </si>
   <si>
     <t>Nowością w serii są umiejętności w polu, które można odblokować dla członków drużyny. Korzystając z tych umiejętności, można odkrywać nowe ścieżki, rozwiązywać zagadki i zyskać przewagę nad przeciwnikami w świecie gry. W Encore pojawiają się również nowe lochy pełne unikalnych przeszkód, jakich dotąd nie było w całej serii!</t>
@@ -4884,39 +4890,39 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Andy" id="{d151c2a0-df19-4a14-9347-cc048611ea99}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={886a0772-a652-4cf0-8001-6b3b369f02a7}" id="{d3d454b3-be32-4bb5-9ee5-0d02d4739b1d}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={7f01b7a3-72ee-45c2-bb66-47cec55f0069}" id="{21c183e5-9d7b-46bd-85b8-31dfe0e576e6}" providerId="google-sheets"/>
-  <x18tc:person displayName="It should say" id="{734320e5-3e20-4768-83aa-53fd6d00a2b2}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={98457d25-d0e2-4f46-8629-2eaf29491de7}" id="{b2c8d6ce-ed5d-4bfe-a786-3e1a9e9b6b2f}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={d86d4f9a-16ae-41c7-9220-a1a73203876c}" id="{acfa75f9-e96f-4a9d-b110-d76db84ecc81}" providerId="google-sheets"/>
-  <x18tc:person displayName="Syntax to insert an image" id="{dd040edc-d412-4a96-8a30-abb5cd966182}" providerId="google-sheets"/>
-  <x18tc:person displayName="" id="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={9da47017-07ee-4d8c-ba08-4a3c2c6332e0}" id="{79188f1b-0105-4ab4-aeb0-86a488fff33a}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={c19c0cfe-a1f1-4cc9-801e-857fe26d952a}" id="{a36c2a8d-b724-4d89-871a-baf15cfce510}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={55cd3fa3-199c-4632-b417-fba209b2594a}" id="{1d1bb5d7-5d98-4532-87ed-e34446609da0}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={0f6dd66b-869f-43d9-bfc0-15b956d18e2a}" id="{d10fe3df-7870-406e-9e16-703c12e7db6a}" providerId="google-sheets"/>
-  <x18tc:person displayName="보석" id="{4e11369d-42ba-45a1-a47a-c31b13620b63}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={5a18eb6c-3f60-4d37-bd2e-2acc3dc98df8}" id="{8fab866b-6aa9-45e6-860d-f11a7c4bffda}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={8da23618-7fc8-4c86-b361-946024645808}" id="{4749739d-aeed-4068-b876-49049b7ad38e}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={87e287a5-c153-40cd-8eed-ec1ec11e568f}" id="{47cee458-8efd-41a9-a03c-c342bb360b7f}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={a2cbbe23-89a4-4696-b8de-12871cb556b8}" id="{53e833d9-b9d0-4887-b728-01a42f8a339f}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={deef05f7-aa29-4a9a-b653-f24d312406f7}" id="{796dbae4-16a5-41f7-91db-495707a85ef4}" providerId="google-sheets"/>
-  <x18tc:person displayName="Marcos Vinicios de Morais" id="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={97913bf9-94e4-4a63-ba01-4e25533c8a02}" id="{70ec7af7-55ed-4fb9-b7ec-1fcfe9c10dfa}" providerId="google-sheets"/>
-  <x18tc:person displayName="baka (Jimmy)" id="{3ab0c541-064f-429b-b0a6-a8589bd53b0b}" providerId="google-sheets"/>
-  <x18tc:person displayName="Danionel" id="{246dcbe0-778a-43e4-b72d-0d0312407132}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={f1835a49-7095-4a4b-b082-eb4c7d31c679}" id="{1b00e706-acda-430a-aac4-4c408fcec4dc}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={63b80276-1f1f-4158-9545-ffdd2d21ecb7}" id="{772c79a3-2dae-4bca-aac7-1c4bb53246a2}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={c88575e6-dacb-4386-bb27-227fb486ed9f}" id="{01d5d661-c192-4d64-8a19-7116b17f11ae}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={3d82b67f-ed31-46ae-aa73-752050e5b296}" id="{34e09fae-62a4-4d13-9da1-f5bb61d2bcf2}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={4508b080-7cdf-41ca-90b8-fa03db8b7544}" id="{52310717-a935-40d2-8377-647ec71bc542}" providerId="google-sheets"/>
-  <x18tc:person displayName="bismuthbloom@gmail.com" id="{d80c5444-42e7-48f2-b20f-ea5b137230c2}" userId="bismuthbloom@gmail.com" providerId="google-sheets"/>
-  <x18tc:person displayName="Aiden" id="{4fb1da2c-5e0c-4f84-b793-b51b84947830}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={8a68bd66-5614-411f-a5a4-51e9af64d185}" id="{94fc03d0-6a11-431d-83f8-0b421a1a61b3}" providerId="google-sheets"/>
-  <x18tc:person displayName="Altoz Bass Tenor" id="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={1aa364c2-7f01-4995-b24e-a3f74b1607eb}" id="{a6aa3007-2310-46af-83db-ecaf2f45afe8}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={71cb1f5f-bab7-4f22-9d94-7a0e119fa63f}" id="{114be160-6969-4eb2-a033-1d8f8cdf42ba}" providerId="google-sheets"/>
+  <x18tc:person displayName="Andy" id="{4fba8901-5e79-4213-a246-9289d576f53a}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={886a0772-a652-4cf0-8001-6b3b369f02a7}" id="{99440684-8175-4bcb-a12a-bdecccba751e}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={7f01b7a3-72ee-45c2-bb66-47cec55f0069}" id="{b09a6581-30bf-468e-8cdf-e9f4ced06365}" providerId="google-sheets"/>
+  <x18tc:person displayName="It should say" id="{cfe4d3c8-9ff0-4254-9df9-7b9777a6b7ce}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={98457d25-d0e2-4f46-8629-2eaf29491de7}" id="{393e095c-a9b4-4efd-b880-1b06d7906940}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={d86d4f9a-16ae-41c7-9220-a1a73203876c}" id="{8cb374ec-11d9-41c5-a2b1-6d0a7a82415a}" providerId="google-sheets"/>
+  <x18tc:person displayName="Syntax to insert an image" id="{c59b55aa-5ec8-434d-8510-c76cc13d10e6}" providerId="google-sheets"/>
+  <x18tc:person displayName="" id="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={9da47017-07ee-4d8c-ba08-4a3c2c6332e0}" id="{433f50a8-b52f-4fdc-b0a0-9cb56881224f}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={c19c0cfe-a1f1-4cc9-801e-857fe26d952a}" id="{dc0bc8fa-6629-4d8b-a9a4-ed9e49205ce6}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={55cd3fa3-199c-4632-b417-fba209b2594a}" id="{5926c0a2-f205-44d3-ab48-a1a9d9b27bad}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={0f6dd66b-869f-43d9-bfc0-15b956d18e2a}" id="{82213706-1931-455f-9aa7-94154deca2ec}" providerId="google-sheets"/>
+  <x18tc:person displayName="보석" id="{574b93ef-cc8d-4e7c-962a-78f24313b660}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={5a18eb6c-3f60-4d37-bd2e-2acc3dc98df8}" id="{f9d1c842-95e0-483e-88dd-f76a75a427c9}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={8da23618-7fc8-4c86-b361-946024645808}" id="{3d83710b-27d9-4891-8de2-8241e0d433e9}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={87e287a5-c153-40cd-8eed-ec1ec11e568f}" id="{03f80cf0-65a9-4dd5-9d10-12f603c66674}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={a2cbbe23-89a4-4696-b8de-12871cb556b8}" id="{463e3740-b99a-4848-abc8-3cfd28b0b271}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={deef05f7-aa29-4a9a-b653-f24d312406f7}" id="{15813a55-54b5-411f-9ac9-feffd08ad44d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Marcos Vinicios de Morais" id="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={97913bf9-94e4-4a63-ba01-4e25533c8a02}" id="{274e15c0-a8c4-4c15-a44e-7125c0e875ff}" providerId="google-sheets"/>
+  <x18tc:person displayName="baka (Jimmy)" id="{863e4ceb-3fab-4cc6-b694-9d4d60fa0df6}" providerId="google-sheets"/>
+  <x18tc:person displayName="Danionel" id="{7953a82e-e467-4643-b007-a362f669553d}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={f1835a49-7095-4a4b-b082-eb4c7d31c679}" id="{2356a069-2a83-45e0-9157-9e96de2f329f}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={63b80276-1f1f-4158-9545-ffdd2d21ecb7}" id="{50dc71f3-9ebb-4197-9935-5ef91e119911}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={c88575e6-dacb-4386-bb27-227fb486ed9f}" id="{0719f8ab-0de1-4fe3-a997-e0470efe15d6}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={3d82b67f-ed31-46ae-aa73-752050e5b296}" id="{d3606ba0-630c-4e55-8be8-8ba81c5a2aaf}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={4508b080-7cdf-41ca-90b8-fa03db8b7544}" id="{72bf7b2a-8664-4cab-b675-b46b6c871a81}" providerId="google-sheets"/>
+  <x18tc:person displayName="bismuthbloom@gmail.com" id="{1960c40d-4d5b-4aec-9f92-9e267404423f}" userId="bismuthbloom@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Aiden" id="{d091de5c-dc11-4c03-8f66-3a5ba1955e83}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={8a68bd66-5614-411f-a5a4-51e9af64d185}" id="{0155967e-b020-4e03-9674-6546c2d0820a}" providerId="google-sheets"/>
+  <x18tc:person displayName="Altoz Bass Tenor" id="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={1aa364c2-7f01-4995-b24e-a3f74b1607eb}" id="{4e184150-c905-4d4e-b00b-0eafdd1d4e38}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={71cb1f5f-bab7-4f22-9d94-7a0e119fa63f}" id="{d8b9a010-134b-42ec-9cef-cc7814969225}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -5151,10 +5157,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-06T17:13:37.00" personId="{246dcbe0-778a-43e4-b72d-0d0312407132}" id="{df83af1c-437c-4c47-b3dc-5002fff775bd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-06T17:13:37.00" personId="{7953a82e-e467-4643-b007-a362f669553d}" id="{9c28bb68-a2e4-4b24-9d52-193c5ad50568}" done="0">
     <x18tc:text xml:space="preserve">Sam uses she/her pronouns now, change your translations if needed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{b2c8d6ce-ed5d-4bfe-a786-3e1a9e9b6b2f}" id="{f4f19ce4-b85f-4922-8185-d088942a8235}" done="1">
+  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{393e095c-a9b4-4efd-b880-1b06d7906940}" id="{11a504f8-1d02-4656-850c-8aa1902d87df}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5167,10 +5173,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{83ef9796-bf61-4a0f-a74f-4c21d0b38e20}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{c7620f24-01d0-4306-9a18-9e570b8b62bb}" done="0">
     <x18tc:text xml:space="preserve">Two people: she/her and he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B31" dT="2026-02-10T08:20:52.00" personId="{01d5d661-c192-4d64-8a19-7116b17f11ae}" id="{b44a2d08-b98a-42d2-8d2b-7e241c6808b5}" done="0">
+  <x18tc:threadedComment ref="B31" dT="2026-02-10T08:20:52.00" personId="{0719f8ab-0de1-4fe3-a997-e0470efe15d6}" id="{5be2d6a9-9f46-4c32-81ff-1d5df8b45743}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5188,13 +5194,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B31" dT="2026-09-08T14:45:44.00" personId="{3ab0c541-064f-429b-b0a6-a8589bd53b0b}" id="{907d2dd1-4e40-45a2-bc27-55e341f64c10}" parentId="{b44a2d08-b98a-42d2-8d2b-7e241c6808b5}">
+  <x18tc:threadedComment ref="B31" dT="2026-09-08T14:45:44.00" personId="{863e4ceb-3fab-4cc6-b694-9d4d60fa0df6}" id="{0edcb1dc-1903-4a04-96f1-f7ae682c8b37}" parentId="{5be2d6a9-9f46-4c32-81ff-1d5df8b45743}">
     <x18tc:text xml:space="preserve">Marked as resolved</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B31" dT="2026-09-08T14:46:13.00" personId="{3ab0c541-064f-429b-b0a6-a8589bd53b0b}" id="{12f423e1-564f-4126-aff1-45ff0159c902}" parentId="{b44a2d08-b98a-42d2-8d2b-7e241c6808b5}">
+  <x18tc:threadedComment ref="B31" dT="2026-09-08T14:46:13.00" personId="{863e4ceb-3fab-4cc6-b694-9d4d60fa0df6}" id="{3698ea6d-a4c8-412b-881b-55b4875e25f1}" parentId="{5be2d6a9-9f46-4c32-81ff-1d5df8b45743}">
     <x18tc:text xml:space="preserve">Re-opened</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{53e833d9-b9d0-4887-b728-01a42f8a339f}" id="{a4247db8-e7d0-4d9c-8de7-35179e7d017b}" done="1">
+  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{463e3740-b99a-4848-abc8-3cfd28b0b271}" id="{e71aa858-6cae-470b-b846-d9c023e5f56e}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5209,13 +5215,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:09:48.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{eac85b5c-76d5-444e-ae58-467ff4302e20}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:09:48.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{18ea824d-a593-4f70-b2e8-e2ff375afd0a}" done="0">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{8a4f013e-762c-45ee-a50b-baca35debd3f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{8aba2c84-630d-47ec-a4c2-c7f99bb28e3a}" done="0">
     <x18tc:text xml:space="preserve">English</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-02-10T08:20:52.00" personId="{52310717-a935-40d2-8377-647ec71bc542}" id="{29106ef4-2c1b-402c-8b82-02a3250baa12}" done="0">
+  <x18tc:threadedComment ref="F18" dT="2026-02-10T08:20:52.00" personId="{72bf7b2a-8664-4cab-b675-b46b6c871a81}" id="{236c5b68-fd4d-4825-afc8-57d3cc7d5740}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5234,7 +5240,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{05738eee-845b-436b-9526-3b14bc25132d}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{1456e244-18d2-463f-bb1b-be677acd7065}" done="0">
     <x18tc:text xml:space="preserve">Check out https://motherencore.com to see in context.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5243,25 +5249,25 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{e24c064d-e97b-4ad8-80e0-da51fbda7c83}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{a0fa8e44-cb60-4c4a-bea8-24962bde096b}" done="0">
     <x18tc:text xml:space="preserve">No change needed here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{967357b8-a868-4acd-b746-3fb2afa7b64d}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{236e0b35-3aa9-480f-b355-c657c883b392}" done="0">
     <x18tc:text xml:space="preserve">Three people: she/her and he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{86d7ffc6-327d-48ed-948b-48599ca2b8ef}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{254b1eef-136b-4996-bdcd-505897ade49b}" done="0">
     <x18tc:text xml:space="preserve">Українська</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{cf8cf740-314d-4ab7-a7a7-83dbdd78b9d0}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{4e8d7dc9-ecb5-44f4-bc6e-8a338b32de5e}" done="0">
     <x18tc:text xml:space="preserve">English</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E79" dT="2026-09-13T07:53:46.00" personId="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" id="{6a15dc04-d87d-4aa5-8d27-163cd998422c}" done="0">
+  <x18tc:threadedComment ref="E79" dT="2026-09-13T07:53:46.00" personId="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" id="{89110fac-62ec-4e82-966d-4f8f167f7b30}" done="0">
     <x18tc:text xml:space="preserve">援のお気持ちありがとうございます！この作品はあくまでファンゲームですので、お金は一切受け取りません。サポートしていただきたい場合はファンゲームを広めるか、作品の開発陣の個別のプロジェクトに支援できます。また、クレジットページにて開発陣のSNSへのリンクがございますので、そちらからフォローしてみることもできます。</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{29c2b519-44e3-45e1-94a4-c99a4877615d}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{121fc451-ea23-48d8-a9ea-7e69f55a7e7a}" done="0">
     <x18tc:text xml:space="preserve">2/3 people (he/him).</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L27" dT="2026-02-10T08:20:52.00" personId="{4749739d-aeed-4068-b876-49049b7ad38e}" id="{c9e44899-5ade-4cb8-bf3e-44d35ec7627f}" done="0">
+  <x18tc:threadedComment ref="L27" dT="2026-02-10T08:20:52.00" personId="{3d83710b-27d9-4891-8de2-8241e0d433e9}" id="{8a0d1b13-5dbb-4d92-afb0-99b90d47d197}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5273,10 +5279,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E15" dT="2026-09-13T07:38:34.00" personId="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" id="{755b8beb-612d-4ff1-a315-2a95dc38f0e3}" done="0">
+  <x18tc:threadedComment ref="E15" dT="2026-09-13T07:38:34.00" personId="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" id="{d544cc66-83c1-496b-bf7a-688bf603216e}" done="0">
     <x18tc:text xml:space="preserve">Proofreading needed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L42" dT="2026-02-10T08:20:52.00" personId="{a6aa3007-2310-46af-83db-ecaf2f45afe8}" id="{8f88c2df-e98b-4a17-8f32-fcab67910b3f}" done="1">
+  <x18tc:threadedComment ref="L42" dT="2026-02-10T08:20:52.00" personId="{4e184150-c905-4d4e-b00b-0eafdd1d4e38}" id="{20078d2e-a9a8-4d56-a40d-85ef10cac6b0}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5288,7 +5294,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L44" dT="2026-02-10T08:20:52.00" personId="{acfa75f9-e96f-4a9d-b110-d76db84ecc81}" id="{edbf5c5e-7092-46a1-a74d-18ceaf61a177}" done="1">
+  <x18tc:threadedComment ref="L44" dT="2026-02-10T08:20:52.00" personId="{8cb374ec-11d9-41c5-a2b1-6d0a7a82415a}" id="{f3c03ad7-edd7-4846-84f3-c8487513eb97}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5300,13 +5306,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{d21f074b-3c98-4907-8310-5baed7847c15}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{bea03f73-a1b1-4fb5-82ba-eddbb18e505c}" done="0">
     <x18tc:text xml:space="preserve">Español</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{69751bdb-90af-4dd3-9447-76aabe4f13fe}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{5d8cdf9f-1a22-437e-bc81-2e788ba130d1}" done="0">
     <x18tc:text xml:space="preserve">No change needed here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a36c2a8d-b724-4d89-871a-baf15cfce510}" id="{199ad6dd-3501-4fd3-84c5-1cd4aceb521d}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{dc0bc8fa-6629-4d8b-a9a4-ed9e49205ce6}" id="{353c4bf7-de6a-4eb1-bf43-f3cffa95358a}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5318,13 +5324,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E90" dT="2026-06-04T09:40:30.00" personId="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" id="{a596ce0a-ff1e-47d2-9a3b-08b5947f9ea2}" done="0">
+  <x18tc:threadedComment ref="E90" dT="2026-06-04T09:40:30.00" personId="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" id="{440f0d14-77f9-4041-b2f1-01c4471c73ce}" done="0">
     <x18tc:text xml:space="preserve">変更する</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{095d24a0-ceb8-40a2-9b80-ccbad5dd97ce}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{3bbd5712-2c2f-4bca-a50c-e3061f71ba6d}" done="0">
     <x18tc:text xml:space="preserve">Three people (including proofreader), all go by he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L31" dT="2026-02-10T08:20:52.00" personId="{114be160-6969-4eb2-a033-1d8f8cdf42ba}" id="{d73f8d07-3c7d-4f88-96cf-887c12d092aa}" done="0">
+  <x18tc:threadedComment ref="L31" dT="2026-02-10T08:20:52.00" personId="{d8b9a010-134b-42ec-9cef-cc7814969225}" id="{2e1627aa-5dd4-4350-b5d8-14cef989b766}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5336,16 +5342,16 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{3680fb3c-fe26-49c3-80a8-b3695cf43903}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{b331d5b7-57c4-4420-b677-4f4564dff3b7}" done="0">
     <x18tc:text xml:space="preserve">Two people (he/him).</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:51.00" personId="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" id="{42d69537-7ca1-4d8f-aaa8-8a19ae5c9f35}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:51.00" personId="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" id="{d83a8ff2-a011-4457-bf3b-ed78fa652031}" done="0">
     <x18tc:text xml:space="preserve">ACT1完成とともに変更</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{96e68654-dd48-436d-ba2f-d6222a7ba18b}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{7291c08e-d08c-4d42-ade7-5ca3b4084159}" done="0">
     <x18tc:text xml:space="preserve">Three people: she/her and he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{34e09fae-62a4-4d13-9da1-f5bb61d2bcf2}" id="{09f4e7cb-2300-43c7-a8d6-346ffdf051bd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{d3606ba0-630c-4e55-8be8-8ba81c5a2aaf}" id="{917ccef4-6e37-40bc-88e7-47651279c387}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5357,7 +5363,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F63" dT="2026-02-10T08:20:52.00" personId="{47cee458-8efd-41a9-a03c-c342bb360b7f}" id="{d9d26a02-38d9-441d-b20a-4090730d88cb}" done="1">
+  <x18tc:threadedComment ref="F63" dT="2026-02-10T08:20:52.00" personId="{03f80cf0-65a9-4dd5-9d10-12f603c66674}" id="{25570a33-6c76-4892-9fd6-8211a690375f}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5374,7 +5380,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{21c183e5-9d7b-46bd-85b8-31dfe0e576e6}" id="{2e7d5d43-0ec6-4d7f-86fe-6cbc007747a8}" done="1">
+  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{b09a6581-30bf-468e-8cdf-e9f4ced06365}" id="{8a7d8e93-78d6-4daf-a2f0-26b4c94260b1}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5386,7 +5392,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{d10fe3df-7870-406e-9e16-703c12e7db6a}" id="{8b817bb4-1df5-442b-a60a-4c44ed154b8c}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{82213706-1931-455f-9aa7-94154deca2ec}" id="{25d17016-b1d4-4325-ad64-69767647bf65}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5398,25 +5404,25 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:15.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{64819f4e-5863-4034-9ca2-0e3b32f5fac9}" parentId="{8b817bb4-1df5-442b-a60a-4c44ed154b8c}">
+  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:15.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{abcbf674-59cb-48b9-9fd3-fbc061dc8a29}" parentId="{25d17016-b1d4-4325-ad64-69767647bf65}">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-05T15:51:09.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{125657d9-ef8a-410f-b01e-d20c93c8d8cd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-05T15:51:09.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{eab2f0e9-cd66-4950-aa65-8276ce51db6d}" done="0">
     <x18tc:text xml:space="preserve">Just duplicating the Spanish column so it doesn't end up empty</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{2c4cd90c-8622-477c-81aa-77a8be70c8a7}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{c3af2e15-5fe9-480a-ba6c-a652344cc8ca}" done="0">
     <x18tc:text xml:space="preserve">Please mind the final whitespace</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{7db8b465-aa0b-4f8d-9278-c6fee85dcb7b}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{9ece4987-cc9b-4a49-9713-10571468e24a}" done="0">
     <x18tc:text xml:space="preserve">Two people (he/him)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{cf0543ab-85a0-49c0-ab0a-df310df21b4c}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{eccc4054-00f5-4edd-a1cb-3ffc308ac98c}" done="0">
     <x18tc:text xml:space="preserve">Backslash added to prevent the “#” symbol from being interpreted as a title tag.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{09ff2aa2-9cbc-4690-84b0-7ed3e4bc8efc}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{83f4dd8a-e29f-4f48-9948-d5308573dbbe}" done="0">
     <x18tc:text xml:space="preserve">Backslash added to prevent the “#” symbol from being interpreted as a title tag.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{796dbae4-16a5-41f7-91db-495707a85ef4}" id="{50b60560-22ab-416d-b3f2-d897752b43c6}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{15813a55-54b5-411f-9ac9-feffd08ad44d}" id="{1d7763f1-c79a-4619-ab6c-2b75c19f9500}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5426,7 +5432,7 @@
 Reply:
 	Yeah I'm going to remove it with this push.</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{d80c5444-42e7-48f2-b20f-ea5b137230c2}" mentionId="{66faa8d8-6244-43d6-92c2-749477803113}" startIndex="376" length="23"/>
+      <x18tc:mention mentionpersonId="{1960c40d-4d5b-4aec-9f92-9e267404423f}" mentionId="{72d241cd-cbfb-4648-a747-597f8ae637f8}" startIndex="376" length="23"/>
     </x18tc:mentions>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5435,32 +5441,32 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:34.00" personId="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" id="{2bf4c17b-f636-4e52-99ed-422d794d9d70}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:34.00" personId="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" id="{892fe179-c59d-4e84-8ca6-84aa7fa357b7}" done="0">
     <x18tc:text xml:space="preserve">ACT２完成とともにリリース</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{7b01e9a2-7798-4406-a713-3eaf32d9ca32}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{3ce6be39-397f-4f2d-a369-bc01e5c80a5f}" done="0">
     <x18tc:text xml:space="preserve">From here, roles have to be singular and gender-neutral.
 If “programmer” can’t be gender-neutral in your language, you can go with “programming” (see next column) instead, and so on.
 Once a cell is done, you can remove the bold style.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{6bfc90e7-a529-4297-abff-3086791bc4f5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{bfdbb542-6cc5-4260-b49f-51887d2cee3e}" done="0">
     <x18tc:text xml:space="preserve">Italiano</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{734320e5-3e20-4768-83aa-53fd6d00a2b2}" id="{38c1c8fd-c36c-48cf-b4ee-f5324bb8f334}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{cfe4d3c8-9ff0-4254-9df9-7b9777a6b7ce}" id="{b297ef8d-a32b-4451-a313-0cc9da6a9145}" done="0">
     <x18tc:text xml:space="preserve">“It [Act 1] is entirely playable in (your language)!”
 But I think the English line can remain empty as it’s kinda expected for the game to be playable in English anyway.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L40" dT="2026-08-27T09:41:22.00" personId="{4fb1da2c-5e0c-4f84-b793-b51b84947830}" id="{76203e11-78e5-46ee-a3de-ece22de2f387}" done="0">
+  <x18tc:threadedComment ref="L40" dT="2026-08-27T09:41:22.00" personId="{d091de5c-dc11-4c03-8f66-3a5ba1955e83}" id="{984b5d1e-3126-4bcc-9ac4-927c104950a0}" done="0">
     <x18tc:text xml:space="preserve">eh</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-25T03:41:20.00" personId="{4e11369d-42ba-45a1-a47a-c31b13620b63}" id="{f955ea67-5e95-4d09-a683-327fb746a452}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-25T03:41:20.00" personId="{574b93ef-cc8d-4e7c-962a-78f24313b660}" id="{37e7f729-3b24-4fb8-b2ef-a18713fe5f35}" done="0">
     <x18tc:text xml:space="preserve">실제 웹사이트에 따라 수정 필요
 Modify according to the website</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{7aa346ad-20a2-4416-b296-90cf15d25294}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{62fd50b0-ab69-49b6-ae5e-f8a7c33a70be}" done="0">
     <x18tc:text xml:space="preserve">Polski</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F1" dT="2026-02-10T08:20:52.00" personId="{772c79a3-2dae-4bca-aac7-1c4bb53246a2}" id="{d2f66c33-55cf-4e66-a5b0-a7dbf881243e}" done="0">
+  <x18tc:threadedComment ref="F1" dT="2026-02-10T08:20:52.00" personId="{50dc71f3-9ebb-4197-9935-5ef91e119911}" id="{a3d6418e-f8eb-451c-9129-fca03642d421}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5473,10 +5479,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{d6dcc41f-46c5-4ac0-aa26-ad223ac45671}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{2d94f0be-9556-4d69-8654-3da20ae15feb}" done="0">
     <x18tc:text xml:space="preserve">This one doesn’t need to be changed, as it already applied to one single person.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L49" dT="2026-02-10T08:20:52.00" personId="{1d1bb5d7-5d98-4532-87ed-e34446609da0}" id="{e9025376-bdba-4586-bb3b-994d27c65656}" done="0">
+  <x18tc:threadedComment ref="L49" dT="2026-02-10T08:20:52.00" personId="{5926c0a2-f205-44d3-ab48-a1a9d9b27bad}" id="{3248f61d-8890-4427-a1de-f6ba24530e60}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5488,13 +5494,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F63" dT="2026-08-25T03:59:16.00" personId="{4e11369d-42ba-45a1-a47a-c31b13620b63}" id="{4c882b70-bfa0-4514-ace2-818ad374f3d6}" done="0">
+  <x18tc:threadedComment ref="F63" dT="2026-08-25T03:59:16.00" personId="{574b93ef-cc8d-4e7c-962a-78f24313b660}" id="{ecdd1fb5-13d4-4e8a-805c-a561e6f1e405}" done="0">
     <x18tc:text xml:space="preserve">![몰?루](/Assets/Funny/idk_ko.jpeg)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:06:31.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{b5181456-eb16-4a9a-9b70-10412a4ec734}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:06:31.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{5aca1fcb-eb14-495c-bd9c-4ff8d7064ebc}" done="0">
     <x18tc:text xml:space="preserve">These links are deprecated.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{79188f1b-0105-4ab4-aeb0-86a488fff33a}" id="{36afca42-4a2e-47de-a6a3-b38f509e683a}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{433f50a8-b52f-4fdc-b0a0-9cb56881224f}" id="{575d1362-2d9a-48c3-aa2d-8a2734231c0c}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5506,16 +5512,16 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{dd040edc-d412-4a96-8a30-abb5cd966182}" id="{230eda97-7c65-4055-9fc3-d4a89c3ee95a}" done="1">
+  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{c59b55aa-5ec8-434d-8510-c76cc13d10e6}" id="{af621491-136a-4f72-adbd-fe110fd44bdd}" done="1">
     <x18tc:text xml:space="preserve">![alt_text](image_url)
 You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
 You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
 Click the link on the left to access the Drive folder where to upload your translated image.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E9" dT="2026-09-13T07:33:28.00" personId="{ac1e4bb6-7d1b-4b08-9e64-3cafd2097b5f}" id="{5af38ea6-f33c-4526-99d9-52bf00ad222e}" done="0">
+  <x18tc:threadedComment ref="E9" dT="2026-09-13T07:33:28.00" personId="{d6014d82-3a4d-4b89-bd39-b3bff84ad775}" id="{189bca0b-5553-4f62-87a6-f17ee63347dc}" done="0">
     <x18tc:text xml:space="preserve">Made the MOTHER Shop link into the JP version</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{8fab866b-6aa9-45e6-860d-f11a7c4bffda}" id="{98185a0c-9d22-46c1-82b3-154fed723813}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{f9d1c842-95e0-483e-88dd-f76a75a427c9}" id="{2df1de04-3c3b-4de0-9a16-3fde31f67766}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5527,7 +5533,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="K1" dT="2026-02-10T08:20:52.00" personId="{70ec7af7-55ed-4fb9-b7ec-1fcfe9c10dfa}" id="{c9acedbd-d5e3-4b5a-bbc8-4eca725f3262}" done="1">
+  <x18tc:threadedComment ref="K1" dT="2026-02-10T08:20:52.00" personId="{274e15c0-a8c4-4c15-a44e-7125c0e875ff}" id="{3f9c57a0-b429-4192-bc01-fbaedcda9e99}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5539,31 +5545,31 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A89" dT="2026-08-03T23:18:53.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{62915ae0-5617-4430-8fe4-90455a4dbd95}" done="1">
+  <x18tc:threadedComment ref="A89" dT="2026-08-03T23:18:53.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{998ab636-60a7-4401-902e-a291407bcf13}" done="1">
     <x18tc:text xml:space="preserve">Include Japanese and Chinese.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{0c6b2add-4a3f-46f9-9082-89f09b601231}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{4f6acda5-f4c8-4c8e-8424-05ffa41f0f14}" done="0">
     <x18tc:text xml:space="preserve">한국어</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:15:01.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{3ea7c14b-455f-4549-b0a5-47ab339941ae}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:15:01.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{0642b6e7-f3b4-4604-aa06-56b1f9daecfb}" done="0">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{8ee779ae-b960-4a62-8ac5-a04f1a8b9d2f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{18fab238-33ec-457f-8457-ff954a98761d}" done="0">
     <x18tc:text xml:space="preserve">This is Markdown syntax for links, please keep the parentheses and brackets like they are in English.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:25.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{ed25c706-4b16-4d7e-881a-33f63d79cf08}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:25.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{5cd33e73-04ea-4baf-853e-77ff8d79a722}" done="0">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{5e19d234-12e3-4dd8-b7ba-ff492b5ef407}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{9c9d9a41-5851-45e0-8f33-bd040e592c6a}" done="0">
     <x18tc:text xml:space="preserve">Deutsch</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{261798a4-c59a-433e-9b7d-d47dbbaf965c}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{27a859a3-133f-48a0-95e3-14a4f878885b}" done="0">
     <x18tc:text xml:space="preserve">Same here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{c1e2f56d-3583-4ea5-9c4c-a4a2ade66c29}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{6be8c85c-f7a4-4f76-826d-b4c9272fdd2c}" done="0">
     <x18tc:text xml:space="preserve">Français</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1b00e706-acda-430a-aac4-4c408fcec4dc}" id="{183e35ff-3766-4a1c-8e82-a2736913f9b5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{2356a069-2a83-45e0-9157-9e96de2f329f}" id="{83617bd9-9e41-4dcb-adba-5c3a3743d318}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5575,10 +5581,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{e6dc5e0c-4dc9-4eab-98e6-f2169bdcc938}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{71eb0a58-1c32-4dd6-ab7a-1a14cbfd0e5a}" done="0">
     <x18tc:text xml:space="preserve">Português brasileiro</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{6faab978-2b20-44f0-b3d7-67a87749564d}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{12fd690a-c630-4174-a521-0db06cdf17ff}" done="0">
     <x18tc:text xml:space="preserve">Check out https://motherencore.com to see in context.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5587,7 +5593,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{21c183e5-9d7b-46bd-85b8-31dfe0e576e6}" id="{871c753d-3906-4b87-8593-d6ce8678ac7b}" done="1">
+  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{b09a6581-30bf-468e-8cdf-e9f4ced06365}" id="{afd2880a-2090-429f-b0d9-61a2c81ed722}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5599,13 +5605,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{dd040edc-d412-4a96-8a30-abb5cd966182}" id="{a378985e-9c03-4601-ae76-36673e5af1a6}" done="1">
+  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{c59b55aa-5ec8-434d-8510-c76cc13d10e6}" id="{319bd969-2d9a-4246-9ee2-831de2a5d16b}" done="1">
     <x18tc:text xml:space="preserve">![alt_text](image_url)
 You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
 You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
 Click the link on the left to access the Drive folder where to upload your translated image.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{b55da5f3-9ea4-40c9-997d-22498a32c5f9}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{7715205c-5f0b-4c02-8e90-2c54d99ed6f1}" done="0">
     <x18tc:text xml:space="preserve">Check out https://motherencore.com to see in context.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5614,27 +5620,27 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{506a9c41-f51f-4a83-ba14-95461c824ef7}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{a4cf48b0-228d-4124-9b4e-6d82e2156821}" done="0">
     <x18tc:text xml:space="preserve">No change needed here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{1d01c816-c748-4232-82e8-358d5e8d6db9}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{199a0ac3-5bd7-4f80-88ea-131eb216fae1}" done="0">
     <x18tc:text xml:space="preserve">にほんご</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B15" dT="2026-09-05T15:09:22.00" personId="{d151c2a0-df19-4a14-9347-cc048611ea99}" id="{4d5b8d4e-e7de-44a3-aaf1-0a8cf576240c}" done="0">
+  <x18tc:threadedComment ref="B15" dT="2026-09-05T15:09:22.00" personId="{4fba8901-5e79-4213-a246-9289d576f53a}" id="{eb868fd7-39ca-44a9-b83d-59638c6ad1d1}" done="0">
     <x18tc:text xml:space="preserve">Edited "wanting for" to "cheering for"</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{b3aebbf4-9cd8-4732-8b0f-3a0b799ab7a6}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{a074977c-c51f-4720-94bf-d48bfd618fd5}" done="0">
     <x18tc:text xml:space="preserve">Two people, he/him and any pronouns.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F10" dT="2026-08-25T03:31:34.00" personId="{4e11369d-42ba-45a1-a47a-c31b13620b63}" id="{e0abb297-1b92-4aeb-8bc0-07df461c455c}" done="1">
+  <x18tc:threadedComment ref="F10" dT="2026-08-25T03:31:34.00" personId="{574b93ef-cc8d-4e7c-962a-78f24313b660}" id="{45c21352-2444-4244-9597-8284cfa31c96}" done="1">
     <x18tc:text xml:space="preserve">실제 웹사이트에 따라 수정 필요
 Modify according to the website</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T17:36:36.00" personId="{081c3182-7f7d-4c7d-9072-66bbf8a722f2}" id="{48d7ce8e-73ad-4915-9dff-cf228eb517ba}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T17:36:36.00" personId="{9f8c30ab-a5f6-402c-ba9d-6991d1f07623}" id="{1e5296b9-dbad-4083-987f-65e1e5240ad0}" done="0">
     <x18tc:text xml:space="preserve">All features are separated into a entry; it's less work than refactoring the spreedsheet 
 parser.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L57" dT="2026-02-10T08:20:52.00" personId="{94fc03d0-6a11-431d-83f8-0b421a1a61b3}" id="{c3f809d7-68d8-4dd1-af6f-17af5a1aa17f}" done="0">
+  <x18tc:threadedComment ref="L57" dT="2026-02-10T08:20:52.00" personId="{0155967e-b020-4e03-9674-6546c2d0820a}" id="{12342dae-419d-4c23-b25b-7edd29130b23}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5646,7 +5652,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{d3d454b3-be32-4bb5-9ee5-0d02d4739b1d}" id="{461e9a4d-8388-412a-aae8-f04ea0a44482}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{99440684-8175-4bcb-a12a-bdecccba751e}" id="{dc919a31-9e8b-4ef5-8b77-e2eee98a5cef}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5658,7 +5664,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0957b3d5-da65-4fb4-9342-aaefff864fa9}" id="{ff812722-9c4d-458a-a22d-735ec621f0dd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1d70bf60-d360-46a1-9ed3-7895ce828cbd}" id="{d59698be-4169-43c4-83c0-f66df470a3a7}" done="0">
     <x18tc:text xml:space="preserve">Русский</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -7637,19 +7643,21 @@
       <c r="G35" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="H35" s="6"/>
+      <c r="H35" s="7" t="s">
+        <v>392</v>
+      </c>
       <c r="I35" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L35" s="7"/>
       <c r="M35" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
@@ -7670,37 +7678,39 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="H36" s="6"/>
+        <v>403</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>404</v>
+      </c>
       <c r="I36" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
@@ -7721,39 +7731,39 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="27" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
@@ -7774,37 +7784,37 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="27" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
@@ -7825,41 +7835,41 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
@@ -7880,41 +7890,41 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
@@ -7935,43 +7945,43 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="6"/>
@@ -7992,43 +8002,43 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="6"/>
@@ -8049,41 +8059,41 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H43" s="30"/>
       <c r="I43" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="J43" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>476</v>
-      </c>
       <c r="K43" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="6"/>
@@ -8104,43 +8114,43 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H44" s="30" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="6"/>
@@ -8161,43 +8171,43 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="6"/>
@@ -8218,39 +8228,39 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="32" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
@@ -8271,16 +8281,16 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="33" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B47" s="22" t="s">
         <v>48</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>48</v>
@@ -8295,16 +8305,16 @@
         <v>50</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>51</v>
@@ -8328,43 +8338,43 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="34" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="6"/>
@@ -8385,43 +8395,43 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="33" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="6"/>
@@ -8442,43 +8452,43 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="28" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="6"/>
@@ -8499,43 +8509,43 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="28" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="6"/>
@@ -8556,43 +8566,43 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="28" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="6"/>
@@ -8613,43 +8623,43 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="6"/>
@@ -8670,43 +8680,43 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="28" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="6"/>
@@ -8727,43 +8737,43 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="6"/>
@@ -8784,43 +8794,43 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="34" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="6"/>
@@ -8841,43 +8851,43 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="28" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="6"/>
@@ -8898,43 +8908,43 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="34" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="6"/>
@@ -8955,43 +8965,43 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="28" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="6"/>
@@ -9012,43 +9022,43 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="28" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="6"/>
@@ -9069,43 +9079,43 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="6"/>
@@ -9126,43 +9136,43 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="28" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="6"/>
@@ -9183,37 +9193,37 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="28" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="4" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="6"/>
@@ -9234,43 +9244,43 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="34" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="6"/>
@@ -9291,43 +9301,43 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="28" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="L65" s="38" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" s="6"/>
@@ -9348,43 +9358,43 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="6"/>
@@ -9405,43 +9415,43 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="28" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="6"/>
@@ -9462,43 +9472,43 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="28" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="6"/>
@@ -9519,43 +9529,43 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="28" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="6"/>
@@ -9576,43 +9586,43 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="28" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="6"/>
@@ -9633,43 +9643,43 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="28" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="6"/>
@@ -9690,41 +9700,41 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="28" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="6"/>
@@ -9745,41 +9755,41 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="28" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="N73" s="3"/>
       <c r="O73" s="6"/>
@@ -9800,41 +9810,41 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="28" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="4" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="6"/>
@@ -9855,41 +9865,41 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="28" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="6"/>
@@ -9910,41 +9920,41 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="28" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="6"/>
@@ -9965,37 +9975,37 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="28" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="4" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="6"/>
@@ -10016,41 +10026,41 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="28" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="4" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="6"/>
@@ -10071,37 +10081,37 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="28" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="4" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="4" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="N79" s="3"/>
       <c r="O79" s="6"/>
@@ -10122,43 +10132,43 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="M80" s="4" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="N80" s="3"/>
       <c r="O80" s="6"/>
@@ -10179,43 +10189,43 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="18" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B81" s="39" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C81" s="40" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="G81" s="40" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="I81" s="40" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="J81" s="40" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="L81" s="40" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="N81" s="19"/>
       <c r="O81" s="20"/>
@@ -10236,43 +10246,43 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="N82" s="3"/>
       <c r="O82" s="6"/>
@@ -10293,43 +10303,43 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="N83" s="3"/>
       <c r="O83" s="6"/>
@@ -10350,43 +10360,43 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="6"/>
@@ -10407,43 +10417,43 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="H85" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="I85" s="4" t="s">
-        <v>985</v>
-      </c>
       <c r="J85" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="6"/>
@@ -10464,43 +10474,43 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="N86" s="3"/>
       <c r="O86" s="6"/>
@@ -10521,43 +10531,43 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="I87" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>1003</v>
-      </c>
       <c r="K87" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="N87" s="3"/>
       <c r="O87" s="6"/>
@@ -10578,43 +10588,43 @@
     </row>
     <row r="88" ht="46.5" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="M88" s="7" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="6"/>
@@ -10635,43 +10645,43 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="7" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="N89" s="6"/>
       <c r="O89" s="6"/>
@@ -10692,43 +10702,43 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E90" s="41" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="I90" s="42" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="N90" s="3"/>
       <c r="O90" s="6"/>
@@ -10749,41 +10759,41 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="N91" s="3"/>
       <c r="O91" s="6"/>
@@ -10804,41 +10814,41 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D92" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E92" s="4" t="s">
         <v>1061</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>1059</v>
-      </c>
       <c r="F92" s="4" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="L92" s="19" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="6"/>
@@ -10859,41 +10869,41 @@
     </row>
     <row r="93" ht="21.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="H93" s="6"/>
       <c r="I93" s="7" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="6"/>
@@ -10914,41 +10924,41 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="H94" s="6"/>
       <c r="I94" s="7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="M94" s="7" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" s="6"/>
@@ -10969,41 +10979,41 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="H95" s="6"/>
       <c r="I95" s="7" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="K95" s="43" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="L95" s="44" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="M95" s="7" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="N95" s="6"/>
       <c r="O95" s="6"/>
@@ -11024,39 +11034,39 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B96" s="45" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="J96" s="46" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="K96" s="43" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="L96" s="47"/>
       <c r="M96" s="7" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="N96" s="6"/>
       <c r="O96" s="6"/>

--- a/src/assets/xlsx/translations.xlsx
+++ b/src/assets/xlsx/translations.xlsx
@@ -14,120 +14,180 @@
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author/>
-    <author>tc={006fb328-f499-4c5a-8b55-a45eb780c4b5}</author>
-    <author>tc={02a41813-fe8d-4270-85fe-a31766c005b4}</author>
-    <author>tc={03418033-4484-44d8-881b-854f15bad89c}</author>
-    <author>tc={0a80988b-e1c9-4bfd-93f8-77dea106e34e}</author>
-    <author>tc={0ca07eab-e45e-42dc-a160-471b15eefb20}</author>
-    <author>tc={0ca644c9-5f17-47ea-a23d-21985ecffa68}</author>
-    <author>tc={0cc7855e-8347-46c8-a1c7-b37e54b0ff01}</author>
-    <author>tc={10d976d3-1153-4867-9b29-a382d87ca2cb}</author>
-    <author>tc={1c4dcbf0-f957-46df-9413-03242f773820}</author>
-    <author>tc={1fbddf5e-9f96-4242-857e-ebecbe218fb9}</author>
-    <author>tc={2719fd2e-6b88-496c-b1ef-29278cf376a7}</author>
-    <author>tc={2c8ed81e-3326-46d4-b763-943e0288fec1}</author>
-    <author>tc={2dbf9a50-de08-448c-921b-f137ceed0ef8}</author>
-    <author>tc={2eb5ab60-dea9-47f8-a8cf-5b93f9d20387}</author>
-    <author>tc={2ebfcb01-b5c6-4e78-8581-4a738e15b523}</author>
-    <author>tc={2f0f22cf-97c8-47da-a936-64bdec5060f6}</author>
-    <author>tc={44ac9be2-6ede-4234-ac17-610e2fa15780}</author>
-    <author>tc={466db0da-0d16-4782-a9ac-f094e280a786}</author>
-    <author>tc={49fa7608-6575-4d10-ab6c-bc0b07063997}</author>
-    <author>tc={4a04c7e6-cd58-4325-adea-4f22053dd934}</author>
-    <author>tc={5a0e6982-35be-44c6-8825-26bb1a3ec5bd}</author>
-    <author>tc={5d67f01f-c50a-4e04-bf45-5f091fa46ced}</author>
-    <author>tc={5e5523d5-467b-42af-a815-d9b53d23486c}</author>
-    <author>tc={601a6e95-2f83-4477-8b6f-1870183f5af0}</author>
-    <author>tc={6026a4bf-051f-44fc-9ff3-86fe3c1a22a8}</author>
-    <author>tc={60b00f4f-63c8-4fac-b601-d3c53ceb3b92}</author>
-    <author>tc={632b1594-4ad3-4cdc-9e94-4280e5e53b60}</author>
-    <author>tc={66410900-defc-4d4d-89f5-75a5ff151486}</author>
-    <author>tc={66ae36f1-65a0-4bc9-9368-c2caca3af5b4}</author>
-    <author>tc={67bfeef1-3e42-4dfa-a26e-9a8a7997a2ef}</author>
-    <author>tc={69c1a2fd-9026-45d3-b0bf-6afedc3ba7a5}</author>
-    <author>tc={6e29eddb-b7cc-443c-8c9e-ba07f26f5cdc}</author>
-    <author>tc={70133ada-1140-4c5c-83db-d89cd490898c}</author>
-    <author>tc={73703df5-6697-469a-a3cd-6d6416f03238}</author>
-    <author>tc={75baa87e-0daf-4d88-be4a-dcc29fc9a2ab}</author>
-    <author>tc={76eecd81-f24b-4a32-8963-ed29c9e3b549}</author>
-    <author>tc={785f2a4f-7399-418a-bdd9-9befb54191c2}</author>
-    <author>tc={7b7af789-9505-4c1c-a5e4-825bd9910483}</author>
-    <author>tc={7f177953-b238-4b0b-9363-9fbb46f886bb}</author>
-    <author>tc={8450f601-2d3c-4553-8d1b-d710abf2fb0f}</author>
-    <author>tc={8acc1d50-ea1b-4c59-87ea-3f7826b246ea}</author>
-    <author>tc={8d7f6841-003a-4409-bc84-98e5cbf6100b}</author>
-    <author>tc={8ec13475-da80-4712-9a9c-5418b01dc331}</author>
-    <author>tc={930be254-c1d2-4647-a663-ecaaff3e0aca}</author>
-    <author>tc={98c96c55-4692-42c1-8dc6-3353f3265043}</author>
-    <author>tc={9a67667e-f06a-4902-af6c-a038d80afdbd}</author>
-    <author>tc={9b38449f-5d3e-4988-8c85-bd98804aac29}</author>
-    <author>tc={9b6068bd-d3e3-490a-a3cc-f773d9b2dad5}</author>
-    <author>tc={9c461af3-0a76-4357-8709-44b79b0dd4a9}</author>
-    <author>tc={9c5b6606-6460-4394-a91c-6d92e36d87d6}</author>
-    <author>tc={9dba93ec-e907-4d8a-8263-668e5a792279}</author>
-    <author>tc={9dbc84ce-d0f6-4532-a8dd-9b2b1de2e2ca}</author>
-    <author>tc={b182435a-8208-478a-8411-9684b207dd91}</author>
-    <author>tc={b27521d1-ca5c-4230-a2c3-6d41d93e19d3}</author>
-    <author>tc={b3f1ed36-ea7f-47f1-94db-fbe1d7153e2f}</author>
-    <author>tc={bb67c07d-98b0-47ae-8673-5e0f6167a8f1}</author>
-    <author>tc={bc0a6b64-d551-4d5d-bbea-41210426058b}</author>
-    <author>tc={bcdbf49a-381b-4392-b1bc-a226ca625149}</author>
-    <author>tc={be47be4c-b536-42ce-be6f-a13096826dfb}</author>
-    <author>tc={c3d8cbd3-d28c-45a4-a5c3-f5e2884da06f}</author>
-    <author>tc={c51b2447-e631-4a6f-bc46-b98af5974d7a}</author>
-    <author>tc={c595d7eb-6e87-4e92-96f2-66f0f375e009}</author>
-    <author>tc={c6730cf7-eb52-4e44-83ad-6fbf9f459c42}</author>
-    <author>tc={c91079ba-27dd-44e0-91e5-48daf7d2f91e}</author>
-    <author>tc={c9a8892a-bcaa-4f99-bace-d9550286d605}</author>
-    <author>tc={d3c092d0-a614-4f4d-a75b-40bf14bf0865}</author>
-    <author>tc={d61d3ac1-4646-4cfb-98eb-c55c8f1eb453}</author>
-    <author>tc={dc4ec4e0-44e0-4ab6-8f81-6a35b6f9f8cd}</author>
-    <author>tc={dc7776e0-8028-451f-befd-ca75dc360899}</author>
-    <author>tc={e84954c0-d0c5-4caa-86fb-9198be6ea767}</author>
-    <author>tc={ec6c9a8d-d58e-4251-baf7-3474f7ca6228}</author>
-    <author>tc={ed193ca0-e81b-4276-916d-e12d401ffb44}</author>
-    <author>tc={f23534da-0d71-462d-9ef0-618a7fb4d356}</author>
-    <author>tc={f2fffab0-04eb-46bd-b447-5c49d9104ad6}</author>
-    <author>tc={fa7572e6-c822-414c-a4e7-cc476aa4f7de}</author>
-    <author>tc={fc8d9e4a-0d5e-4392-9ce1-64242683d796}</author>
-    <author>tc={fde29e80-d481-473e-8561-39a94b51bf93}</author>
-    <author>tc={fe470b81-53cb-4e9a-97a0-b3fb9323c784}</author>
+    <author>tc={0d9f261e-6d73-4b8d-9c9b-a6bd7c7b4737}</author>
+    <author>tc={139e050c-c289-441c-965e-3b33d9b1a0d0}</author>
+    <author>tc={15a9cdee-2196-4249-a2f5-d6d4758cc8fa}</author>
+    <author>tc={1797d56b-7de7-4dd1-8367-190d8ed9b71a}</author>
+    <author>tc={19006183-814e-484a-b1b4-8acdff0f26fe}</author>
+    <author>tc={1e25414e-a9e3-4900-b5de-162cf0b8f885}</author>
+    <author>tc={20655de3-1bb2-455c-8194-4dad8b1da06a}</author>
+    <author>tc={236d2932-626f-4e6b-9687-e7d336e3e885}</author>
+    <author>tc={255de392-ad36-46dd-9eb7-c2782b472eea}</author>
+    <author>tc={2603192d-6d6c-4efe-a57b-92b8cf1e9c78}</author>
+    <author>tc={280a4ccf-d324-453d-8175-7c20353c80d9}</author>
+    <author>tc={2892e23c-bb9d-4f2b-9058-05da9bdcc3e7}</author>
+    <author>tc={2bb25c71-e13f-4911-9260-d88d479f3b24}</author>
+    <author>tc={2d10255f-a602-4f34-a181-cad4606ccf92}</author>
+    <author>tc={2de8525c-cbab-47ad-a067-83e489a582be}</author>
+    <author>tc={2e94e805-272c-4561-a43a-e90a60217815}</author>
+    <author>tc={31a61dd4-ea85-4917-ace5-792fd05bc5d9}</author>
+    <author>tc={333b9de2-d579-4843-9826-1bcf122d7417}</author>
+    <author>tc={33e4222c-7842-4ed2-ba68-605154f2aa08}</author>
+    <author>tc={340713ce-abac-4ccd-803f-11e857beb63a}</author>
+    <author>tc={35e6330e-d8ee-4639-bb67-86ec7c17a0a4}</author>
+    <author>tc={36de6290-1673-45d5-9ee6-9656000001ad}</author>
+    <author>tc={381259fb-7422-4b13-8188-ce4f65c7f2b7}</author>
+    <author>tc={40412b85-a802-4e60-af96-ad409284053a}</author>
+    <author>tc={40dc7763-bb48-44d2-a850-5951f004bc97}</author>
+    <author>tc={49ecf6e7-b70e-4c27-b0cf-ae57244efc76}</author>
+    <author>tc={52801b53-d9ca-477c-aece-af3ab389bd22}</author>
+    <author>tc={52ce54d3-bbf5-400b-ab48-5a4a6d4dde44}</author>
+    <author>tc={54d45a73-cb05-4b0a-b3b8-2d35fa4a331f}</author>
+    <author>tc={5b337d0e-0a52-41f8-9d60-46603971e594}</author>
+    <author>tc={5c8e2781-2c32-4f64-8f07-80b10552412c}</author>
+    <author>tc={5d8cf83c-434f-4ac0-b993-adaa8c79c8b7}</author>
+    <author>tc={5dbbe192-f116-41dc-a5ae-91d4b4346dc0}</author>
+    <author>tc={60e461a9-b36e-4f83-8cd7-1fc925a77102}</author>
+    <author>tc={64ca7417-4076-48a5-a53e-da087901bd7b}</author>
+    <author>tc={6508a3e3-0a73-48ad-a311-f2ebb36a12ca}</author>
+    <author>tc={71e487f6-fd35-4653-9694-a6e58a5549b2}</author>
+    <author>tc={73347ccf-7072-4d46-ad36-5499aff3631d}</author>
+    <author>tc={737482d5-7437-48a0-b8a9-55c05bea729f}</author>
+    <author>tc={7f6133c7-b934-499c-a6db-2dfcdf999865}</author>
+    <author>tc={7f9a66b6-733c-46fa-ab12-1223740d1b6e}</author>
+    <author>tc={8189dae4-e47f-4195-ba5f-dc7a8d2fd8c2}</author>
+    <author>tc={856cb280-38e1-4416-9ecf-e9684ae70b7a}</author>
+    <author>tc={867a849d-6e1a-473f-be87-0074e6e9a3a1}</author>
+    <author>tc={87b39ee5-fcb5-4da0-a050-3e4f483237d0}</author>
+    <author>tc={8a55ac4d-8c02-4433-905b-f199bf071b21}</author>
+    <author>tc={8c804f1a-29a1-49a2-8402-146261413779}</author>
+    <author>tc={8cf87132-ad0d-4385-aee0-03ec3d82e3be}</author>
+    <author>tc={8f81d3dd-1312-4982-94e9-d4c6b7e02f4c}</author>
+    <author>tc={90b0a8d9-0fe6-4f42-aa3a-46c4f9467fd2}</author>
+    <author>tc={90c4aceb-a2eb-40e0-be46-e57a410b76d6}</author>
+    <author>tc={92cd855f-46f7-4600-90de-bd97114414b2}</author>
+    <author>tc={966735a5-b23a-4d35-9bc9-9904e8b747df}</author>
+    <author>tc={96918f0a-ef75-4797-9e0a-64727be31579}</author>
+    <author>tc={9840b638-f7bd-406c-9169-12e158f56357}</author>
+    <author>tc={98be36ba-e647-49d9-b6af-223f898981a9}</author>
+    <author>tc={9d9b5956-d03b-4126-ac49-9562ad29826a}</author>
+    <author>tc={a0fc82db-f396-4f03-8bff-6edab3b0603f}</author>
+    <author>tc={a5c0b4a6-d856-4c1f-8f64-bbcb0caf7d29}</author>
+    <author>tc={a901c7a0-c951-49d1-9a06-2b0cf1f9cd10}</author>
+    <author>tc={ac7ccbe3-9879-47fb-b9e5-4ed7cbe8f12d}</author>
+    <author>tc={b111389d-3e4c-4c02-9507-b6efbc2c0546}</author>
+    <author>tc={b334a638-155d-468e-b357-e40af35e7207}</author>
+    <author>tc={b7d04dd8-b0b7-4970-8f90-4e181530b97d}</author>
+    <author>tc={c5c9626c-8649-43fa-a504-c15d2a351181}</author>
+    <author>tc={c60c62fb-9821-40bc-b627-491b0e423919}</author>
+    <author>tc={cb412cbf-8232-41c6-94ad-4e9f77514aa3}</author>
+    <author>tc={cc44bae2-2338-4bed-b74a-545f3822d4e2}</author>
+    <author>tc={cfa765af-cd8b-4e2e-a060-c538157f01ef}</author>
+    <author>tc={d5546657-23ac-4de1-ae1a-f2889d20a03a}</author>
+    <author>tc={dab604aa-881a-41bb-971d-82f63a072bbe}</author>
+    <author>tc={e0382cf9-d1cf-448b-84e2-8f02c6a6aacf}</author>
+    <author>tc={ef592d31-2bd9-4579-926c-58c982531371}</author>
+    <author>tc={f0688438-8bed-47fb-8dcc-e49f9634940d}</author>
+    <author>tc={f09601ed-d9f6-4a95-814a-f676a577d600}</author>
+    <author>tc={f6e65078-0f34-4582-ada2-df68221eba94}</author>
+    <author>tc={fe7323c8-8c38-45c6-8198-519fd3bf3859}</author>
+    <author>tc={ff2bc842-c0fb-4549-8b18-d16d18896b58}</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B19">
+    <comment authorId="0" ref="B20">
       <text>
         <t xml:space="preserve">This is Markdown syntax.
 Text between * displays as italics.</t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{006fb328-f499-4c5a-8b55-a45eb780c4b5}" ref="A1">
+    <comment authorId="1" xr:uid="{0d9f261e-6d73-4b8d-9c9b-a6bd7c7b4737}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Marked in gray are currently not used in version Act 2 of the site.
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Roots no longer exists, this should be changed or removed.
+Reply:
+	I suggest we remove this paragraph entirely, what do you think @bismuthbloom@gmail.com?
+Reply:
+	Yeah I'm going to remove it with this push.
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{02a41813-fe8d-4270-85fe-a31766c005b4}" ref="A1">
+    <comment authorId="2" xr:uid="{139e050c-c289-441c-965e-3b33d9b1a0d0}" ref="B64">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Check out https://motherencore.com to see in context.
+	![alt_text](image_url)
+You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
+You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
+Click the link on the left to access the Drive folder where to upload your translated image.
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{03418033-4484-44d8-881b-854f15bad89c}" ref="L40">
+    <comment authorId="3" xr:uid="{15a9cdee-2196-4249-a2f5-d6d4758cc8fa}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	eh
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	This is European Spanish (Español Castellano)
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{0a80988b-e1c9-4bfd-93f8-77dea106e34e}" ref="F18">
+    <comment authorId="4" xr:uid="{1797d56b-7de7-4dd1-8367-190d8ed9b71a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	All features are separated into a entry; it's less work than refactoring the spreedsheet 
+parser.
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{19006183-814e-484a-b1b4-8acdff0f26fe}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No change needed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="6" xr:uid="{1e25414e-a9e3-4900-b5de-162cf0b8f885}" ref="F10">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	실제 웹사이트에 따라 수정 필요
+Modify according to the website
+</t>
+      </text>
+    </comment>
+    <comment authorId="7" xr:uid="{20655de3-1bb2-455c-8194-4dad8b1da06a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Two people: she/her and he/him.
+</t>
+      </text>
+    </comment>
+    <comment authorId="8" xr:uid="{236d2932-626f-4e6b-9687-e7d336e3e885}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
+</t>
+      </text>
+    </comment>
+    <comment authorId="9" xr:uid="{255de392-ad36-46dd-9eb7-c2782b472eea}" ref="F19">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -146,43 +206,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="5" xr:uid="{0ca07eab-e45e-42dc-a160-471b15eefb20}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Українська
-</t>
-      </text>
-    </comment>
-    <comment authorId="6" xr:uid="{0ca644c9-5f17-47ea-a23d-21985ecffa68}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	This is Markdown syntax for links, please keep the parentheses and brackets like they are in English.
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{0cc7855e-8347-46c8-a1c7-b37e54b0ff01}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No change needed here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="8" xr:uid="{10d976d3-1153-4867-9b29-a382d87ca2cb}" ref="E79">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	援のお気持ちありがとうございます！この作品はあくまでファンゲームですので、お金は一切受け取りません。サポートしていただきたい場合はファンゲームを広めるか、作品の開発陣の個別のプロジェクトに支援できます。また、クレジットページにて開発陣のSNSへのリンクがございますので、そちらからフォローしてみることもできます。
-</t>
-      </text>
-    </comment>
-    <comment authorId="9" xr:uid="{1c4dcbf0-f957-46df-9413-03242f773820}" ref="A1">
+    <comment authorId="10" xr:uid="{2603192d-6d6c-4efe-a57b-92b8cf1e9c78}" ref="K1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -190,20 +214,11 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Changed "demo" to Act 1
+	Don’t include to the site update.
 </t>
       </text>
     </comment>
-    <comment authorId="10" xr:uid="{1fbddf5e-9f96-4242-857e-ebecbe218fb9}" ref="B15">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Edited "wanting for" to "cheering for"
-</t>
-      </text>
-    </comment>
-    <comment authorId="11" xr:uid="{2719fd2e-6b88-496c-b1ef-29278cf376a7}" ref="A1">
+    <comment authorId="11" xr:uid="{280a4ccf-d324-453d-8175-7c20353c80d9}" ref="J1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -211,41 +226,71 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Please make sure it flows correctly between SITE_ABOUT_DL_INTRO_3 and SITE_ABOUT_DL_INTRO_4 after replacing Demo with Act 1.
-Reply:
-	Marked in gray are currently not used in version Act 2 of the site.
+	Don’t include to the site update.
 </t>
       </text>
     </comment>
-    <comment authorId="12" xr:uid="{2c8ed81e-3326-46d4-b763-943e0288fec1}" ref="A1">
+    <comment authorId="12" xr:uid="{2892e23c-bb9d-4f2b-9058-05da9bdcc3e7}" ref="L32">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	ACT２完成とともにリリース
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	turnipman i beg you give this a look
 </t>
       </text>
     </comment>
-    <comment authorId="13" xr:uid="{2dbf9a50-de08-448c-921b-f137ceed0ef8}" ref="A1">
+    <comment authorId="13" xr:uid="{2bb25c71-e13f-4911-9260-d88d479f3b24}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	실제 웹사이트에 따라 수정 필요
-Modify according to the website
+	Check out https://motherencore.com to see in context.
 </t>
       </text>
     </comment>
-    <comment authorId="14" xr:uid="{2eb5ab60-dea9-47f8-a8cf-5b93f9d20387}" ref="A1">
+    <comment authorId="14" xr:uid="{2d10255f-a602-4f34-a181-cad4606ccf92}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Italiano
+	ACT1完成とともに変更
 </t>
       </text>
     </comment>
-    <comment authorId="15" xr:uid="{2ebfcb01-b5c6-4e78-8581-4a738e15b523}" ref="A1">
+    <comment authorId="15" xr:uid="{2de8525c-cbab-47ad-a067-83e489a582be}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Русский
+</t>
+      </text>
+    </comment>
+    <comment authorId="16" xr:uid="{2e94e805-272c-4561-a43a-e90a60217815}" ref="L43">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	miiight need a quick review
+</t>
+      </text>
+    </comment>
+    <comment authorId="17" xr:uid="{31a61dd4-ea85-4917-ace5-792fd05bc5d9}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	English
+</t>
+      </text>
+    </comment>
+    <comment authorId="18" xr:uid="{333b9de2-d579-4843-9826-1bcf122d7417}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -254,7 +299,34 @@
 </t>
       </text>
     </comment>
-    <comment authorId="16" xr:uid="{2f0f22cf-97c8-47da-a936-64bdec5060f6}" ref="A1">
+    <comment authorId="19" xr:uid="{33e4222c-7842-4ed2-ba68-605154f2aa08}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	These links are deprecated.
+</t>
+      </text>
+    </comment>
+    <comment authorId="20" xr:uid="{340713ce-abac-4ccd-803f-11e857beb63a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Three people: she/her and he/him.
+</t>
+      </text>
+    </comment>
+    <comment authorId="21" xr:uid="{35e6330e-d8ee-4639-bb67-86ec7c17a0a4}" ref="F64">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	![몰?루](/Assets/Funny/idk_ko.jpeg)
+</t>
+      </text>
+    </comment>
+    <comment authorId="22" xr:uid="{36de6290-1673-45d5-9ee6-9656000001ad}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -266,25 +338,34 @@
 </t>
       </text>
     </comment>
-    <comment authorId="17" xr:uid="{44ac9be2-6ede-4234-ac17-610e2fa15780}" ref="A1">
+    <comment authorId="23" xr:uid="{381259fb-7422-4b13-8188-ce4f65c7f2b7}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
+	Three people (including proofreader), all go by he/him.
 </t>
       </text>
     </comment>
-    <comment authorId="18" xr:uid="{466db0da-0d16-4782-a9ac-f094e280a786}" ref="E9">
+    <comment authorId="24" xr:uid="{40412b85-a802-4e60-af96-ad409284053a}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Made the MOTHER Shop link into the JP version
+	Two people (he/him).
 </t>
       </text>
     </comment>
-    <comment authorId="19" xr:uid="{49fa7608-6575-4d10-ab6c-bc0b07063997}" ref="A1">
+    <comment authorId="25" xr:uid="{40dc7763-bb48-44d2-a850-5951f004bc97}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Check out https://motherencore.com to see in context.
+</t>
+      </text>
+    </comment>
+    <comment authorId="26" xr:uid="{49ecf6e7-b70e-4c27-b0cf-ae57244efc76}" ref="L45">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -292,20 +373,49 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	she/her
+	please review
 </t>
       </text>
     </comment>
-    <comment authorId="20" xr:uid="{4a04c7e6-cd58-4325-adea-4f22053dd934}" ref="A1">
+    <comment authorId="27" xr:uid="{52801b53-d9ca-477c-aece-af3ab389bd22}" ref="B64">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	ACT1完成とともに変更
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	The English answer is an image:
+https://motherencore.com/Assets/Funny/idk.png
+If you want to use an image in your language too, please specify its full url.
 </t>
       </text>
     </comment>
-    <comment authorId="21" xr:uid="{5a0e6982-35be-44c6-8825-26bb1a3ec5bd}" ref="F63">
+    <comment authorId="28" xr:uid="{52ce54d3-bbf5-400b-ab48-5a4a6d4dde44}" ref="B64">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	![alt_text](image_url)
+You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
+You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
+Click the link on the left to access the Drive folder where to upload your translated image.
+</t>
+      </text>
+    </comment>
+    <comment authorId="29" xr:uid="{54d45a73-cb05-4b0a-b3b8-2d35fa4a331f}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Add "[" at the start of the cell. Fixed in the current json file, but for future it should be fixed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="30" xr:uid="{5b337d0e-0a52-41f8-9d60-46603971e594}" ref="F64">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -321,37 +431,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="22" xr:uid="{5d67f01f-c50a-4e04-bf45-5f091fa46ced}" ref="E90">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	変更する
-</t>
-      </text>
-    </comment>
-    <comment authorId="23" xr:uid="{5e5523d5-467b-42af-a815-d9b53d23486c}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Marked in gray are currently not used in version Act 2 of the site.
-</t>
-      </text>
-    </comment>
-    <comment authorId="24" xr:uid="{601a6e95-2f83-4477-8b6f-1870183f5af0}" ref="B63">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	![alt_text](image_url)
-You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
-You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
-Click the link on the left to access the Drive folder where to upload your translated image.
-</t>
-      </text>
-    </comment>
-    <comment authorId="25" xr:uid="{6026a4bf-051f-44fc-9ff3-86fe3c1a22a8}" ref="L31">
+    <comment authorId="31" xr:uid="{5c8e2781-2c32-4f64-8f07-80b10552412c}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -359,11 +439,38 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	turnipman i beg you give this a look
+	Replaced "the demo" with it
 </t>
       </text>
     </comment>
-    <comment authorId="26" xr:uid="{60b00f4f-63c8-4fac-b601-d3c53ceb3b92}" ref="B31">
+    <comment authorId="32" xr:uid="{5d8cf83c-434f-4ac0-b993-adaa8c79c8b7}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ACT２完成とともにリリース
+</t>
+      </text>
+    </comment>
+    <comment authorId="33" xr:uid="{5dbbe192-f116-41dc-a5ae-91d4b4346dc0}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Sam uses she/her pronouns now, change your translations if needed
+</t>
+      </text>
+    </comment>
+    <comment authorId="34" xr:uid="{60e461a9-b36e-4f83-8cd7-1fc925a77102}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Українська
+</t>
+      </text>
+    </comment>
+    <comment authorId="35" xr:uid="{64ca7417-4076-48a5-a53e-da087901bd7b}" ref="B32">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -385,7 +492,59 @@
 </t>
       </text>
     </comment>
-    <comment authorId="27" xr:uid="{632b1594-4ad3-4cdc-9e94-4280e5e53b60}" ref="A1">
+    <comment authorId="36" xr:uid="{6508a3e3-0a73-48ad-a311-f2ebb36a12ca}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Two people, he/him and any pronouns.
+</t>
+      </text>
+    </comment>
+    <comment authorId="37" xr:uid="{71e487f6-fd35-4653-9694-a6e58a5549b2}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	“It [Act 1] is entirely playable in (your language)!”
+But I think the English line can remain empty as it’s kinda expected for the game to be playable in English anyway.
+</t>
+      </text>
+    </comment>
+    <comment authorId="38" xr:uid="{73347ccf-7072-4d46-ad36-5499aff3631d}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	she/her
+</t>
+      </text>
+    </comment>
+    <comment authorId="39" xr:uid="{737482d5-7437-48a0-b8a9-55c05bea729f}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Deutsch
+</t>
+      </text>
+    </comment>
+    <comment authorId="40" xr:uid="{7f6133c7-b934-499c-a6db-2dfcdf999865}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Changed "demo" to Act 1
+</t>
+      </text>
+    </comment>
+    <comment authorId="41" xr:uid="{7f9a66b6-733c-46fa-ab12-1223740d1b6e}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -394,7 +553,61 @@
 </t>
       </text>
     </comment>
-    <comment authorId="28" xr:uid="{66410900-defc-4d4d-89f5-75a5ff151486}" ref="J1">
+    <comment authorId="42" xr:uid="{8189dae4-e47f-4195-ba5f-dc7a8d2fd8c2}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No change needed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="43" xr:uid="{856cb280-38e1-4416-9ecf-e9684ae70b7a}" ref="E16">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Proofreading needed
+</t>
+      </text>
+    </comment>
+    <comment authorId="44" xr:uid="{867a849d-6e1a-473f-be87-0074e6e9a3a1}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Français
+</t>
+      </text>
+    </comment>
+    <comment authorId="45" xr:uid="{87b39ee5-fcb5-4da0-a050-3e4f483237d0}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Check out https://motherencore.com to see in context.
+</t>
+      </text>
+    </comment>
+    <comment authorId="46" xr:uid="{8a55ac4d-8c02-4433-905b-f199bf071b21}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Two people (he/him)
+</t>
+      </text>
+    </comment>
+    <comment authorId="47" xr:uid="{8c804f1a-29a1-49a2-8402-146261413779}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	This is Markdown syntax for links, please keep the parentheses and brackets like they are in English.
+</t>
+      </text>
+    </comment>
+    <comment authorId="48" xr:uid="{8cf87132-ad0d-4385-aee0-03ec3d82e3be}" ref="J1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -406,144 +619,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="29" xr:uid="{66ae36f1-65a0-4bc9-9368-c2caca3af5b4}" ref="F63">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	![몰?루](/Assets/Funny/idk_ko.jpeg)
-</t>
-      </text>
-    </comment>
-    <comment authorId="30" xr:uid="{67bfeef1-3e42-4dfa-a26e-9a8a7997a2ef}" ref="J1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Don’t include to the site update.
-</t>
-      </text>
-    </comment>
-    <comment authorId="31" xr:uid="{69c1a2fd-9026-45d3-b0bf-6afedc3ba7a5}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Please mind the final whitespace
-</t>
-      </text>
-    </comment>
-    <comment authorId="32" xr:uid="{6e29eddb-b7cc-443c-8c9e-ba07f26f5cdc}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Polski
-</t>
-      </text>
-    </comment>
-    <comment authorId="33" xr:uid="{70133ada-1140-4c5c-83db-d89cd490898c}" ref="B63">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	The English answer is an image:
-https://motherencore.com/Assets/Funny/idk.png
-If you want to use an image in your language too, please specify its full url.
-</t>
-      </text>
-    </comment>
-    <comment authorId="34" xr:uid="{73703df5-6697-469a-a3cd-6d6416f03238}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No change needed here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="35" xr:uid="{75baa87e-0daf-4d88-be4a-dcc29fc9a2ab}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	한국어
-</t>
-      </text>
-    </comment>
-    <comment authorId="36" xr:uid="{76eecd81-f24b-4a32-8963-ed29c9e3b549}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Three people (including proofreader), all go by he/him.
-</t>
-      </text>
-    </comment>
-    <comment authorId="37" xr:uid="{785f2a4f-7399-418a-bdd9-9befb54191c2}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Same here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="38" xr:uid="{7b7af789-9505-4c1c-a5e4-825bd9910483}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Three people: she/her and he/him.
-</t>
-      </text>
-    </comment>
-    <comment authorId="39" xr:uid="{7f177953-b238-4b0b-9363-9fbb46f886bb}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Français
-</t>
-      </text>
-    </comment>
-    <comment authorId="40" xr:uid="{8450f601-2d3c-4553-8d1b-d710abf2fb0f}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Русский
-</t>
-      </text>
-    </comment>
-    <comment authorId="41" xr:uid="{8acc1d50-ea1b-4c59-87ea-3f7826b246ea}" ref="A89">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Include Japanese and Chinese.
-</t>
-      </text>
-    </comment>
-    <comment authorId="42" xr:uid="{8d7f6841-003a-4409-bc84-98e5cbf6100b}" ref="L27">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	can replace "недруг" with "ворог", but generally just needs review
-</t>
-      </text>
-    </comment>
-    <comment authorId="43" xr:uid="{8ec13475-da80-4712-9a9c-5418b01dc331}" ref="L57">
+    <comment authorId="49" xr:uid="{8f81d3dd-1312-4982-94e9-d4c6b7e02f4c}" ref="L58">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -555,7 +631,80 @@
 </t>
       </text>
     </comment>
-    <comment authorId="44" xr:uid="{930be254-c1d2-4647-a663-ecaaff3e0aca}" ref="A1">
+    <comment authorId="50" xr:uid="{90b0a8d9-0fe6-4f42-aa3a-46c4f9467fd2}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Marked in gray are currently not used in version Act 2 of the site.
+</t>
+      </text>
+    </comment>
+    <comment authorId="51" xr:uid="{90c4aceb-a2eb-40e0-be46-e57a410b76d6}" ref="L41">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	eh
+</t>
+      </text>
+    </comment>
+    <comment authorId="52" xr:uid="{92cd855f-46f7-4600-90de-bd97114414b2}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	This one doesn’t need to be changed, as it already applied to one single person.
+</t>
+      </text>
+    </comment>
+    <comment authorId="53" xr:uid="{966735a5-b23a-4d35-9bc9-9904e8b747df}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	한국어
+</t>
+      </text>
+    </comment>
+    <comment authorId="54" xr:uid="{96918f0a-ef75-4797-9e0a-64727be31579}" ref="E80">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	援のお気持ちありがとうございます！この作品はあくまでファンゲームですので、お金は一切受け取りません。サポートしていただきたい場合はファンゲームを広めるか、作品の開発陣の個別のプロジェクトに支援できます。また、クレジットページにて開発陣のSNSへのリンクがございますので、そちらからフォローしてみることもできます。
+</t>
+      </text>
+    </comment>
+    <comment authorId="55" xr:uid="{9840b638-f7bd-406c-9169-12e158f56357}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Marked in gray are currently not used in version Act 2 of the site.
+</t>
+      </text>
+    </comment>
+    <comment authorId="56" xr:uid="{98be36ba-e647-49d9-b6af-223f898981a9}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Please mind the final whitespace
+</t>
+      </text>
+    </comment>
+    <comment authorId="57" xr:uid="{9d9b5956-d03b-4126-ac49-9562ad29826a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	실제 웹사이트에 따라 수정 필요
+Modify according to the website
+</t>
+      </text>
+    </comment>
+    <comment authorId="58" xr:uid="{a0fc82db-f396-4f03-8bff-6edab3b0603f}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -564,7 +713,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="45" xr:uid="{98c96c55-4692-42c1-8dc6-3353f3265043}" ref="A1">
+    <comment authorId="59" xr:uid="{a5c0b4a6-d856-4c1f-8f64-bbcb0caf7d29}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	にほんご
+</t>
+      </text>
+    </comment>
+    <comment authorId="60" xr:uid="{a901c7a0-c951-49d1-9a06-2b0cf1f9cd10}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -575,47 +733,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="46" xr:uid="{9a67667e-f06a-4902-af6c-a038d80afdbd}" ref="A1">
+    <comment authorId="61" xr:uid="{ac7ccbe3-9879-47fb-b9e5-4ed7cbe8f12d}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	All features are separated into a entry; it's less work than refactoring the spreedsheet 
-parser.
+	Same here.
 </t>
       </text>
     </comment>
-    <comment authorId="47" xr:uid="{9b38449f-5d3e-4988-8c85-bd98804aac29}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Check out https://motherencore.com to see in context.
-</t>
-      </text>
-    </comment>
-    <comment authorId="48" xr:uid="{9b6068bd-d3e3-490a-a3cc-f773d9b2dad5}" ref="E15">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Proofreading needed
-</t>
-      </text>
-    </comment>
-    <comment authorId="49" xr:uid="{9c461af3-0a76-4357-8709-44b79b0dd4a9}" ref="L49">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wip
-</t>
-      </text>
-    </comment>
-    <comment authorId="50" xr:uid="{9c5b6606-6460-4394-a91c-6d92e36d87d6}" ref="J1">
+    <comment authorId="62" xr:uid="{b111389d-3e4c-4c02-9507-b6efbc2c0546}" ref="F1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -628,7 +755,79 @@
 </t>
       </text>
     </comment>
-    <comment authorId="51" xr:uid="{9dba93ec-e907-4d8a-8263-668e5a792279}" ref="A1">
+    <comment authorId="63" xr:uid="{b334a638-155d-468e-b357-e40af35e7207}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No change needed here.
+</t>
+      </text>
+    </comment>
+    <comment authorId="64" xr:uid="{b7d04dd8-b0b7-4970-8f90-4e181530b97d}" ref="B16">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Edited "wanting for" to "cheering for"
+</t>
+      </text>
+    </comment>
+    <comment authorId="65" xr:uid="{c5c9626c-8649-43fa-a504-c15d2a351181}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	2/3 people (he/him).
+</t>
+      </text>
+    </comment>
+    <comment authorId="66" xr:uid="{c60c62fb-9821-40bc-b627-491b0e423919}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Polski
+</t>
+      </text>
+    </comment>
+    <comment authorId="67" xr:uid="{cb412cbf-8232-41c6-94ad-4e9f77514aa3}" ref="E9">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Made the MOTHER Shop link into the JP version
+</t>
+      </text>
+    </comment>
+    <comment authorId="68" xr:uid="{cc44bae2-2338-4bed-b74a-545f3822d4e2}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Just duplicating the Spanish column so it doesn't end up empty
+</t>
+      </text>
+    </comment>
+    <comment authorId="69" xr:uid="{cfa765af-cd8b-4e2e-a060-c538157f01ef}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Español
+</t>
+      </text>
+    </comment>
+    <comment authorId="70" xr:uid="{d5546657-23ac-4de1-ae1a-f2889d20a03a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Italiano
+</t>
+      </text>
+    </comment>
+    <comment authorId="71" xr:uid="{dab604aa-881a-41bb-971d-82f63a072bbe}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -636,47 +835,61 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Replaced "the demo" with it
+	Please make sure it flows correctly between SITE_ABOUT_DL_INTRO_3 and SITE_ABOUT_DL_INTRO_4 after replacing Demo with Act 1.
+Reply:
+	Marked in gray are currently not used in version Act 2 of the site.
 </t>
       </text>
     </comment>
-    <comment authorId="52" xr:uid="{9dbc84ce-d0f6-4532-a8dd-9b2b1de2e2ca}" ref="A1">
+    <comment authorId="72" xr:uid="{e0382cf9-d1cf-448b-84e2-8f02c6a6aacf}" ref="E91">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	This one doesn’t need to be changed, as it already applied to one single person.
+	変更する
 </t>
       </text>
     </comment>
-    <comment authorId="53" xr:uid="{b182435a-8208-478a-8411-9684b207dd91}" ref="A1">
+    <comment authorId="73" xr:uid="{ef592d31-2bd9-4579-926c-58c982531371}" ref="L28">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Two people: she/her and he/him.
+	[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	can replace "недруг" with "ворог", but generally just needs review
 </t>
       </text>
     </comment>
-    <comment authorId="54" xr:uid="{b27521d1-ca5c-4230-a2c3-6d41d93e19d3}" ref="A1">
+    <comment authorId="74" xr:uid="{f0688438-8bed-47fb-8dcc-e49f9634940d}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Sam uses she/her pronouns now, change your translations if needed
+	Three people: she/her and he/him.
 </t>
       </text>
     </comment>
-    <comment authorId="55" xr:uid="{b3f1ed36-ea7f-47f1-94db-fbe1d7153e2f}" ref="A1">
+    <comment authorId="75" xr:uid="{f09601ed-d9f6-4a95-814a-f676a577d600}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Deutsch
+	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
 </t>
       </text>
     </comment>
-    <comment authorId="56" xr:uid="{bb67c07d-98b0-47ae-8673-5e0f6167a8f1}" ref="F1">
+    <comment authorId="76" xr:uid="{f6e65078-0f34-4582-ada2-df68221eba94}" ref="A90">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Include Japanese and Chinese.
+</t>
+      </text>
+    </comment>
+    <comment authorId="77" xr:uid="{fe7323c8-8c38-45c6-8198-519fd3bf3859}" ref="J1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -689,16 +902,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="57" xr:uid="{bc0a6b64-d551-4d5d-bbea-41210426058b}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Three people: she/her and he/him.
-</t>
-      </text>
-    </comment>
-    <comment authorId="58" xr:uid="{bcdbf49a-381b-4392-b1bc-a226ca625149}" ref="L44">
+    <comment authorId="78" xr:uid="{ff2bc842-c0fb-4549-8b18-d16d18896b58}" ref="L50">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -706,211 +910,7 @@
 	[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	please review
-</t>
-      </text>
-    </comment>
-    <comment authorId="59" xr:uid="{be47be4c-b536-42ce-be6f-a13096826dfb}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Backslash added to prevent the “#” symbol from being interpreted as a title tag.
-</t>
-      </text>
-    </comment>
-    <comment authorId="60" xr:uid="{c3d8cbd3-d28c-45a4-a5c3-f5e2884da06f}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Two people (he/him).
-</t>
-      </text>
-    </comment>
-    <comment authorId="61" xr:uid="{c51b2447-e631-4a6f-bc46-b98af5974d7a}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Roots no longer exists, this should be changed or removed.
-Reply:
-	I suggest we remove this paragraph entirely, what do you think @bismuthbloom@gmail.com?
-Reply:
-	Yeah I'm going to remove it with this push.
-</t>
-      </text>
-    </comment>
-    <comment authorId="62" xr:uid="{c595d7eb-6e87-4e92-96f2-66f0f375e009}" ref="B63">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	![alt_text](image_url)
-You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
-You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
-Click the link on the left to access the Drive folder where to upload your translated image.
-</t>
-      </text>
-    </comment>
-    <comment authorId="63" xr:uid="{c6730cf7-eb52-4e44-83ad-6fbf9f459c42}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	English
-</t>
-      </text>
-    </comment>
-    <comment authorId="64" xr:uid="{c91079ba-27dd-44e0-91e5-48daf7d2f91e}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	2/3 people (he/him).
-</t>
-      </text>
-    </comment>
-    <comment authorId="65" xr:uid="{c9a8892a-bcaa-4f99-bace-d9550286d605}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	にほんご
-</t>
-      </text>
-    </comment>
-    <comment authorId="66" xr:uid="{d3c092d0-a614-4f4d-a75b-40bf14bf0865}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Español
-</t>
-      </text>
-    </comment>
-    <comment authorId="67" xr:uid="{d61d3ac1-4646-4cfb-98eb-c55c8f1eb453}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Check out https://motherencore.com to see in context.
-</t>
-      </text>
-    </comment>
-    <comment authorId="68" xr:uid="{dc4ec4e0-44e0-4ab6-8f81-6a35b6f9f8cd}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Add "[" at the start of the cell. Fixed in the current json file, but for future it should be fixed here.
-</t>
-      </text>
-    </comment>
-    <comment authorId="69" xr:uid="{dc7776e0-8028-451f-befd-ca75dc360899}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	This is European Spanish (Español Castellano)
-</t>
-      </text>
-    </comment>
-    <comment authorId="70" xr:uid="{e84954c0-d0c5-4caa-86fb-9198be6ea767}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Two people (he/him)
-</t>
-      </text>
-    </comment>
-    <comment authorId="71" xr:uid="{ec6c9a8d-d58e-4251-baf7-3474f7ca6228}" ref="L42">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	miiight need a quick review
-</t>
-      </text>
-    </comment>
-    <comment authorId="72" xr:uid="{ed193ca0-e81b-4276-916d-e12d401ffb44}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	These links are deprecated.
-</t>
-      </text>
-    </comment>
-    <comment authorId="73" xr:uid="{f23534da-0d71-462d-9ef0-618a7fb4d356}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	“It [Act 1] is entirely playable in (your language)!”
-But I think the English line can remain empty as it’s kinda expected for the game to be playable in English anyway.
-</t>
-      </text>
-    </comment>
-    <comment authorId="74" xr:uid="{f2fffab0-04eb-46bd-b447-5c49d9104ad6}" ref="K1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Don’t include to the site update.
-</t>
-      </text>
-    </comment>
-    <comment authorId="75" xr:uid="{fa7572e6-c822-414c-a4e7-cc476aa4f7de}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Just duplicating the Spanish column so it doesn't end up empty
-</t>
-      </text>
-    </comment>
-    <comment authorId="76" xr:uid="{fc8d9e4a-0d5e-4392-9ce1-64242683d796}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Two people, he/him and any pronouns.
-</t>
-      </text>
-    </comment>
-    <comment authorId="77" xr:uid="{fde29e80-d481-473e-8561-39a94b51bf93}" ref="F10">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	실제 웹사이트에 따라 수정 필요
-Modify according to the website
-</t>
-      </text>
-    </comment>
-    <comment authorId="78" xr:uid="{fe470b81-53cb-4e9a-97a0-b3fb9323c784}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No change needed here.
+	wip
 </t>
       </text>
     </comment>
@@ -919,7 +919,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="1146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="1148">
   <si>
     <t>key</t>
   </si>
@@ -1284,6 +1284,12 @@
   </si>
   <si>
     <t>第一幕&amp;第二幕 现已推出！</t>
+  </si>
+  <si>
+    <t>SITE_BANNER_DEVLOG_NEWS</t>
+  </si>
+  <si>
+    <t>Read the latest news!</t>
   </si>
   <si>
     <t>SITE_HOME_HEADLINE</t>
@@ -5035,44 +5041,44 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Andy" id="{96f189bd-e52c-438a-bd23-2243d057e9f5}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={886a0772-a652-4cf0-8001-6b3b369f02a7}" id="{edb94916-1f3c-4424-9e50-64fd03f26652}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={7f01b7a3-72ee-45c2-bb66-47cec55f0069}" id="{46621b50-bbc0-465b-8096-c5c38238fd11}" providerId="google-sheets"/>
-  <x18tc:person displayName="It should say" id="{56f1c93b-e824-48d5-9188-0f5fe1eef959}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={98457d25-d0e2-4f46-8629-2eaf29491de7}" id="{d1305d1d-518e-43a5-a7e2-8f954674aec5}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={d86d4f9a-16ae-41c7-9220-a1a73203876c}" id="{66f3434b-a8a0-4c50-a038-0399ce5e2a5d}" providerId="google-sheets"/>
-  <x18tc:person displayName="Syntax to insert an image" id="{aa36bd1e-9a57-422b-a85d-b527e92ef2a7}" providerId="google-sheets"/>
-  <x18tc:person displayName="" id="{a81a1166-c954-4e55-890f-3982c7762ac2}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={9da47017-07ee-4d8c-ba08-4a3c2c6332e0}" id="{c9806458-11be-469c-b8f8-871b51d48eb1}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={c19c0cfe-a1f1-4cc9-801e-857fe26d952a}" id="{ceb3cd56-b60f-4037-9001-12af829969cf}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={55cd3fa3-199c-4632-b417-fba209b2594a}" id="{2cb93ba1-da7c-44e4-b57f-ea597fab6616}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={0f6dd66b-869f-43d9-bfc0-15b956d18e2a}" id="{df072fe9-4d80-4992-b368-1d6fdf462405}" providerId="google-sheets"/>
-  <x18tc:person displayName="보석" id="{ec07d127-5809-4290-811e-a65c956803c9}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={5a18eb6c-3f60-4d37-bd2e-2acc3dc98df8}" id="{a4216300-3b20-4942-9464-0e2f1b4d0a43}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={8da23618-7fc8-4c86-b361-946024645808}" id="{7084451a-f0e1-428e-9af2-b2690cfd618b}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={87e287a5-c153-40cd-8eed-ec1ec11e568f}" id="{3abe3a9c-9fd1-4561-a273-f6ba255256f0}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={a2cbbe23-89a4-4696-b8de-12871cb556b8}" id="{81d3ddfe-e3b5-4c56-ac37-73849823ae7f}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={deef05f7-aa29-4a9a-b653-f24d312406f7}" id="{35a1d006-1449-43e6-a654-e94e48b853a8}" providerId="google-sheets"/>
-  <x18tc:person displayName="Marcos Vinicios de Morais" id="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={97913bf9-94e4-4a63-ba01-4e25533c8a02}" id="{dc151804-7211-49d9-971f-75a7c1046fe5}" providerId="google-sheets"/>
-  <x18tc:person displayName="baka (Jimmy)" id="{78fcdf4d-9cc3-4b97-9c61-5ea7290cc6de}" providerId="google-sheets"/>
-  <x18tc:person displayName="Danionel" id="{5854d707-18da-4cee-9e77-a8b56f0eb5bb}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={f1835a49-7095-4a4b-b082-eb4c7d31c679}" id="{0aa4e09d-c8b9-4c42-9697-015dc89a88b5}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={63b80276-1f1f-4158-9545-ffdd2d21ecb7}" id="{e8801c46-c217-4335-983b-06c9a88d6001}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={c88575e6-dacb-4386-bb27-227fb486ed9f}" id="{46d0db03-c514-428e-86a5-19ae153bc010}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={3d82b67f-ed31-46ae-aa73-752050e5b296}" id="{2eb4c227-7311-4b18-a293-6a9ac10efa82}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={4508b080-7cdf-41ca-90b8-fa03db8b7544}" id="{220b43fb-356b-4a2a-b4a3-de360a23d9a9}" providerId="google-sheets"/>
-  <x18tc:person displayName="bismuthbloom@gmail.com" id="{00280267-c64f-461e-a7a8-daf92496f69c}" userId="bismuthbloom@gmail.com" providerId="google-sheets"/>
-  <x18tc:person displayName="Aiden" id="{22bcdd3b-4c75-481d-818f-e32834552275}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={8a68bd66-5614-411f-a5a4-51e9af64d185}" id="{59f51fbf-2b7c-4a6c-8f61-8a476115c91d}" providerId="google-sheets"/>
-  <x18tc:person displayName="Altoz Bass Tenor" id="{6595ce0d-9691-4031-939c-69dcccc2657a}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={1aa364c2-7f01-4995-b24e-a3f74b1607eb}" id="{e4e6e3fe-e93b-4656-9304-66b137e6ec81}" providerId="google-sheets"/>
-  <x18tc:person displayName="tc={71cb1f5f-bab7-4f22-9d94-7a0e119fa63f}" id="{d22cc993-15ba-42bb-8c71-52455ec51b8a}" providerId="google-sheets"/>
+  <x18tc:person displayName="Andy" id="{65dc10b5-c626-44a2-ae8e-755d76d7b490}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={886a0772-a652-4cf0-8001-6b3b369f02a7}" id="{1502506d-ae30-414f-9097-ebcc0d0330bb}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={7f01b7a3-72ee-45c2-bb66-47cec55f0069}" id="{a86ab71f-5892-41f1-b9c0-2eb727605150}" providerId="google-sheets"/>
+  <x18tc:person displayName="It should say" id="{bfe96830-b6a1-4050-9fa3-a7ec3249d799}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={98457d25-d0e2-4f46-8629-2eaf29491de7}" id="{98b1f695-b0c0-4115-95dc-421c70ee6756}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={d86d4f9a-16ae-41c7-9220-a1a73203876c}" id="{c3c79262-8b6e-470e-bdd2-0e6defd68034}" providerId="google-sheets"/>
+  <x18tc:person displayName="Syntax to insert an image" id="{8f5d9aaf-502a-4d28-b8e7-47aeb09fdfa7}" providerId="google-sheets"/>
+  <x18tc:person displayName="" id="{c959c6b2-2511-4213-992b-316da21d9c88}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={9da47017-07ee-4d8c-ba08-4a3c2c6332e0}" id="{37e0add7-beb1-4ee2-a820-eca50306f3d3}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={c19c0cfe-a1f1-4cc9-801e-857fe26d952a}" id="{6c7a8691-b083-499c-b6a7-4bb8b426889e}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={55cd3fa3-199c-4632-b417-fba209b2594a}" id="{d1d48ba5-2418-4d4e-b490-51f97962b851}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={0f6dd66b-869f-43d9-bfc0-15b956d18e2a}" id="{56a22405-3daa-47c9-b790-a9c58bae3755}" providerId="google-sheets"/>
+  <x18tc:person displayName="보석" id="{93c5ba82-6524-41b5-953e-94eb8c447466}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={5a18eb6c-3f60-4d37-bd2e-2acc3dc98df8}" id="{6009fd20-8b5e-46d9-a8b7-0728a972dbea}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={8da23618-7fc8-4c86-b361-946024645808}" id="{ae0b1b08-0c5f-44d8-a6f7-4a49f0da2108}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={87e287a5-c153-40cd-8eed-ec1ec11e568f}" id="{a51abb43-c2fd-4ac0-af65-a2d453610e59}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={a2cbbe23-89a4-4696-b8de-12871cb556b8}" id="{d8a5310a-bc81-4fbb-9301-c4aa848fb8c2}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={deef05f7-aa29-4a9a-b653-f24d312406f7}" id="{980e08e6-106e-43c1-a6b6-24ac5482f04b}" providerId="google-sheets"/>
+  <x18tc:person displayName="Marcos Vinicios de Morais" id="{283a5e59-40f1-4f8a-9f61-6869827603b7}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={97913bf9-94e4-4a63-ba01-4e25533c8a02}" id="{2a464da5-9b4c-4e81-8a7d-60d12a5b3e28}" providerId="google-sheets"/>
+  <x18tc:person displayName="baka (Jimmy)" id="{dfa16b5f-8d1a-4531-9295-51a962fdfe1d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Danionel" id="{ca5696e5-4107-4b11-92ed-c8c5b9986b85}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={f1835a49-7095-4a4b-b082-eb4c7d31c679}" id="{01a460fa-4a2d-46dd-bdfd-618205d90612}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={63b80276-1f1f-4158-9545-ffdd2d21ecb7}" id="{8f07f022-d64e-4efe-a2e3-984e6e153623}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={c88575e6-dacb-4386-bb27-227fb486ed9f}" id="{c0d3192b-fa41-4f53-971b-8a7103d9a7b9}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={3d82b67f-ed31-46ae-aa73-752050e5b296}" id="{6d199fa3-9a2e-47e8-a9ce-d1ac375bd7e6}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={4508b080-7cdf-41ca-90b8-fa03db8b7544}" id="{1e6f3e1e-9e8c-4e56-a70c-a54e2ffad514}" providerId="google-sheets"/>
+  <x18tc:person displayName="bismuthbloom@gmail.com" id="{e7750c45-8861-4137-85b0-a0243272f11b}" userId="bismuthbloom@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Aiden" id="{ba2ea41b-4cb1-4181-9c01-4adfab25490c}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={8a68bd66-5614-411f-a5a4-51e9af64d185}" id="{2c3282d5-6051-425d-b4cc-dc3ba3c277cd}" providerId="google-sheets"/>
+  <x18tc:person displayName="Altoz Bass Tenor" id="{bb7ceead-00d7-43da-a888-4bc723fb1720}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={1aa364c2-7f01-4995-b24e-a3f74b1607eb}" id="{673d8875-7ff4-482c-a230-4787ebfd3624}" providerId="google-sheets"/>
+  <x18tc:person displayName="tc={71cb1f5f-bab7-4f22-9d94-7a0e119fa63f}" id="{2000d820-b8f9-472c-8666-f1874c5077bb}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J96" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J97" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="10">
     <tableColumn name="key" id="1"/>
     <tableColumn name="en" id="2"/>
@@ -5090,7 +5096,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="K1:N94" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="K1:N95" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="4">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -5302,10 +5308,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-06T17:13:37.00" personId="{5854d707-18da-4cee-9e77-a8b56f0eb5bb}" id="{b27521d1-ca5c-4230-a2c3-6d41d93e19d3}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-06T17:13:37.00" personId="{ca5696e5-4107-4b11-92ed-c8c5b9986b85}" id="{5dbbe192-f116-41dc-a5ae-91d4b4346dc0}" done="0">
     <x18tc:text xml:space="preserve">Sam uses she/her pronouns now, change your translations if needed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{d1305d1d-518e-43a5-a7e2-8f954674aec5}" id="{9c5b6606-6460-4394-a91c-6d92e36d87d6}" done="1">
+  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{98b1f695-b0c0-4115-95dc-421c70ee6756}" id="{fe7323c8-8c38-45c6-8198-519fd3bf3859}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5318,10 +5324,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{b182435a-8208-478a-8411-9684b207dd91}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{20655de3-1bb2-455c-8194-4dad8b1da06a}" done="0">
     <x18tc:text xml:space="preserve">Two people: she/her and he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B31" dT="2026-02-10T08:20:52.00" personId="{46d0db03-c514-428e-86a5-19ae153bc010}" id="{60b00f4f-63c8-4fac-b601-d3c53ceb3b92}" done="0">
+  <x18tc:threadedComment ref="B32" dT="2026-02-10T08:20:52.00" personId="{c0d3192b-fa41-4f53-971b-8a7103d9a7b9}" id="{64ca7417-4076-48a5-a53e-da087901bd7b}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5339,13 +5345,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B31" dT="2026-09-08T14:45:44.00" personId="{78fcdf4d-9cc3-4b97-9c61-5ea7290cc6de}" id="{f972b795-acc0-46d1-8300-5d81b7f05811}" parentId="{60b00f4f-63c8-4fac-b601-d3c53ceb3b92}">
+  <x18tc:threadedComment ref="B32" dT="2026-09-08T14:45:44.00" personId="{dfa16b5f-8d1a-4531-9295-51a962fdfe1d}" id="{26b7b030-6978-45c2-a7b4-beac541ee466}" parentId="{64ca7417-4076-48a5-a53e-da087901bd7b}">
     <x18tc:text xml:space="preserve">Marked as resolved</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B31" dT="2026-09-08T14:46:13.00" personId="{78fcdf4d-9cc3-4b97-9c61-5ea7290cc6de}" id="{b8890e39-98fd-44a5-acff-1fdff640ebe0}" parentId="{60b00f4f-63c8-4fac-b601-d3c53ceb3b92}">
+  <x18tc:threadedComment ref="B32" dT="2026-09-08T14:46:13.00" personId="{dfa16b5f-8d1a-4531-9295-51a962fdfe1d}" id="{33240b00-f78d-44e3-a2ad-5a3f526484e9}" parentId="{64ca7417-4076-48a5-a53e-da087901bd7b}">
     <x18tc:text xml:space="preserve">Re-opened</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{81d3ddfe-e3b5-4c56-ac37-73849823ae7f}" id="{70133ada-1140-4c5c-83db-d89cd490898c}" done="1">
+  <x18tc:threadedComment ref="B64" dT="2026-02-10T08:20:52.00" personId="{d8a5310a-bc81-4fbb-9301-c4aa848fb8c2}" id="{52801b53-d9ca-477c-aece-af3ab389bd22}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5360,13 +5366,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:09:48.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{5e5523d5-467b-42af-a815-d9b53d23486c}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:09:48.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{9840b638-f7bd-406c-9169-12e158f56357}" done="0">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{c6730cf7-eb52-4e44-83ad-6fbf9f459c42}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{a0fc82db-f396-4f03-8bff-6edab3b0603f}" done="0">
     <x18tc:text xml:space="preserve">English</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-02-10T08:20:52.00" personId="{220b43fb-356b-4a2a-b4a3-de360a23d9a9}" id="{0a80988b-e1c9-4bfd-93f8-77dea106e34e}" done="0">
+  <x18tc:threadedComment ref="F19" dT="2026-02-10T08:20:52.00" personId="{1e6f3e1e-9e8c-4e56-a70c-a54e2ffad514}" id="{255de392-ad36-46dd-9eb7-c2782b472eea}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5385,7 +5391,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{02a41813-fe8d-4270-85fe-a31766c005b4}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{2bb25c71-e13f-4911-9260-d88d479f3b24}" done="0">
     <x18tc:text xml:space="preserve">Check out https://motherencore.com to see in context.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5394,25 +5400,25 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{0cc7855e-8347-46c8-a1c7-b37e54b0ff01}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{19006183-814e-484a-b1b4-8acdff0f26fe}" done="0">
     <x18tc:text xml:space="preserve">No change needed here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{7b7af789-9505-4c1c-a5e4-825bd9910483}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{f0688438-8bed-47fb-8dcc-e49f9634940d}" done="0">
     <x18tc:text xml:space="preserve">Three people: she/her and he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{0ca07eab-e45e-42dc-a160-471b15eefb20}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{60e461a9-b36e-4f83-8cd7-1fc925a77102}" done="0">
     <x18tc:text xml:space="preserve">Українська</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{930be254-c1d2-4647-a663-ecaaff3e0aca}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{31a61dd4-ea85-4917-ace5-792fd05bc5d9}" done="0">
     <x18tc:text xml:space="preserve">English</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E79" dT="2026-09-13T07:53:46.00" personId="{6595ce0d-9691-4031-939c-69dcccc2657a}" id="{10d976d3-1153-4867-9b29-a382d87ca2cb}" done="0">
+  <x18tc:threadedComment ref="E80" dT="2026-09-13T07:53:46.00" personId="{bb7ceead-00d7-43da-a888-4bc723fb1720}" id="{96918f0a-ef75-4797-9e0a-64727be31579}" done="0">
     <x18tc:text xml:space="preserve">援のお気持ちありがとうございます！この作品はあくまでファンゲームですので、お金は一切受け取りません。サポートしていただきたい場合はファンゲームを広めるか、作品の開発陣の個別のプロジェクトに支援できます。また、クレジットページにて開発陣のSNSへのリンクがございますので、そちらからフォローしてみることもできます。</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{c91079ba-27dd-44e0-91e5-48daf7d2f91e}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{c5c9626c-8649-43fa-a504-c15d2a351181}" done="0">
     <x18tc:text xml:space="preserve">2/3 people (he/him).</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L27" dT="2026-02-10T08:20:52.00" personId="{7084451a-f0e1-428e-9af2-b2690cfd618b}" id="{8d7f6841-003a-4409-bc84-98e5cbf6100b}" done="0">
+  <x18tc:threadedComment ref="L28" dT="2026-02-10T08:20:52.00" personId="{ae0b1b08-0c5f-44d8-a6f7-4a49f0da2108}" id="{ef592d31-2bd9-4579-926c-58c982531371}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5424,10 +5430,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E15" dT="2026-09-13T07:38:34.00" personId="{6595ce0d-9691-4031-939c-69dcccc2657a}" id="{9b6068bd-d3e3-490a-a3cc-f773d9b2dad5}" done="0">
+  <x18tc:threadedComment ref="E16" dT="2026-09-13T07:38:34.00" personId="{bb7ceead-00d7-43da-a888-4bc723fb1720}" id="{856cb280-38e1-4416-9ecf-e9684ae70b7a}" done="0">
     <x18tc:text xml:space="preserve">Proofreading needed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L42" dT="2026-02-10T08:20:52.00" personId="{e4e6e3fe-e93b-4656-9304-66b137e6ec81}" id="{ec6c9a8d-d58e-4251-baf7-3474f7ca6228}" done="1">
+  <x18tc:threadedComment ref="L43" dT="2026-02-10T08:20:52.00" personId="{673d8875-7ff4-482c-a230-4787ebfd3624}" id="{2e94e805-272c-4561-a43a-e90a60217815}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5439,7 +5445,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L44" dT="2026-02-10T08:20:52.00" personId="{66f3434b-a8a0-4c50-a038-0399ce5e2a5d}" id="{bcdbf49a-381b-4392-b1bc-a226ca625149}" done="1">
+  <x18tc:threadedComment ref="L45" dT="2026-02-10T08:20:52.00" personId="{c3c79262-8b6e-470e-bdd2-0e6defd68034}" id="{49ecf6e7-b70e-4c27-b0cf-ae57244efc76}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5451,13 +5457,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{d3c092d0-a614-4f4d-a75b-40bf14bf0865}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{cfa765af-cd8b-4e2e-a060-c538157f01ef}" done="0">
     <x18tc:text xml:space="preserve">Español</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{73703df5-6697-469a-a3cd-6d6416f03238}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{8189dae4-e47f-4195-ba5f-dc7a8d2fd8c2}" done="0">
     <x18tc:text xml:space="preserve">No change needed here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{ceb3cd56-b60f-4037-9001-12af829969cf}" id="{dc7776e0-8028-451f-befd-ca75dc360899}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{6c7a8691-b083-499c-b6a7-4bb8b426889e}" id="{15a9cdee-2196-4249-a2f5-d6d4758cc8fa}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5469,13 +5475,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E90" dT="2026-06-04T09:40:30.00" personId="{6595ce0d-9691-4031-939c-69dcccc2657a}" id="{5d67f01f-c50a-4e04-bf45-5f091fa46ced}" done="0">
+  <x18tc:threadedComment ref="E91" dT="2026-06-04T09:40:30.00" personId="{bb7ceead-00d7-43da-a888-4bc723fb1720}" id="{e0382cf9-d1cf-448b-84e2-8f02c6a6aacf}" done="0">
     <x18tc:text xml:space="preserve">変更する</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{76eecd81-f24b-4a32-8963-ed29c9e3b549}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{381259fb-7422-4b13-8188-ce4f65c7f2b7}" done="0">
     <x18tc:text xml:space="preserve">Three people (including proofreader), all go by he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L31" dT="2026-02-10T08:20:52.00" personId="{d22cc993-15ba-42bb-8c71-52455ec51b8a}" id="{6026a4bf-051f-44fc-9ff3-86fe3c1a22a8}" done="0">
+  <x18tc:threadedComment ref="L32" dT="2026-02-10T08:20:52.00" personId="{2000d820-b8f9-472c-8666-f1874c5077bb}" id="{2892e23c-bb9d-4f2b-9058-05da9bdcc3e7}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5487,16 +5493,16 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{c3d8cbd3-d28c-45a4-a5c3-f5e2884da06f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{40412b85-a802-4e60-af96-ad409284053a}" done="0">
     <x18tc:text xml:space="preserve">Two people (he/him).</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:51.00" personId="{6595ce0d-9691-4031-939c-69dcccc2657a}" id="{4a04c7e6-cd58-4325-adea-4f22053dd934}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:51.00" personId="{bb7ceead-00d7-43da-a888-4bc723fb1720}" id="{2d10255f-a602-4f34-a181-cad4606ccf92}" done="0">
     <x18tc:text xml:space="preserve">ACT1完成とともに変更</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{bc0a6b64-d551-4d5d-bbea-41210426058b}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{340713ce-abac-4ccd-803f-11e857beb63a}" done="0">
     <x18tc:text xml:space="preserve">Three people: she/her and he/him.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{2eb4c227-7311-4b18-a293-6a9ac10efa82}" id="{1c4dcbf0-f957-46df-9413-03242f773820}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{6d199fa3-9a2e-47e8-a9ce-d1ac375bd7e6}" id="{7f6133c7-b934-499c-a6db-2dfcdf999865}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5508,7 +5514,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F63" dT="2026-02-10T08:20:52.00" personId="{3abe3a9c-9fd1-4561-a273-f6ba255256f0}" id="{5a0e6982-35be-44c6-8825-26bb1a3ec5bd}" done="1">
+  <x18tc:threadedComment ref="F64" dT="2026-02-10T08:20:52.00" personId="{a51abb43-c2fd-4ac0-af65-a2d453610e59}" id="{5b337d0e-0a52-41f8-9d60-46603971e594}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5525,7 +5531,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{46621b50-bbc0-465b-8096-c5c38238fd11}" id="{67bfeef1-3e42-4dfa-a26e-9a8a7997a2ef}" done="1">
+  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{a86ab71f-5892-41f1-b9c0-2eb727605150}" id="{8cf87132-ad0d-4385-aee0-03ec3d82e3be}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5537,7 +5543,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{df072fe9-4d80-4992-b368-1d6fdf462405}" id="{2719fd2e-6b88-496c-b1ef-29278cf376a7}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{56a22405-3daa-47c9-b790-a9c58bae3755}" id="{dab604aa-881a-41bb-971d-82f63a072bbe}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5549,25 +5555,25 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:15.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{59f1abfc-06a9-4cba-b024-988e5828e3b3}" parentId="{2719fd2e-6b88-496c-b1ef-29278cf376a7}">
+  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:15.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{3d5fd22f-1265-4d75-9432-4bc09cf352f2}" parentId="{dab604aa-881a-41bb-971d-82f63a072bbe}">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-05T15:51:09.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{fa7572e6-c822-414c-a4e7-cc476aa4f7de}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-05T15:51:09.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{cc44bae2-2338-4bed-b74a-545f3822d4e2}" done="0">
     <x18tc:text xml:space="preserve">Just duplicating the Spanish column so it doesn't end up empty</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{69c1a2fd-9026-45d3-b0bf-6afedc3ba7a5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{98be36ba-e647-49d9-b6af-223f898981a9}" done="0">
     <x18tc:text xml:space="preserve">Please mind the final whitespace</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{e84954c0-d0c5-4caa-86fb-9198be6ea767}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{8a55ac4d-8c02-4433-905b-f199bf071b21}" done="0">
     <x18tc:text xml:space="preserve">Two people (he/him)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{44ac9be2-6ede-4234-ac17-610e2fa15780}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{f09601ed-d9f6-4a95-814a-f676a577d600}" done="0">
     <x18tc:text xml:space="preserve">Backslash added to prevent the “#” symbol from being interpreted as a title tag.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{be47be4c-b536-42ce-be6f-a13096826dfb}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{236d2932-626f-4e6b-9687-e7d336e3e885}" done="0">
     <x18tc:text xml:space="preserve">Backslash added to prevent the “#” symbol from being interpreted as a title tag.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{35a1d006-1449-43e6-a654-e94e48b853a8}" id="{c51b2447-e631-4a6f-bc46-b98af5974d7a}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{980e08e6-106e-43c1-a6b6-24ac5482f04b}" id="{0d9f261e-6d73-4b8d-9c9b-a6bd7c7b4737}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5577,7 +5583,7 @@
 Reply:
 	Yeah I'm going to remove it with this push.</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{00280267-c64f-461e-a7a8-daf92496f69c}" mentionId="{65870dc9-9284-4210-88db-260570ec6597}" startIndex="376" length="23"/>
+      <x18tc:mention mentionpersonId="{e7750c45-8861-4137-85b0-a0243272f11b}" mentionId="{97a9e2f7-42cd-412c-bae8-0f143b2ec641}" startIndex="376" length="23"/>
     </x18tc:mentions>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5586,32 +5592,32 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:34.00" personId="{6595ce0d-9691-4031-939c-69dcccc2657a}" id="{2c8ed81e-3326-46d4-b763-943e0288fec1}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-06-04T09:39:34.00" personId="{bb7ceead-00d7-43da-a888-4bc723fb1720}" id="{5d8cf83c-434f-4ac0-b993-adaa8c79c8b7}" done="0">
     <x18tc:text xml:space="preserve">ACT２完成とともにリリース</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{98c96c55-4692-42c1-8dc6-3353f3265043}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{a901c7a0-c951-49d1-9a06-2b0cf1f9cd10}" done="0">
     <x18tc:text xml:space="preserve">From here, roles have to be singular and gender-neutral.
 If “programmer” can’t be gender-neutral in your language, you can go with “programming” (see next column) instead, and so on.
 Once a cell is done, you can remove the bold style.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{2eb5ab60-dea9-47f8-a8cf-5b93f9d20387}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{d5546657-23ac-4de1-ae1a-f2889d20a03a}" done="0">
     <x18tc:text xml:space="preserve">Italiano</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{56f1c93b-e824-48d5-9188-0f5fe1eef959}" id="{f23534da-0d71-462d-9ef0-618a7fb4d356}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{bfe96830-b6a1-4050-9fa3-a7ec3249d799}" id="{71e487f6-fd35-4653-9694-a6e58a5549b2}" done="0">
     <x18tc:text xml:space="preserve">“It [Act 1] is entirely playable in (your language)!”
 But I think the English line can remain empty as it’s kinda expected for the game to be playable in English anyway.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L40" dT="2026-08-27T09:41:22.00" personId="{22bcdd3b-4c75-481d-818f-e32834552275}" id="{03418033-4484-44d8-881b-854f15bad89c}" done="0">
+  <x18tc:threadedComment ref="L41" dT="2026-08-27T09:41:22.00" personId="{ba2ea41b-4cb1-4181-9c01-4adfab25490c}" id="{90c4aceb-a2eb-40e0-be46-e57a410b76d6}" done="0">
     <x18tc:text xml:space="preserve">eh</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-25T03:41:20.00" personId="{ec07d127-5809-4290-811e-a65c956803c9}" id="{2dbf9a50-de08-448c-921b-f137ceed0ef8}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-25T03:41:20.00" personId="{93c5ba82-6524-41b5-953e-94eb8c447466}" id="{9d9b5956-d03b-4126-ac49-9562ad29826a}" done="0">
     <x18tc:text xml:space="preserve">실제 웹사이트에 따라 수정 필요
 Modify according to the website</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{6e29eddb-b7cc-443c-8c9e-ba07f26f5cdc}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{c60c62fb-9821-40bc-b627-491b0e423919}" done="0">
     <x18tc:text xml:space="preserve">Polski</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F1" dT="2026-02-10T08:20:52.00" personId="{e8801c46-c217-4335-983b-06c9a88d6001}" id="{bb67c07d-98b0-47ae-8673-5e0f6167a8f1}" done="0">
+  <x18tc:threadedComment ref="F1" dT="2026-02-10T08:20:52.00" personId="{8f07f022-d64e-4efe-a2e3-984e6e153623}" id="{b111389d-3e4c-4c02-9507-b6efbc2c0546}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5624,10 +5630,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{9dbc84ce-d0f6-4532-a8dd-9b2b1de2e2ca}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{92cd855f-46f7-4600-90de-bd97114414b2}" done="0">
     <x18tc:text xml:space="preserve">This one doesn’t need to be changed, as it already applied to one single person.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L49" dT="2026-02-10T08:20:52.00" personId="{2cb93ba1-da7c-44e4-b57f-ea597fab6616}" id="{9c461af3-0a76-4357-8709-44b79b0dd4a9}" done="0">
+  <x18tc:threadedComment ref="L50" dT="2026-02-10T08:20:52.00" personId="{d1d48ba5-2418-4d4e-b490-51f97962b851}" id="{ff2bc842-c0fb-4549-8b18-d16d18896b58}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5639,13 +5645,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F63" dT="2026-08-25T03:59:16.00" personId="{ec07d127-5809-4290-811e-a65c956803c9}" id="{66ae36f1-65a0-4bc9-9368-c2caca3af5b4}" done="0">
+  <x18tc:threadedComment ref="F64" dT="2026-08-25T03:59:16.00" personId="{93c5ba82-6524-41b5-953e-94eb8c447466}" id="{35e6330e-d8ee-4639-bb67-86ec7c17a0a4}" done="0">
     <x18tc:text xml:space="preserve">![몰?루](/Assets/Funny/idk_ko.jpeg)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:06:31.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{ed193ca0-e81b-4276-916d-e12d401ffb44}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:06:31.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{33e4222c-7842-4ed2-ba68-605154f2aa08}" done="0">
     <x18tc:text xml:space="preserve">These links are deprecated.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c9806458-11be-469c-b8f8-871b51d48eb1}" id="{49fa7608-6575-4d10-ab6c-bc0b07063997}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{37e0add7-beb1-4ee2-a820-eca50306f3d3}" id="{73347ccf-7072-4d46-ad36-5499aff3631d}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5657,16 +5663,16 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{aa36bd1e-9a57-422b-a85d-b527e92ef2a7}" id="{c595d7eb-6e87-4e92-96f2-66f0f375e009}" done="1">
+  <x18tc:threadedComment ref="B64" dT="2026-02-10T08:20:52.00" personId="{8f5d9aaf-502a-4d28-b8e7-47aeb09fdfa7}" id="{139e050c-c289-441c-965e-3b33d9b1a0d0}" done="1">
     <x18tc:text xml:space="preserve">![alt_text](image_url)
 You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
 You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
 Click the link on the left to access the Drive folder where to upload your translated image.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E9" dT="2026-09-13T07:33:28.00" personId="{6595ce0d-9691-4031-939c-69dcccc2657a}" id="{466db0da-0d16-4782-a9ac-f094e280a786}" done="0">
+  <x18tc:threadedComment ref="E9" dT="2026-09-13T07:33:28.00" personId="{bb7ceead-00d7-43da-a888-4bc723fb1720}" id="{cb412cbf-8232-41c6-94ad-4e9f77514aa3}" done="0">
     <x18tc:text xml:space="preserve">Made the MOTHER Shop link into the JP version</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a4216300-3b20-4942-9464-0e2f1b4d0a43}" id="{9dba93ec-e907-4d8a-8263-668e5a792279}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{6009fd20-8b5e-46d9-a8b7-0728a972dbea}" id="{5c8e2781-2c32-4f64-8f07-80b10552412c}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5678,7 +5684,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="K1" dT="2026-02-10T08:20:52.00" personId="{dc151804-7211-49d9-971f-75a7c1046fe5}" id="{f2fffab0-04eb-46bd-b447-5c49d9104ad6}" done="1">
+  <x18tc:threadedComment ref="K1" dT="2026-02-10T08:20:52.00" personId="{2a464da5-9b4c-4e81-8a7d-60d12a5b3e28}" id="{2603192d-6d6c-4efe-a57b-92b8cf1e9c78}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5690,31 +5696,31 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A89" dT="2026-08-03T23:18:53.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{8acc1d50-ea1b-4c59-87ea-3f7826b246ea}" done="1">
+  <x18tc:threadedComment ref="A90" dT="2026-08-03T23:18:53.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{f6e65078-0f34-4582-ada2-df68221eba94}" done="1">
     <x18tc:text xml:space="preserve">Include Japanese and Chinese.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{75baa87e-0daf-4d88-be4a-dcc29fc9a2ab}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{966735a5-b23a-4d35-9bc9-9904e8b747df}" done="0">
     <x18tc:text xml:space="preserve">한국어</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:15:01.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{006fb328-f499-4c5a-8b55-a45eb780c4b5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T18:15:01.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{7f9a66b6-733c-46fa-ab12-1223740d1b6e}" done="0">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{0ca644c9-5f17-47ea-a23d-21985ecffa68}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{8c804f1a-29a1-49a2-8402-146261413779}" done="0">
     <x18tc:text xml:space="preserve">This is Markdown syntax for links, please keep the parentheses and brackets like they are in English.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:25.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{632b1594-4ad3-4cdc-9e94-4280e5e53b60}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-05T02:49:25.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{90b0a8d9-0fe6-4f42-aa3a-46c4f9467fd2}" done="0">
     <x18tc:text xml:space="preserve">Marked in gray are currently not used in version Act 2 of the site.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{b3f1ed36-ea7f-47f1-94db-fbe1d7153e2f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{737482d5-7437-48a0-b8a9-55c05bea729f}" done="0">
     <x18tc:text xml:space="preserve">Deutsch</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{785f2a4f-7399-418a-bdd9-9befb54191c2}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{ac7ccbe3-9879-47fb-b9e5-4ed7cbe8f12d}" done="0">
     <x18tc:text xml:space="preserve">Same here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{7f177953-b238-4b0b-9363-9fbb46f886bb}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{867a849d-6e1a-473f-be87-0074e6e9a3a1}" done="0">
     <x18tc:text xml:space="preserve">Français</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{0aa4e09d-c8b9-4c42-9697-015dc89a88b5}" id="{2f0f22cf-97c8-47da-a936-64bdec5060f6}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{01a460fa-4a2d-46dd-bdfd-618205d90612}" id="{36de6290-1673-45d5-9ee6-9656000001ad}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5726,10 +5732,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{2ebfcb01-b5c6-4e78-8581-4a738e15b523}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{333b9de2-d579-4843-9826-1bcf122d7417}" done="0">
     <x18tc:text xml:space="preserve">Português brasileiro</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{d61d3ac1-4646-4cfb-98eb-c55c8f1eb453}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{40dc7763-bb48-44d2-a850-5951f004bc97}" done="0">
     <x18tc:text xml:space="preserve">Check out https://motherencore.com to see in context.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5738,7 +5744,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{46621b50-bbc0-465b-8096-c5c38238fd11}" id="{66410900-defc-4d4d-89f5-75a5ff151486}" done="1">
+  <x18tc:threadedComment ref="J1" dT="2026-02-10T08:20:52.00" personId="{a86ab71f-5892-41f1-b9c0-2eb727605150}" id="{280a4ccf-d324-453d-8175-7c20353c80d9}" done="1">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5750,13 +5756,13 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B63" dT="2026-02-10T08:20:52.00" personId="{aa36bd1e-9a57-422b-a85d-b527e92ef2a7}" id="{601a6e95-2f83-4477-8b6f-1870183f5af0}" done="1">
+  <x18tc:threadedComment ref="B64" dT="2026-02-10T08:20:52.00" personId="{8f5d9aaf-502a-4d28-b8e7-47aeb09fdfa7}" id="{52ce54d3-bbf5-400b-ab48-5a4a6d4dde44}" done="1">
     <x18tc:text xml:space="preserve">![alt_text](image_url)
 You can use an meme image file here, just like the English “IDK” meme image (check the website!), but an equivalent in your language.
 You can either find an existing meme in your language that says something akin to “I don’t know”, or just edit the English image. Then, replace the url between parentheses.
 Click the link on the left to access the Drive folder where to upload your translated image.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{9b38449f-5d3e-4988-8c85-bd98804aac29}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{87b39ee5-fcb5-4da0-a050-3e4f483237d0}" done="0">
     <x18tc:text xml:space="preserve">Check out https://motherencore.com to see in context.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5765,27 +5771,27 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{fe470b81-53cb-4e9a-97a0-b3fb9323c784}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{b334a638-155d-468e-b357-e40af35e7207}" done="0">
     <x18tc:text xml:space="preserve">No change needed here.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{c9a8892a-bcaa-4f99-bace-d9550286d605}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{a5c0b4a6-d856-4c1f-8f64-bbcb0caf7d29}" done="0">
     <x18tc:text xml:space="preserve">にほんご</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B15" dT="2026-09-05T15:09:22.00" personId="{96f189bd-e52c-438a-bd23-2243d057e9f5}" id="{1fbddf5e-9f96-4242-857e-ebecbe218fb9}" done="0">
+  <x18tc:threadedComment ref="B16" dT="2026-09-05T15:09:22.00" personId="{65dc10b5-c626-44a2-ae8e-755d76d7b490}" id="{b7d04dd8-b0b7-4970-8f90-4e181530b97d}" done="0">
     <x18tc:text xml:space="preserve">Edited "wanting for" to "cheering for"</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{fc8d9e4a-0d5e-4392-9ce1-64242683d796}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{6508a3e3-0a73-48ad-a311-f2ebb36a12ca}" done="0">
     <x18tc:text xml:space="preserve">Two people, he/him and any pronouns.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F10" dT="2026-08-25T03:31:34.00" personId="{ec07d127-5809-4290-811e-a65c956803c9}" id="{fde29e80-d481-473e-8561-39a94b51bf93}" done="1">
+  <x18tc:threadedComment ref="F10" dT="2026-08-25T03:31:34.00" personId="{93c5ba82-6524-41b5-953e-94eb8c447466}" id="{1e25414e-a9e3-4900-b5de-162cf0b8f885}" done="1">
     <x18tc:text xml:space="preserve">실제 웹사이트에 따라 수정 필요
 Modify according to the website</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T17:36:36.00" personId="{a347cb52-f656-4b3a-934c-6fe04de0a9f4}" id="{9a67667e-f06a-4902-af6c-a038d80afdbd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T17:36:36.00" personId="{283a5e59-40f1-4f8a-9f61-6869827603b7}" id="{1797d56b-7de7-4dd1-8367-190d8ed9b71a}" done="0">
     <x18tc:text xml:space="preserve">All features are separated into a entry; it's less work than refactoring the spreedsheet 
 parser.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L57" dT="2026-02-10T08:20:52.00" personId="{59f51fbf-2b7c-4a6c-8f61-8a476115c91d}" id="{8ec13475-da80-4712-9a9c-5418b01dc331}" done="0">
+  <x18tc:threadedComment ref="L58" dT="2026-02-10T08:20:52.00" personId="{2c3282d5-6051-425d-b4cc-dc3ba3c277cd}" id="{8f81d3dd-1312-4982-94e9-d4c6b7e02f4c}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5797,7 +5803,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{edb94916-1f3c-4424-9e50-64fd03f26652}" id="{dc4ec4e0-44e0-4ab6-8f81-6a35b6f9f8cd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{1502506d-ae30-414f-9097-ebcc0d0330bb}" id="{54d45a73-cb05-4b0a-b3b8-2d35fa4a331f}" done="0">
     <x18tc:text xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
@@ -5809,7 +5815,7 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{a81a1166-c954-4e55-890f-3982c7762ac2}" id="{8450f601-2d3c-4553-8d1b-d710abf2fb0f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-02-10T08:20:52.00" personId="{c959c6b2-2511-4213-992b-316da21d9c88}" id="{2de8525c-cbab-47ad-a067-83e489a582be}" done="0">
     <x18tc:text xml:space="preserve">Русский</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -6464,45 +6470,23 @@
       <c r="AC11" s="7"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>133</v>
-      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="4"/>
       <c r="N12" s="3"/>
       <c r="O12" s="6"/>
       <c r="P12" s="7"/>
@@ -6521,48 +6505,48 @@
       <c r="AC12" s="6"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="M13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="N13" s="6"/>
+      <c r="N13" s="3"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="17"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
@@ -6578,48 +6562,48 @@
       <c r="AC13" s="6"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="M14" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="6"/>
       <c r="O14" s="6"/>
-      <c r="P14" s="7"/>
+      <c r="P14" s="17"/>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
@@ -6635,158 +6619,158 @@
       <c r="AC14" s="6"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="M15" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="N15" s="3"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="B16" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="E16" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="F16" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="H16" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="J16" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="20"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
+      <c r="L16" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="M16" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
-      <c r="AB16" s="6"/>
-      <c r="AC16" s="6"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="L17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="M17" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="6"/>
@@ -6806,44 +6790,44 @@
       <c r="AC17" s="6"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="M18" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="6"/>
@@ -6864,43 +6848,43 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="M19" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="6"/>
@@ -6920,44 +6904,44 @@
       <c r="AC19" s="6"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="M20" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="6"/>
@@ -6977,44 +6961,44 @@
       <c r="AC20" s="6"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="L21" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="M21" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="6"/>
@@ -7035,43 +7019,43 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="M22" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="6"/>
@@ -7091,44 +7075,44 @@
       <c r="AC22" s="6"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="M23" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="6"/>
@@ -7148,44 +7132,44 @@
       <c r="AC23" s="6"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="L24" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M24" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="6"/>
@@ -7206,43 +7190,43 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="M25" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="6"/>
@@ -7262,44 +7246,44 @@
       <c r="AC25" s="6"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="M26" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="6"/>
@@ -7319,44 +7303,44 @@
       <c r="AC26" s="6"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="M27" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="6"/>
@@ -7377,43 +7361,43 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="M28" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="6"/>
@@ -7433,44 +7417,44 @@
       <c r="AC28" s="6"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="M29" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="6"/>
@@ -7490,44 +7474,44 @@
       <c r="AC29" s="6"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="L30" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="M30" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>337</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="6"/>
@@ -7548,43 +7532,43 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="M31" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="6"/>
@@ -7605,43 +7589,43 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="M32" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="6"/>
@@ -7662,45 +7646,45 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="M33" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="N33" s="6"/>
+      <c r="N33" s="3"/>
       <c r="O33" s="6"/>
       <c r="P33" s="7"/>
       <c r="Q33" s="6"/>
@@ -7719,41 +7703,43 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="L34" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="M34" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="K34" s="6"/>
-      <c r="L34" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -7773,44 +7759,42 @@
       <c r="AC34" s="6"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="M35" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>400</v>
       </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
@@ -7831,41 +7815,43 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="L36" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="M36" s="7" t="s">
         <v>402</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="K36" s="6"/>
-      <c r="L36" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>412</v>
       </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
@@ -7886,43 +7872,41 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="M37" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>424</v>
       </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
@@ -7943,41 +7927,43 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="L38" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="M38" s="7" t="s">
         <v>426</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="K38" s="6"/>
-      <c r="L38" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>436</v>
       </c>
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
@@ -7997,44 +7983,42 @@
       <c r="AC38" s="6"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>428</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="M39" s="7" t="s">
         <v>438</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>449</v>
       </c>
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
@@ -8055,43 +8039,43 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="L40" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="M40" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="M40" s="7" t="s">
-        <v>462</v>
       </c>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
@@ -8111,46 +8095,46 @@
       <c r="AC40" s="6"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="M41" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="N41" s="3"/>
+      <c r="N41" s="6"/>
       <c r="O41" s="6"/>
       <c r="P41" s="7"/>
       <c r="Q41" s="6"/>
@@ -8168,44 +8152,44 @@
       <c r="AC41" s="6"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="M42" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="M42" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="6"/>
@@ -8226,43 +8210,43 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="M43" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>490</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="H43" s="27" t="s">
-        <v>494</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="6"/>
@@ -8283,43 +8267,43 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="H44" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="M44" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="C44" s="27" t="s">
-        <v>500</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="H44" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="6"/>
@@ -8339,44 +8323,44 @@
       <c r="AC44" s="6"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>502</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>507</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="M45" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="6"/>
@@ -8396,46 +8380,46 @@
       <c r="AC45" s="6"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="M46" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="M46" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="N46" s="6"/>
+      <c r="N46" s="3"/>
       <c r="O46" s="6"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="6"/>
@@ -8453,46 +8437,46 @@
       <c r="AC46" s="6"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>527</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B47" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="M47" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N47" s="3"/>
+      <c r="N47" s="6"/>
       <c r="O47" s="6"/>
       <c r="P47" s="7"/>
       <c r="Q47" s="6"/>
@@ -8510,44 +8494,44 @@
       <c r="AC47" s="6"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="30" t="s">
+        <v>539</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="L48" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="M48" s="4" t="s">
-        <v>555</v>
+        <v>51</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="6"/>
@@ -8567,44 +8551,44 @@
       <c r="AC48" s="6"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="31" t="s">
+        <v>545</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="M49" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>568</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="6"/>
@@ -8624,44 +8608,44 @@
       <c r="AC49" s="6"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="30" t="s">
+        <v>558</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>559</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="M50" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>581</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="6"/>
@@ -8682,43 +8666,43 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="26" t="s">
+        <v>571</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="M51" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="J51" s="32" t="s">
-        <v>591</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>594</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="6"/>
@@ -8739,43 +8723,43 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="26" t="s">
+        <v>584</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="J52" s="32" t="s">
+        <v>593</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="M52" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>607</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="6"/>
@@ -8796,43 +8780,43 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="26" t="s">
+        <v>597</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="M53" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>620</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="6"/>
@@ -8853,43 +8837,43 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="26" t="s">
+        <v>610</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="L54" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="M54" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="M54" s="4" t="s">
-        <v>633</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="6"/>
@@ -8909,44 +8893,44 @@
       <c r="AC54" s="6"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="30" t="s">
+      <c r="A55" s="26" t="s">
+        <v>623</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>624</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="M55" s="4" t="s">
         <v>635</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>646</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="6"/>
@@ -8966,44 +8950,44 @@
       <c r="AC55" s="6"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>637</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="L56" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="M56" s="4" t="s">
         <v>648</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>659</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="6"/>
@@ -9023,44 +9007,44 @@
       <c r="AC56" s="6"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="26" t="s">
+      <c r="A57" s="31" t="s">
+        <v>649</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>650</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="M57" s="4" t="s">
         <v>661</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>672</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="6"/>
@@ -9080,44 +9064,44 @@
       <c r="AC57" s="6"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="26" t="s">
+        <v>662</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="M58" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="M58" s="4" t="s">
-        <v>685</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="6"/>
@@ -9137,44 +9121,44 @@
       <c r="AC58" s="6"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="31" t="s">
+        <v>675</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="M59" s="4" t="s">
         <v>687</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="D59" s="33" t="s">
-        <v>689</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>690</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>698</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="6"/>
@@ -9195,43 +9179,43 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="26" t="s">
+        <v>688</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>691</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>692</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="M60" s="4" t="s">
         <v>700</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>707</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>711</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="6"/>
@@ -9252,43 +9236,43 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="26" t="s">
+        <v>701</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="L61" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="M61" s="4" t="s">
         <v>713</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="H61" s="32" t="s">
-        <v>719</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>724</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="6"/>
@@ -9309,43 +9293,43 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>715</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="H62" s="32" t="s">
+        <v>721</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="M62" s="4" t="s">
         <v>726</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>737</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="6"/>
@@ -9366,41 +9350,43 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="26" t="s">
+        <v>727</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>728</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="L63" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="M63" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>744</v>
-      </c>
-      <c r="H63" s="35" t="s">
-        <v>745</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="L63" s="3"/>
-      <c r="M63" s="4" t="s">
-        <v>749</v>
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="6"/>
@@ -9420,44 +9406,42 @@
       <c r="AC63" s="6"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="26" t="s">
+        <v>740</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="H64" s="35" t="s">
+        <v>747</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="K64" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="L64" s="3"/>
+      <c r="M64" s="4" t="s">
         <v>751</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="M64" s="4" t="s">
-        <v>762</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="6"/>
@@ -9477,42 +9461,44 @@
       <c r="AC64" s="6"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="26" t="s">
+      <c r="A65" s="31" t="s">
+        <v>752</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>753</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="L65" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="M65" s="4" t="s">
         <v>764</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>767</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="L65" s="36"/>
-      <c r="M65" s="4" t="s">
-        <v>774</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" s="6"/>
@@ -9533,43 +9519,41 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="26" t="s">
+        <v>765</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="K66" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="L66" s="36"/>
+      <c r="M66" s="4" t="s">
         <v>776</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="M66" s="4" t="s">
-        <v>787</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="6"/>
@@ -9590,43 +9574,43 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>778</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="M67" s="4" t="s">
         <v>789</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>796</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>800</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="6"/>
@@ -9647,43 +9631,43 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="26" t="s">
+        <v>790</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="L68" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="M68" s="4" t="s">
         <v>802</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>809</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="M68" s="4" t="s">
-        <v>813</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="6"/>
@@ -9704,43 +9688,43 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="26" t="s">
+        <v>803</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="M69" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>822</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="M69" s="4" t="s">
-        <v>826</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="6"/>
@@ -9761,43 +9745,43 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="26" t="s">
+        <v>816</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="L70" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="M70" s="4" t="s">
         <v>828</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="M70" s="4" t="s">
-        <v>839</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="6"/>
@@ -9818,43 +9802,43 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="26" t="s">
+        <v>829</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="M71" s="4" t="s">
         <v>841</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>848</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>849</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="M71" s="4" t="s">
-        <v>852</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="6"/>
@@ -9875,43 +9859,43 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="26" t="s">
+        <v>842</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>843</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="L72" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="M72" s="4" t="s">
         <v>854</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>856</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>858</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>859</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>860</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>861</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>862</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>863</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>864</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>865</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="6"/>
@@ -9932,43 +9916,43 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="26" t="s">
+        <v>855</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>856</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="L73" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="M73" s="4" t="s">
         <v>867</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>869</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>872</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>873</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>875</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>877</v>
-      </c>
-      <c r="M73" s="4" t="s">
-        <v>878</v>
       </c>
       <c r="N73" s="3"/>
       <c r="O73" s="6"/>
@@ -9989,43 +9973,43 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="26" t="s">
+        <v>868</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>869</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="L74" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="M74" s="4" t="s">
         <v>880</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>881</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>882</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>883</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>884</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>885</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>886</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>887</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>888</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>889</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>890</v>
-      </c>
-      <c r="M74" s="4" t="s">
-        <v>891</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="6"/>
@@ -10046,43 +10030,43 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="26" t="s">
+        <v>881</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>882</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="L75" s="4" t="s">
         <v>892</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="M75" s="4" t="s">
         <v>893</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>894</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>895</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>896</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>897</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>898</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>900</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="K75" s="4" t="s">
-        <v>902</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="M75" s="4" t="s">
-        <v>904</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="6"/>
@@ -10103,43 +10087,43 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="26" t="s">
+        <v>894</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>895</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="M76" s="4" t="s">
         <v>906</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>917</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="6"/>
@@ -10160,41 +10144,43 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="26" t="s">
+        <v>907</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>908</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="L77" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="M77" s="4" t="s">
         <v>919</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>926</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>928</v>
-      </c>
-      <c r="L77" s="3"/>
-      <c r="M77" s="4" t="s">
-        <v>929</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="6"/>
@@ -10215,43 +10201,41 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="K78" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="L78" s="3"/>
+      <c r="M78" s="4" t="s">
         <v>931</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>932</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>934</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>935</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>936</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>937</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>938</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>941</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" s="6"/>
@@ -10272,41 +10256,43 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="26" t="s">
+        <v>932</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>933</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="K79" s="4" t="s">
         <v>942</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="L79" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="M79" s="4" t="s">
         <v>943</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>945</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>947</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>949</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>950</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>951</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>952</v>
-      </c>
-      <c r="L79" s="3"/>
-      <c r="M79" s="4" t="s">
-        <v>953</v>
       </c>
       <c r="N79" s="3"/>
       <c r="O79" s="6"/>
@@ -10326,44 +10312,42 @@
       <c r="AC79" s="6"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="26" t="s">
+        <v>944</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K80" s="4" t="s">
         <v>954</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="L80" s="3"/>
+      <c r="M80" s="4" t="s">
         <v>955</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>956</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>957</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>959</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>960</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>961</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>964</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="M80" s="4" t="s">
-        <v>966</v>
       </c>
       <c r="N80" s="3"/>
       <c r="O80" s="6"/>
@@ -10383,158 +10367,158 @@
       <c r="AC80" s="6"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="18" t="s">
+      <c r="A81" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="B81" s="37" t="s">
+      <c r="M81" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="C81" s="38" t="s">
+      <c r="N81" s="3"/>
+      <c r="O81" s="6"/>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="6"/>
+      <c r="R81" s="6"/>
+      <c r="S81" s="6"/>
+      <c r="T81" s="6"/>
+      <c r="U81" s="6"/>
+      <c r="V81" s="6"/>
+      <c r="W81" s="6"/>
+      <c r="X81" s="6"/>
+      <c r="Y81" s="6"/>
+      <c r="Z81" s="6"/>
+      <c r="AA81" s="6"/>
+      <c r="AB81" s="6"/>
+      <c r="AC81" s="6"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="18" t="s">
         <v>969</v>
       </c>
-      <c r="D81" s="38" t="s">
+      <c r="B82" s="37" t="s">
         <v>970</v>
       </c>
-      <c r="E81" s="38" t="s">
+      <c r="C82" s="38" t="s">
         <v>971</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="D82" s="38" t="s">
         <v>972</v>
       </c>
-      <c r="G81" s="38" t="s">
+      <c r="E82" s="38" t="s">
         <v>973</v>
       </c>
-      <c r="H81" s="38" t="s">
+      <c r="F82" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="I81" s="38" t="s">
+      <c r="G82" s="38" t="s">
         <v>975</v>
       </c>
-      <c r="J81" s="38" t="s">
+      <c r="H82" s="38" t="s">
         <v>976</v>
       </c>
-      <c r="K81" s="38" t="s">
+      <c r="I82" s="38" t="s">
         <v>977</v>
       </c>
-      <c r="L81" s="38" t="s">
+      <c r="J82" s="38" t="s">
         <v>978</v>
       </c>
-      <c r="M81" s="4" t="s">
+      <c r="K82" s="38" t="s">
         <v>979</v>
       </c>
-      <c r="N81" s="19"/>
-      <c r="O81" s="20"/>
-      <c r="P81" s="21"/>
-      <c r="Q81" s="20"/>
-      <c r="R81" s="20"/>
-      <c r="S81" s="20"/>
-      <c r="T81" s="20"/>
-      <c r="U81" s="20"/>
-      <c r="V81" s="20"/>
-      <c r="W81" s="20"/>
-      <c r="X81" s="20"/>
-      <c r="Y81" s="20"/>
-      <c r="Z81" s="20"/>
-      <c r="AA81" s="20"/>
-      <c r="AB81" s="20"/>
-      <c r="AC81" s="20"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="4" t="s">
+      <c r="L82" s="38" t="s">
         <v>980</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="M82" s="4" t="s">
         <v>981</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>990</v>
-      </c>
-      <c r="M82" s="4" t="s">
-        <v>991</v>
-      </c>
-      <c r="N82" s="3"/>
-      <c r="O82" s="6"/>
-      <c r="P82" s="7"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
-      <c r="V82" s="6"/>
-      <c r="W82" s="6"/>
-      <c r="X82" s="6"/>
-      <c r="Y82" s="6"/>
-      <c r="Z82" s="6"/>
-      <c r="AA82" s="6"/>
-      <c r="AB82" s="6"/>
-      <c r="AC82" s="6"/>
+      <c r="N82" s="19"/>
+      <c r="O82" s="20"/>
+      <c r="P82" s="21"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="20"/>
+      <c r="V82" s="20"/>
+      <c r="W82" s="20"/>
+      <c r="X82" s="20"/>
+      <c r="Y82" s="20"/>
+      <c r="Z82" s="20"/>
+      <c r="AA82" s="20"/>
+      <c r="AB82" s="20"/>
+      <c r="AC82" s="20"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="L83" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="M83" s="4" t="s">
         <v>993</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>994</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>996</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="M83" s="4" t="s">
-        <v>1004</v>
       </c>
       <c r="N83" s="3"/>
       <c r="O83" s="6"/>
@@ -10555,43 +10539,43 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="M84" s="4" t="s">
         <v>1006</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="M84" s="4" t="s">
-        <v>1010</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="6"/>
@@ -10611,41 +10595,41 @@
       <c r="AC84" s="6"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L85" s="3" t="s">
         <v>1011</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>1014</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="L85" s="4" t="s">
-        <v>1015</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>1012</v>
@@ -10668,44 +10652,44 @@
       <c r="AC85" s="6"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="I86" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K86" s="4" t="s">
         <v>1017</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>1026</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>1027</v>
+      <c r="L86" s="4" t="s">
+        <v>1017</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="N86" s="3"/>
       <c r="O86" s="6"/>
@@ -10726,40 +10710,40 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L87" s="3" t="s">
         <v>1029</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>1033</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>1034</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>1030</v>
@@ -10781,45 +10765,45 @@
       <c r="AB87" s="6"/>
       <c r="AC87" s="6"/>
     </row>
-    <row r="88" ht="46.5" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="K88" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="L88" s="3" t="s">
         <v>1036</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>1041</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>1042</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>1043</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>1045</v>
-      </c>
-      <c r="M88" s="7" t="s">
-        <v>1046</v>
+      <c r="M88" s="4" t="s">
+        <v>1032</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="6"/>
@@ -10838,47 +10822,47 @@
       <c r="AB88" s="6"/>
       <c r="AC88" s="6"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="7" t="s">
+    <row r="89" ht="46.5" customHeight="1">
+      <c r="A89" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L89" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="M89" s="7" t="s">
         <v>1048</v>
       </c>
-      <c r="C89" s="7" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>1052</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>1053</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>1056</v>
-      </c>
-      <c r="K89" s="7" t="s">
-        <v>1057</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>1058</v>
-      </c>
-      <c r="M89" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="N89" s="6"/>
+      <c r="N89" s="3"/>
       <c r="O89" s="6"/>
       <c r="P89" s="7"/>
       <c r="Q89" s="6"/>
@@ -10896,46 +10880,46 @@
       <c r="AC89" s="6"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="L90" s="7" t="s">
         <v>1060</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="M90" s="4" t="s">
         <v>1061</v>
       </c>
-      <c r="C90" s="39" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>1065</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>1067</v>
-      </c>
-      <c r="I90" s="35" t="s">
-        <v>1068</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>1071</v>
-      </c>
-      <c r="M90" s="4" t="s">
-        <v>1072</v>
-      </c>
-      <c r="N90" s="3"/>
+      <c r="N90" s="6"/>
       <c r="O90" s="6"/>
       <c r="P90" s="7"/>
       <c r="Q90" s="6"/>
@@ -10953,44 +10937,44 @@
       <c r="AC90" s="6"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="14" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C91" s="39" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I91" s="35" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L91" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="M91" s="4" t="s">
         <v>1074</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>1080</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>1081</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>1082</v>
-      </c>
-      <c r="L91" s="19" t="s">
-        <v>1083</v>
-      </c>
-      <c r="M91" s="4" t="s">
-        <v>1084</v>
       </c>
       <c r="N91" s="3"/>
       <c r="O91" s="6"/>
@@ -11011,43 +10995,43 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L92" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="M92" s="4" t="s">
         <v>1086</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>1089</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="L92" s="19" t="s">
-        <v>1092</v>
-      </c>
-      <c r="M92" s="4" t="s">
-        <v>1093</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="6"/>
@@ -11066,49 +11050,49 @@
       <c r="AB92" s="6"/>
       <c r="AC92" s="6"/>
     </row>
-    <row r="93" ht="21.0" customHeight="1">
-      <c r="A93" s="14" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K93" s="4" t="s">
         <v>1094</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="L93" s="19" t="s">
+        <v>1094</v>
+      </c>
+      <c r="M93" s="4" t="s">
         <v>1095</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>1101</v>
-      </c>
-      <c r="I93" s="7" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J93" s="7" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K93" s="4" t="s">
-        <v>1104</v>
-      </c>
-      <c r="L93" s="4" t="s">
-        <v>1105</v>
-      </c>
-      <c r="M93" s="4" t="s">
-        <v>1106</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="6"/>
-      <c r="P93" s="6"/>
+      <c r="P93" s="7"/>
       <c r="Q93" s="6"/>
       <c r="R93" s="6"/>
       <c r="S93" s="6"/>
@@ -11123,45 +11107,45 @@
       <c r="AB93" s="6"/>
       <c r="AC93" s="6"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="21.0" customHeight="1">
       <c r="A94" s="14" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L94" s="4" t="s">
         <v>1107</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="M94" s="4" t="s">
         <v>1108</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>1110</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>1112</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>1113</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>1114</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>1115</v>
-      </c>
-      <c r="J94" s="7" t="s">
-        <v>1116</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>1117</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>1118</v>
-      </c>
-      <c r="M94" s="7" t="s">
-        <v>1119</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" s="6"/>
@@ -11182,45 +11166,45 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L95" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="M95" s="7" t="s">
         <v>1121</v>
       </c>
-      <c r="C95" s="7" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>1126</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>1127</v>
-      </c>
-      <c r="I95" s="7" t="s">
-        <v>1128</v>
-      </c>
-      <c r="J95" s="7" t="s">
-        <v>1129</v>
-      </c>
-      <c r="K95" s="41" t="s">
-        <v>1130</v>
-      </c>
-      <c r="L95" s="42" t="s">
-        <v>1131</v>
-      </c>
-      <c r="M95" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="N95" s="6"/>
+      <c r="N95" s="3"/>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
@@ -11239,43 +11223,43 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="14" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K96" s="41" t="s">
+        <v>1132</v>
+      </c>
+      <c r="L96" s="42" t="s">
         <v>1133</v>
       </c>
-      <c r="B96" s="43" t="s">
+      <c r="M96" s="7" t="s">
         <v>1134</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>1136</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>1138</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>1139</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>1141</v>
-      </c>
-      <c r="J96" s="44" t="s">
-        <v>1142</v>
-      </c>
-      <c r="K96" s="41" t="s">
-        <v>1143</v>
-      </c>
-      <c r="L96" s="41" t="s">
-        <v>1144</v>
-      </c>
-      <c r="M96" s="7" t="s">
-        <v>1145</v>
       </c>
       <c r="N96" s="6"/>
       <c r="O96" s="6"/>
@@ -11295,18 +11279,45 @@
       <c r="AC96" s="6"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="45"/>
-      <c r="L97" s="45"/>
+      <c r="A97" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B97" s="43" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="J97" s="44" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K97" s="41" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L97" s="41" t="s">
+        <v>1146</v>
+      </c>
+      <c r="M97" s="7" t="s">
+        <v>1147</v>
+      </c>
       <c r="N97" s="6"/>
       <c r="O97" s="6"/>
       <c r="P97" s="6"/>
@@ -11337,7 +11348,6 @@
       <c r="J98" s="6"/>
       <c r="K98" s="45"/>
       <c r="L98" s="45"/>
-      <c r="M98" s="6"/>
       <c r="N98" s="6"/>
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
@@ -11459,7 +11469,7 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
-      <c r="K102" s="41"/>
+      <c r="K102" s="45"/>
       <c r="L102" s="45"/>
       <c r="M102" s="6"/>
       <c r="N102" s="6"/>
@@ -11490,7 +11500,7 @@
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
-      <c r="K103" s="45"/>
+      <c r="K103" s="41"/>
       <c r="L103" s="45"/>
       <c r="M103" s="6"/>
       <c r="N103" s="6"/>
@@ -17215,35 +17225,35 @@
       <c r="AC287" s="6"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="46"/>
-      <c r="B288" s="46"/>
-      <c r="C288" s="46"/>
-      <c r="D288" s="46"/>
-      <c r="E288" s="46"/>
-      <c r="F288" s="46"/>
-      <c r="G288" s="46"/>
-      <c r="H288" s="46"/>
-      <c r="I288" s="46"/>
-      <c r="J288" s="46"/>
-      <c r="K288" s="46"/>
-      <c r="L288" s="46"/>
-      <c r="M288" s="46"/>
-      <c r="N288" s="46"/>
-      <c r="O288" s="46"/>
-      <c r="P288" s="46"/>
-      <c r="Q288" s="46"/>
-      <c r="R288" s="46"/>
-      <c r="S288" s="46"/>
-      <c r="T288" s="46"/>
-      <c r="U288" s="46"/>
-      <c r="V288" s="46"/>
-      <c r="W288" s="46"/>
-      <c r="X288" s="46"/>
-      <c r="Y288" s="46"/>
-      <c r="Z288" s="46"/>
-      <c r="AA288" s="46"/>
-      <c r="AB288" s="46"/>
-      <c r="AC288" s="46"/>
+      <c r="A288" s="6"/>
+      <c r="B288" s="6"/>
+      <c r="C288" s="6"/>
+      <c r="D288" s="6"/>
+      <c r="E288" s="6"/>
+      <c r="F288" s="6"/>
+      <c r="G288" s="6"/>
+      <c r="H288" s="6"/>
+      <c r="I288" s="6"/>
+      <c r="J288" s="6"/>
+      <c r="K288" s="45"/>
+      <c r="L288" s="45"/>
+      <c r="M288" s="6"/>
+      <c r="N288" s="6"/>
+      <c r="O288" s="6"/>
+      <c r="P288" s="6"/>
+      <c r="Q288" s="6"/>
+      <c r="R288" s="6"/>
+      <c r="S288" s="6"/>
+      <c r="T288" s="6"/>
+      <c r="U288" s="6"/>
+      <c r="V288" s="6"/>
+      <c r="W288" s="6"/>
+      <c r="X288" s="6"/>
+      <c r="Y288" s="6"/>
+      <c r="Z288" s="6"/>
+      <c r="AA288" s="6"/>
+      <c r="AB288" s="6"/>
+      <c r="AC288" s="6"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="46"/>
@@ -38263,38 +38273,69 @@
       <c r="AB966" s="46"/>
       <c r="AC966" s="46"/>
     </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="A967" s="46"/>
+      <c r="B967" s="46"/>
+      <c r="C967" s="46"/>
+      <c r="D967" s="46"/>
+      <c r="E967" s="46"/>
+      <c r="F967" s="46"/>
+      <c r="G967" s="46"/>
+      <c r="H967" s="46"/>
+      <c r="I967" s="46"/>
+      <c r="J967" s="46"/>
+      <c r="K967" s="46"/>
+      <c r="L967" s="46"/>
+      <c r="M967" s="46"/>
+      <c r="N967" s="46"/>
+      <c r="O967" s="46"/>
+      <c r="P967" s="46"/>
+      <c r="Q967" s="46"/>
+      <c r="R967" s="46"/>
+      <c r="S967" s="46"/>
+      <c r="T967" s="46"/>
+      <c r="U967" s="46"/>
+      <c r="V967" s="46"/>
+      <c r="W967" s="46"/>
+      <c r="X967" s="46"/>
+      <c r="Y967" s="46"/>
+      <c r="Z967" s="46"/>
+      <c r="AA967" s="46"/>
+      <c r="AB967" s="46"/>
+      <c r="AC967" s="46"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:M95">
+  <conditionalFormatting sqref="A1:M96">
     <cfRule type="containsBlanks" dxfId="4" priority="1">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B106">
+  <conditionalFormatting sqref="B107">
     <cfRule type="notContainsBlanks" dxfId="5" priority="2">
-      <formula>LEN(TRIM(B106))&gt;0</formula>
+      <formula>LEN(TRIM(B107))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M95 A96:L96 N96">
+  <conditionalFormatting sqref="M96 A97:L97 N97">
     <cfRule type="containsBlanks" dxfId="4" priority="3">
-      <formula>LEN(TRIM(M95))=0</formula>
+      <formula>LEN(TRIM(M96))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F111">
+  <conditionalFormatting sqref="F112">
     <cfRule type="notContainsBlanks" dxfId="5" priority="4">
-      <formula>LEN(TRIM(F111))&gt;0</formula>
+      <formula>LEN(TRIM(F112))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink r:id="rId4" ref="B81"/>
-    <hyperlink r:id="rId5" ref="C81"/>
-    <hyperlink r:id="rId6" ref="D81"/>
-    <hyperlink r:id="rId7" ref="E81"/>
-    <hyperlink r:id="rId8" ref="G81"/>
-    <hyperlink r:id="rId9" ref="H81"/>
-    <hyperlink r:id="rId10" ref="I81"/>
-    <hyperlink r:id="rId11" ref="J81"/>
-    <hyperlink r:id="rId12" ref="K81"/>
-    <hyperlink r:id="rId13" ref="L81"/>
+    <hyperlink r:id="rId4" ref="B82"/>
+    <hyperlink r:id="rId5" ref="C82"/>
+    <hyperlink r:id="rId6" ref="D82"/>
+    <hyperlink r:id="rId7" ref="E82"/>
+    <hyperlink r:id="rId8" ref="G82"/>
+    <hyperlink r:id="rId9" ref="H82"/>
+    <hyperlink r:id="rId10" ref="I82"/>
+    <hyperlink r:id="rId11" ref="J82"/>
+    <hyperlink r:id="rId12" ref="K82"/>
+    <hyperlink r:id="rId13" ref="L82"/>
   </hyperlinks>
   <drawing r:id="rId14"/>
   <legacyDrawing r:id="rId15"/>
